--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G25">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G54">

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU65"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,7 +919,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G5">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-31 11:30:00</t>
+          <t>2026-08-31 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-31 12:00:00</t>
+          <t>2026-08-31 11:30:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G8">
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-31 12:45:00</t>
+          <t>2026-08-31 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-31 13:00:00</t>
+          <t>2026-08-31 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G13">
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G15">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-31 13:15:00</t>
+          <t>2026-08-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-08-31 13:30:00</t>
+          <t>2026-08-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-08-31 13:30:00</t>
+          <t>2026-08-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-31 14:00:00</t>
+          <t>2026-08-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-31 14:00:00</t>
+          <t>2026-08-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-31 14:30:00</t>
+          <t>2026-08-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-31 14:30:00</t>
+          <t>2026-08-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-31 15:00:00</t>
+          <t>2026-08-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-08-31 15:00:00</t>
+          <t>2026-08-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-31 15:15:00</t>
+          <t>2026-08-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-31 15:15:00</t>
+          <t>2026-08-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-31 15:30:00</t>
+          <t>2026-08-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-08-31 15:30:00</t>
+          <t>2026-08-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G46">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-08-31 15:45:00</t>
+          <t>2026-08-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-08-31 15:45:00</t>
+          <t>2026-08-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00:00</t>
+          <t>2026-08-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00:00</t>
+          <t>2026-08-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G54">
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-31 16:15:00</t>
+          <t>2026-08-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-08-31 16:30:00</t>
+          <t>2026-08-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-31 16:30:00</t>
+          <t>2026-08-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-31 19:00:00</t>
+          <t>2026-08-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G59">
@@ -9935,55 +9935,55 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-31 19:15:00</t>
+          <t>2026-08-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:00</t>
+          <t>2026-08-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:00</t>
+          <t>2026-08-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-31 21:00:00</t>
+          <t>2026-08-31 19:00:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-31 21:00:00</t>
+          <t>2026-08-31 19:15:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-08-31 21:00:00</t>
+          <t>2026-08-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10857,156 +10857,808 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-08-31 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Boston Legacy W</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>21:45</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Universidad Católica</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>2026-08-31 21:45:00</t>
         </is>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G9">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-31 12:45:00</t>
+          <t>2026-08-31 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-31 13:00:00</t>
+          <t>2026-08-31 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G16">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-31 13:15:00</t>
+          <t>2026-08-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G19">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-31 13:30:00</t>
+          <t>2026-08-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G23">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-31 14:00:00</t>
+          <t>2026-08-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N30">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-31 14:30:00</t>
+          <t>2026-08-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-31 15:00:00</t>
+          <t>2026-08-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-31 15:15:00</t>
+          <t>2026-08-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-08-31 15:30:00</t>
+          <t>2026-08-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-08-31 15:45:00</t>
+          <t>2026-08-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00:00</t>
+          <t>2026-08-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G56">
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-31 16:15:00</t>
+          <t>2026-08-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,65 +9926,65 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q59">
-        <v>1.39</v>
+        <v>2.23</v>
       </c>
       <c r="R59">
-        <v>3.69</v>
+        <v>2.32</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="T59">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="U59">
+        <v>2.87</v>
+      </c>
+      <c r="V59">
+        <v>1.4</v>
+      </c>
+      <c r="W59">
+        <v>1.08</v>
+      </c>
+      <c r="X59">
+        <v>1.05</v>
+      </c>
+      <c r="Y59">
+        <v>1.25</v>
+      </c>
+      <c r="Z59">
+        <v>3.3</v>
+      </c>
+      <c r="AA59">
+        <v>1.91</v>
+      </c>
+      <c r="AB59">
+        <v>1.85</v>
+      </c>
+      <c r="AC59">
+        <v>3.12</v>
+      </c>
+      <c r="AD59">
+        <v>1.33</v>
+      </c>
+      <c r="AE59">
+        <v>1.11</v>
+      </c>
+      <c r="AF59">
         <v>1.8</v>
       </c>
-      <c r="V59">
+      <c r="AG59">
         <v>1.91</v>
       </c>
-      <c r="W59">
-        <v>1.22</v>
-      </c>
-      <c r="X59">
-        <v>1.01</v>
-      </c>
-      <c r="Y59">
-        <v>1.06</v>
-      </c>
-      <c r="Z59">
-        <v>7.5</v>
-      </c>
-      <c r="AA59">
-        <v>1.29</v>
-      </c>
-      <c r="AB59">
-        <v>3.3</v>
-      </c>
-      <c r="AC59">
-        <v>1.78</v>
-      </c>
-      <c r="AD59">
-        <v>1.98</v>
-      </c>
-      <c r="AE59">
-        <v>1.36</v>
-      </c>
-      <c r="AF59">
-        <v>1.95</v>
-      </c>
-      <c r="AG59">
-        <v>1.75</v>
-      </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>7.6</v>
+        <v>2.12</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G60">
@@ -10098,55 +10098,55 @@
         <v>0</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-31 16:30:00</t>
+          <t>2026-08-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G61">
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-31 19:00:00</t>
+          <t>2026-08-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-31 19:15:00</t>
+          <t>2026-08-31 19:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:00</t>
+          <t>2026-08-31 19:15:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:00</t>
+          <t>2026-08-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-08-31 21:00:00</t>
+          <t>2026-08-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G68">
@@ -11509,156 +11509,319 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Boston Legacy W</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>0</v>
+      </c>
+      <c r="AB69">
+        <v>0</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69">
+        <v>0</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>21:45</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Universidad Católica</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>2026-08-31 21:45:00</t>
         </is>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1489,25 +1489,25 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G9">
@@ -2274,16 +2274,16 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -2298,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="O33">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>5.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W33">
         <v>1.13</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA33">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AB33">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AC33">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AD33">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE33">
         <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="V34">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA34">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AC34">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>1.55</v>
+      </c>
+      <c r="O35">
+        <v>4.15</v>
+      </c>
+      <c r="P35">
+        <v>5.05</v>
+      </c>
+      <c r="Q35">
+        <v>1.96</v>
+      </c>
+      <c r="R35">
+        <v>2.61</v>
+      </c>
+      <c r="S35">
+        <v>1.22</v>
+      </c>
+      <c r="T35">
+        <v>3.64</v>
+      </c>
+      <c r="U35">
+        <v>2.2</v>
+      </c>
+      <c r="V35">
         <v>1.6</v>
       </c>
-      <c r="O35">
-        <v>3.9</v>
-      </c>
-      <c r="P35">
-        <v>4.6</v>
-      </c>
-      <c r="Q35">
-        <v>2.08</v>
-      </c>
-      <c r="R35">
-        <v>2.28</v>
-      </c>
-      <c r="S35">
-        <v>1.29</v>
-      </c>
-      <c r="T35">
-        <v>3.3</v>
-      </c>
-      <c r="U35">
-        <v>2.34</v>
-      </c>
-      <c r="V35">
-        <v>1.51</v>
-      </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA35">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AB35">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
         <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL57">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,10 +6675,10 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -6687,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -6705,25 +6705,25 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>2.65</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -7339,10 +7339,10 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -7351,31 +7351,31 @@
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q60">
         <v>1.39</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q69">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>3.48</v>
+      </c>
+      <c r="O47">
+        <v>3.74</v>
+      </c>
+      <c r="P47">
+        <v>1.97</v>
+      </c>
+      <c r="Q47">
+        <v>3.9</v>
+      </c>
+      <c r="R47">
+        <v>2.39</v>
+      </c>
+      <c r="S47">
+        <v>1.3</v>
+      </c>
+      <c r="T47">
+        <v>3.3</v>
+      </c>
+      <c r="U47">
+        <v>2.5</v>
+      </c>
+      <c r="V47">
         <v>1.47</v>
       </c>
-      <c r="O47">
-        <v>4.2</v>
-      </c>
-      <c r="P47">
-        <v>6.5</v>
-      </c>
-      <c r="Q47">
-        <v>1.95</v>
-      </c>
-      <c r="R47">
-        <v>2.33</v>
-      </c>
-      <c r="S47">
-        <v>1.33</v>
-      </c>
-      <c r="T47">
-        <v>2.88</v>
-      </c>
-      <c r="U47">
-        <v>2.48</v>
-      </c>
-      <c r="V47">
-        <v>1.44</v>
-      </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AB47">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AC47">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="AD47">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AG47">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.48</v>
+        <v>1.47</v>
       </c>
       <c r="O48">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>1.97</v>
+        <v>6.5</v>
       </c>
       <c r="Q48">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V48">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA48">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AB48">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AC48">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AE48">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AG48">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.2</v>
+        <v>2.55</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.48</v>
+        <v>1.47</v>
       </c>
       <c r="O47">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="P47">
-        <v>1.97</v>
+        <v>6.5</v>
       </c>
       <c r="Q47">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="R47">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V47">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z47">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA47">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AB47">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AC47">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AG47">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.2</v>
+        <v>2.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>3.48</v>
+      </c>
+      <c r="O48">
+        <v>3.74</v>
+      </c>
+      <c r="P48">
+        <v>1.97</v>
+      </c>
+      <c r="Q48">
+        <v>3.9</v>
+      </c>
+      <c r="R48">
+        <v>2.39</v>
+      </c>
+      <c r="S48">
+        <v>1.3</v>
+      </c>
+      <c r="T48">
+        <v>3.3</v>
+      </c>
+      <c r="U48">
+        <v>2.5</v>
+      </c>
+      <c r="V48">
         <v>1.47</v>
       </c>
-      <c r="O48">
-        <v>4.2</v>
-      </c>
-      <c r="P48">
-        <v>6.5</v>
-      </c>
-      <c r="Q48">
-        <v>1.95</v>
-      </c>
-      <c r="R48">
-        <v>2.33</v>
-      </c>
-      <c r="S48">
-        <v>1.33</v>
-      </c>
-      <c r="T48">
-        <v>2.88</v>
-      </c>
-      <c r="U48">
-        <v>2.48</v>
-      </c>
-      <c r="V48">
-        <v>1.44</v>
-      </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AC48">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="AD48">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AG48">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="O59">
-        <v>3.65</v>
+        <v>8.25</v>
       </c>
       <c r="P59">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="Q59">
-        <v>2.23</v>
+        <v>1.39</v>
       </c>
       <c r="R59">
-        <v>2.32</v>
+        <v>3.69</v>
       </c>
       <c r="S59">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="U59">
-        <v>2.87</v>
+        <v>1.8</v>
       </c>
       <c r="V59">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="Z59">
+        <v>7.5</v>
+      </c>
+      <c r="AA59">
+        <v>1.29</v>
+      </c>
+      <c r="AB59">
         <v>3.3</v>
       </c>
-      <c r="AA59">
-        <v>1.91</v>
-      </c>
-      <c r="AB59">
-        <v>1.85</v>
-      </c>
       <c r="AC59">
-        <v>3.12</v>
+        <v>1.78</v>
       </c>
       <c r="AD59">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF59">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG59">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AK59">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,65 +10089,65 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="O60">
-        <v>8.25</v>
+        <v>3.65</v>
       </c>
       <c r="P60">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="Q60">
-        <v>1.39</v>
+        <v>2.23</v>
       </c>
       <c r="R60">
-        <v>3.69</v>
+        <v>2.32</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="T60">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="U60">
+        <v>2.87</v>
+      </c>
+      <c r="V60">
+        <v>1.4</v>
+      </c>
+      <c r="W60">
+        <v>1.08</v>
+      </c>
+      <c r="X60">
+        <v>1.05</v>
+      </c>
+      <c r="Y60">
+        <v>1.25</v>
+      </c>
+      <c r="Z60">
+        <v>3.3</v>
+      </c>
+      <c r="AA60">
+        <v>1.91</v>
+      </c>
+      <c r="AB60">
+        <v>1.85</v>
+      </c>
+      <c r="AC60">
+        <v>3.12</v>
+      </c>
+      <c r="AD60">
+        <v>1.33</v>
+      </c>
+      <c r="AE60">
+        <v>1.11</v>
+      </c>
+      <c r="AF60">
         <v>1.8</v>
       </c>
-      <c r="V60">
+      <c r="AG60">
         <v>1.91</v>
       </c>
-      <c r="W60">
-        <v>1.22</v>
-      </c>
-      <c r="X60">
-        <v>1.01</v>
-      </c>
-      <c r="Y60">
-        <v>1.06</v>
-      </c>
-      <c r="Z60">
-        <v>7.5</v>
-      </c>
-      <c r="AA60">
-        <v>1.29</v>
-      </c>
-      <c r="AB60">
-        <v>3.3</v>
-      </c>
-      <c r="AC60">
-        <v>1.78</v>
-      </c>
-      <c r="AD60">
-        <v>1.98</v>
-      </c>
-      <c r="AE60">
-        <v>1.36</v>
-      </c>
-      <c r="AF60">
-        <v>1.95</v>
-      </c>
-      <c r="AG60">
-        <v>1.75</v>
-      </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>7.6</v>
+        <v>2.12</v>
       </c>
       <c r="AL60">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1305,13 +1305,13 @@
         <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
         <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.1</v>
@@ -1323,16 +1323,16 @@
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA6">
         <v>1.73</v>
       </c>
       <c r="AB6">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="AD6">
         <v>1.43</v>
@@ -1344,7 +1344,7 @@
         <v>1.72</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,58 +1450,58 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA7">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB7">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AC7">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD7">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE7">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
         <v>1.46</v>
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q67">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q38">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="R38">
         <v>2</v>
@@ -6536,10 +6536,10 @@
         <v>1.06</v>
       </c>
       <c r="Y38">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Z38">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AA38">
         <v>2.66</v>
@@ -6557,10 +6557,10 @@
         <v>1</v>
       </c>
       <c r="AF38">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG38">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK38">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4713,7 +4713,7 @@
         <v>1.66</v>
       </c>
       <c r="O27">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
         <v>5.1</v>
@@ -4725,10 +4725,10 @@
         <v>2.01</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U27">
         <v>2.96</v>
@@ -4740,7 +4740,7 @@
         <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
         <v>1.36</v>
@@ -4749,19 +4749,19 @@
         <v>2.92</v>
       </c>
       <c r="AA27">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AB27">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
         <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
         <v>1.95</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>13.5</v>
       </c>
       <c r="Q37">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="R37">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T37">
         <v>4</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="V37">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="W37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB37">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="AC37">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AD37">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AG37">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK37">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -7007,7 +7007,7 @@
         <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
         <v>2.88</v>
@@ -7019,37 +7019,37 @@
         <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
         <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AB41">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC41">
         <v>3.6</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG41">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8296,25 +8296,25 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q49">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="R49">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S49">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T49">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="U49">
         <v>3.2</v>
@@ -8323,37 +8323,37 @@
         <v>1.3</v>
       </c>
       <c r="W49">
+        <v>1.02</v>
+      </c>
+      <c r="X49">
+        <v>1.04</v>
+      </c>
+      <c r="Y49">
+        <v>1.39</v>
+      </c>
+      <c r="Z49">
+        <v>2.59</v>
+      </c>
+      <c r="AA49">
+        <v>2.4</v>
+      </c>
+      <c r="AB49">
+        <v>1.6</v>
+      </c>
+      <c r="AC49">
+        <v>4.4</v>
+      </c>
+      <c r="AD49">
+        <v>1.14</v>
+      </c>
+      <c r="AE49">
         <v>1.01</v>
       </c>
-      <c r="X49">
-        <v>1.03</v>
-      </c>
-      <c r="Y49">
-        <v>1.33</v>
-      </c>
-      <c r="Z49">
-        <v>2.83</v>
-      </c>
-      <c r="AA49">
-        <v>2.12</v>
-      </c>
-      <c r="AB49">
-        <v>1.63</v>
-      </c>
-      <c r="AC49">
-        <v>3.76</v>
-      </c>
-      <c r="AD49">
-        <v>1.19</v>
-      </c>
-      <c r="AE49">
-        <v>1.02</v>
-      </c>
       <c r="AF49">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AG49">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q54">
-        <v>4.04</v>
+        <v>3.64</v>
       </c>
       <c r="R54">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T54">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U54">
+        <v>2.97</v>
+      </c>
+      <c r="V54">
+        <v>1.31</v>
+      </c>
+      <c r="W54">
+        <v>1.02</v>
+      </c>
+      <c r="X54">
+        <v>1.01</v>
+      </c>
+      <c r="Y54">
+        <v>1.31</v>
+      </c>
+      <c r="Z54">
         <v>2.92</v>
       </c>
-      <c r="V54">
-        <v>1.32</v>
-      </c>
-      <c r="W54">
-        <v>1.06</v>
-      </c>
-      <c r="X54">
-        <v>1.02</v>
-      </c>
-      <c r="Y54">
+      <c r="AA54">
+        <v>2.06</v>
+      </c>
+      <c r="AB54">
+        <v>1.71</v>
+      </c>
+      <c r="AC54">
+        <v>3.72</v>
+      </c>
+      <c r="AD54">
+        <v>1.2</v>
+      </c>
+      <c r="AE54">
+        <v>1.03</v>
+      </c>
+      <c r="AF54">
+        <v>1.82</v>
+      </c>
+      <c r="AG54">
+        <v>1.82</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>1.25</v>
+      </c>
+      <c r="AK54">
         <v>1.3</v>
-      </c>
-      <c r="Z54">
-        <v>2.97</v>
-      </c>
-      <c r="AA54">
-        <v>2.01</v>
-      </c>
-      <c r="AB54">
-        <v>1.7</v>
-      </c>
-      <c r="AC54">
-        <v>3.42</v>
-      </c>
-      <c r="AD54">
-        <v>1.23</v>
-      </c>
-      <c r="AE54">
-        <v>1.05</v>
-      </c>
-      <c r="AF54">
-        <v>1.76</v>
-      </c>
-      <c r="AG54">
-        <v>1.91</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.57</v>
-      </c>
-      <c r="AK54">
-        <v>1.28</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="R55">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T55">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U55">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="V55">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W55">
+        <v>1.02</v>
+      </c>
+      <c r="X55">
         <v>1.04</v>
       </c>
-      <c r="X55">
+      <c r="Y55">
+        <v>1.38</v>
+      </c>
+      <c r="Z55">
+        <v>2.68</v>
+      </c>
+      <c r="AA55">
+        <v>2.23</v>
+      </c>
+      <c r="AB55">
+        <v>1.57</v>
+      </c>
+      <c r="AC55">
+        <v>4</v>
+      </c>
+      <c r="AD55">
+        <v>1.17</v>
+      </c>
+      <c r="AE55">
         <v>1.02</v>
       </c>
-      <c r="Y55">
-        <v>1.28</v>
-      </c>
-      <c r="Z55">
-        <v>3.08</v>
-      </c>
-      <c r="AA55">
-        <v>1.93</v>
-      </c>
-      <c r="AB55">
-        <v>1.76</v>
-      </c>
-      <c r="AC55">
-        <v>3.2</v>
-      </c>
-      <c r="AD55">
-        <v>1.26</v>
-      </c>
-      <c r="AE55">
-        <v>1.06</v>
-      </c>
       <c r="AF55">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q56">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R56">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="S56">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T56">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="U56">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V56">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W56">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X56">
+        <v>1.03</v>
+      </c>
+      <c r="Y56">
+        <v>1.37</v>
+      </c>
+      <c r="Z56">
+        <v>2.66</v>
+      </c>
+      <c r="AA56">
+        <v>2.36</v>
+      </c>
+      <c r="AB56">
+        <v>1.56</v>
+      </c>
+      <c r="AC56">
+        <v>4.2</v>
+      </c>
+      <c r="AD56">
+        <v>1.15</v>
+      </c>
+      <c r="AE56">
         <v>1.01</v>
       </c>
-      <c r="Y56">
-        <v>1.29</v>
-      </c>
-      <c r="Z56">
-        <v>3.04</v>
-      </c>
-      <c r="AA56">
-        <v>2.01</v>
-      </c>
-      <c r="AB56">
-        <v>1.7</v>
-      </c>
-      <c r="AC56">
-        <v>3.5</v>
-      </c>
-      <c r="AD56">
-        <v>1.22</v>
-      </c>
-      <c r="AE56">
-        <v>1.04</v>
-      </c>
       <c r="AF56">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AG56">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,65 +9600,65 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q57">
-        <v>4.34</v>
+        <v>3.64</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T57">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="U57">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="V57">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W57">
         <v>1.04</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="Z57">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AA57">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="AB57">
+        <v>1.51</v>
+      </c>
+      <c r="AC57">
+        <v>4.4</v>
+      </c>
+      <c r="AD57">
+        <v>1.14</v>
+      </c>
+      <c r="AE57">
+        <v>1.01</v>
+      </c>
+      <c r="AF57">
+        <v>1.95</v>
+      </c>
+      <c r="AG57">
         <v>1.7</v>
       </c>
-      <c r="AC57">
-        <v>3.34</v>
-      </c>
-      <c r="AD57">
-        <v>1.24</v>
-      </c>
-      <c r="AE57">
-        <v>1.05</v>
-      </c>
-      <c r="AF57">
-        <v>1.78</v>
-      </c>
-      <c r="AG57">
-        <v>1.86</v>
-      </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,61 +9926,61 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O59">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P59">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Q59">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="R59">
-        <v>3.69</v>
+        <v>2.96</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U59">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V59">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="W59">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z59">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA59">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AC59">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AD59">
+        <v>1.9</v>
+      </c>
+      <c r="AE59">
+        <v>1.3</v>
+      </c>
+      <c r="AF59">
         <v>1.98</v>
-      </c>
-      <c r="AE59">
-        <v>1.36</v>
-      </c>
-      <c r="AF59">
-        <v>1.95</v>
       </c>
       <c r="AG59">
         <v>1.75</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK59">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O60">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q60">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="R60">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="S60">
+        <v>1.4</v>
+      </c>
+      <c r="T60">
+        <v>2.73</v>
+      </c>
+      <c r="U60">
+        <v>2.63</v>
+      </c>
+      <c r="V60">
         <v>1.37</v>
       </c>
-      <c r="T60">
-        <v>3</v>
-      </c>
-      <c r="U60">
-        <v>2.87</v>
-      </c>
-      <c r="V60">
-        <v>1.4</v>
-      </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z60">
         <v>3.3</v>
       </c>
       <c r="AA60">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB60">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC60">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AD60">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
         <v>1.8</v>
       </c>
       <c r="AG60">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AL60">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1299,28 +1299,28 @@
         <v>4.1</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
         <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="U6">
         <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
         <v>4.05</v>
@@ -1459,55 +1459,55 @@
         <v>1.52</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="R7">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="S7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="U7">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB7">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AC7">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD7">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AG7">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q12">
         <v>2.63</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
         <v>2.7</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
         <v>1.76</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
         <v>3.24</v>
       </c>
       <c r="P17">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>4.34</v>
+        <v>3.35</v>
       </c>
       <c r="R17">
         <v>2.2</v>
@@ -3098,28 +3098,28 @@
         <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="AA17">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB17">
         <v>1.8</v>
@@ -3128,16 +3128,16 @@
         <v>3.05</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
         <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK17">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>3.18</v>
       </c>
       <c r="R21">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="S21">
         <v>1.55</v>
@@ -3765,19 +3765,19 @@
         <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z21">
         <v>2.58</v>
       </c>
       <c r="AA21">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AB21">
         <v>1.49</v>
       </c>
       <c r="AC21">
-        <v>4.87</v>
+        <v>4.65</v>
       </c>
       <c r="AD21">
         <v>1.12</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AK21">
         <v>1.52</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="O22">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q22">
-        <v>4.8</v>
+        <v>4.52</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
         <v>1.34</v>
       </c>
       <c r="T22">
-        <v>3.09</v>
+        <v>2.99</v>
       </c>
       <c r="U22">
         <v>2.69</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z22">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD22">
         <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG22">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.14</v>
@@ -4058,22 +4058,22 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="P23">
         <v>6.6</v>
       </c>
       <c r="Q23">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="R23">
         <v>2.42</v>
       </c>
       <c r="S23">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
         <v>3.36</v>
@@ -4082,31 +4082,31 @@
         <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB23">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC23">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE23">
         <v>1.17</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Q24">
-        <v>5.42</v>
+        <v>7.2</v>
       </c>
       <c r="R24">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="S24">
         <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="V24">
+        <v>1.36</v>
+      </c>
+      <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
         <v>1.35</v>
       </c>
-      <c r="W24">
-        <v>1.04</v>
-      </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>1.33</v>
-      </c>
       <c r="Z24">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA24">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB24">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC24">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AG24">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4396,13 +4396,13 @@
         <v>3.04</v>
       </c>
       <c r="R25">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.4</v>
       </c>
       <c r="T25">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U25">
         <v>2.9</v>
@@ -4411,7 +4411,7 @@
         <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.02</v>
@@ -4426,7 +4426,7 @@
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC25">
         <v>3.42</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
         <v>1.44</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="S29">
         <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="U29">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA29">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB29">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC29">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD29">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF29">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,43 +5525,43 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O32">
         <v>3.3</v>
       </c>
       <c r="P32">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q32">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="R32">
         <v>2.06</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
         <v>2.84</v>
       </c>
       <c r="U32">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA32">
         <v>1.86</v>
@@ -5570,19 +5570,19 @@
         <v>1.89</v>
       </c>
       <c r="AC32">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
         <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q33">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R33">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
         <v>1.22</v>
@@ -5709,34 +5709,34 @@
         <v>3.75</v>
       </c>
       <c r="U33">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="V33">
         <v>1.7</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z33">
         <v>5.2</v>
       </c>
       <c r="AA33">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AB33">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AC33">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD33">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE33">
         <v>1.22</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
         <v>1.96</v>
@@ -5854,7 +5854,7 @@
         <v>1.6</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
         <v>4.6</v>
@@ -5866,46 +5866,46 @@
         <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="V34">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD34">
         <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
         <v>2.08</v>
@@ -5924,7 +5924,7 @@
         <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>5.05</v>
+        <v>5.41</v>
       </c>
       <c r="Q35">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="R35">
         <v>2.61</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W35">
         <v>1.13</v>
@@ -6047,16 +6047,16 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA35">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB35">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC35">
         <v>2.35</v>
@@ -6065,10 +6065,10 @@
         <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
         <v>2.2</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,31 +6180,31 @@
         <v>1.33</v>
       </c>
       <c r="O36">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P36">
-        <v>6.5</v>
+        <v>7.35</v>
       </c>
       <c r="Q36">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
         <v>2.85</v>
       </c>
       <c r="S36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U36">
         <v>2.12</v>
       </c>
       <c r="V36">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6213,7 +6213,7 @@
         <v>1.09</v>
       </c>
       <c r="Z36">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA36">
         <v>1.47</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6512,46 +6512,46 @@
         <v>3.8</v>
       </c>
       <c r="Q38">
-        <v>2.68</v>
+        <v>2.97</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S38">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="T38">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U38">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="V38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X38">
         <v>1.06</v>
       </c>
       <c r="Y38">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z38">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AA38">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AB38">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AC38">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AD38">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE38">
         <v>1</v>
@@ -6560,7 +6560,7 @@
         <v>2.2</v>
       </c>
       <c r="AG38">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O40">
+        <v>3.8</v>
+      </c>
+      <c r="P40">
+        <v>3.75</v>
+      </c>
+      <c r="Q40">
+        <v>2.2</v>
+      </c>
+      <c r="R40">
+        <v>2.43</v>
+      </c>
+      <c r="S40">
+        <v>1.22</v>
+      </c>
+      <c r="T40">
         <v>3.9</v>
       </c>
-      <c r="P40">
-        <v>3.9</v>
-      </c>
-      <c r="Q40">
-        <v>2.15</v>
-      </c>
-      <c r="R40">
-        <v>2.46</v>
-      </c>
-      <c r="S40">
-        <v>1.25</v>
-      </c>
-      <c r="T40">
-        <v>3.75</v>
-      </c>
       <c r="U40">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5.6</v>
+        <v>5.41</v>
       </c>
       <c r="AA40">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AC40">
         <v>2.14</v>
       </c>
       <c r="AD40">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AE40">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
         <v>1.98</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O46">
         <v>3.6</v>
       </c>
       <c r="P46">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q46">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S46">
         <v>1.47</v>
@@ -7828,13 +7828,13 @@
         <v>2.47</v>
       </c>
       <c r="U46">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V46">
         <v>1.3</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
         <v>1.04</v>
@@ -7843,28 +7843,28 @@
         <v>1.38</v>
       </c>
       <c r="Z46">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA46">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AB46">
         <v>1.6</v>
       </c>
       <c r="AC46">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AD46">
         <v>1.17</v>
       </c>
       <c r="AE46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="AG46">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7982,52 +7982,52 @@
         <v>1.95</v>
       </c>
       <c r="R47">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S47">
         <v>1.33</v>
       </c>
       <c r="T47">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z47">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="AA47">
         <v>1.88</v>
       </c>
       <c r="AB47">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC47">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AD47">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE47">
         <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG47">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="O48">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="P48">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="Q48">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="R48">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="S48">
         <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
         <v>2.5</v>
@@ -8163,31 +8163,31 @@
         <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA48">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE48">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
         <v>2.21</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q50">
-        <v>4.6</v>
+        <v>4.79</v>
       </c>
       <c r="R50">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T50">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U50">
         <v>2.81</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.05</v>
@@ -8495,13 +8495,13 @@
         <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AA50">
         <v>2</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC50">
         <v>3.4</v>
@@ -8513,7 +8513,7 @@
         <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG50">
         <v>1.9</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="AK50">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
         <v>4</v>
@@ -8637,16 +8637,16 @@
         <v>2.15</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T51">
         <v>3.09</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>1.07</v>
@@ -8658,13 +8658,13 @@
         <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="AA51">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC51">
         <v>3.26</v>
@@ -8676,10 +8676,10 @@
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="O52">
-        <v>2.4</v>
+        <v>4.16</v>
       </c>
       <c r="P52">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q52">
-        <v>6</v>
+        <v>4.74</v>
       </c>
       <c r="R52">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U52">
         <v>2.7</v>
       </c>
       <c r="V52">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z52">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AA52">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB52">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC52">
         <v>2.88</v>
@@ -8839,10 +8839,10 @@
         <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG52">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="O53">
         <v>3.7</v>
       </c>
       <c r="P53">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q53">
-        <v>5.86</v>
+        <v>4.5</v>
       </c>
       <c r="R53">
         <v>2.25</v>
@@ -8966,7 +8966,7 @@
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="U53">
         <v>2.75</v>
@@ -8975,37 +8975,37 @@
         <v>1.4</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA53">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB53">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC53">
         <v>2.92</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF53">
         <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O58">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R58">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="S58">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="U58">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V58">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="W58">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X58">
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z58">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA58">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AB58">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC58">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AD58">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AE58">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AF58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG58">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK58">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>4.02</v>
+        <v>4.33</v>
       </c>
       <c r="R61">
         <v>2.2</v>
       </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U61">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W61">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z61">
         <v>3.9</v>
       </c>
       <c r="AA61">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB61">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC61">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AD61">
         <v>1.4</v>
       </c>
       <c r="AE61">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AK61">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O62">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="P62">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q62">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R62">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="U62">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>5.95</v>
+        <v>6.45</v>
       </c>
       <c r="AA62">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="AC62">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AD62">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AE62">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AF62">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG62">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK62">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="O63">
         <v>3.3</v>
       </c>
       <c r="P63">
-        <v>5.8</v>
+        <v>6.97</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA63">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AB63">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="O64">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P64">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q64">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="R64">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U64">
         <v>2.75</v>
@@ -10777,13 +10777,13 @@
         <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA64">
         <v>1.89</v>
       </c>
       <c r="AB64">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC64">
         <v>3.25</v>
@@ -10792,13 +10792,13 @@
         <v>1.29</v>
       </c>
       <c r="AE64">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG64">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q65">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="R65">
         <v>2</v>
       </c>
       <c r="S65">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T65">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U65">
         <v>2.95</v>
@@ -10937,7 +10937,7 @@
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z65">
         <v>3.1</v>
@@ -10946,22 +10946,22 @@
         <v>2.13</v>
       </c>
       <c r="AB65">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD65">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE65">
         <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
         <v>3.3</v>
       </c>
       <c r="P66">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q66">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S66">
         <v>1.45</v>
@@ -11097,7 +11097,7 @@
         <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
         <v>1.33</v>
@@ -11106,25 +11106,25 @@
         <v>3.11</v>
       </c>
       <c r="AA66">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AB66">
         <v>1.71</v>
       </c>
       <c r="AC66">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD66">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
         <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG66">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>2.8</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA68">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AB68">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O69">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O70">
         <v>3.6</v>
@@ -11728,13 +11728,13 @@
         <v>3.8</v>
       </c>
       <c r="Q70">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T70">
         <v>3.2</v>
@@ -11749,19 +11749,19 @@
         <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="AA70">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB70">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC70">
         <v>3.05</v>
@@ -11770,13 +11770,13 @@
         <v>1.38</v>
       </c>
       <c r="AE70">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
         <v>1.68</v>
       </c>
       <c r="AG70">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4713,52 +4713,52 @@
         <v>1.66</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P27">
-        <v>5.1</v>
+        <v>4.88</v>
       </c>
       <c r="Q27">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="R27">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="S27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
         <v>2.96</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AA27">
         <v>2.12</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>4.49</v>
+        <v>3.9</v>
       </c>
       <c r="O28">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q28">
-        <v>5.46</v>
+        <v>4.86</v>
       </c>
       <c r="R28">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="S28">
         <v>1.47</v>
       </c>
       <c r="T28">
-        <v>2.41</v>
+        <v>2.58</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V28">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA28">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB28">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>4.05</v>
+        <v>4.21</v>
       </c>
       <c r="AD28">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF28">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG28">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="O37">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>13.5</v>
@@ -6355,16 +6355,16 @@
         <v>3.15</v>
       </c>
       <c r="S37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
         <v>4</v>
       </c>
       <c r="U37">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="V37">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W37">
         <v>1.2</v>
@@ -6397,7 +6397,7 @@
         <v>2.11</v>
       </c>
       <c r="AG37">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK37">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O41">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q41">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="R41">
         <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="U41">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
         <v>1.04</v>
@@ -7031,10 +7031,10 @@
         <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB41">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC41">
         <v>3.6</v>
@@ -7049,7 +7049,7 @@
         <v>1.76</v>
       </c>
       <c r="AG41">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O49">
         <v>3</v>
@@ -8305,10 +8305,10 @@
         <v>3.3</v>
       </c>
       <c r="Q49">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="R49">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S49">
         <v>1.5</v>
@@ -8329,7 +8329,7 @@
         <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z49">
         <v>2.59</v>
@@ -8338,7 +8338,7 @@
         <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC49">
         <v>4.4</v>
@@ -8347,13 +8347,13 @@
         <v>1.14</v>
       </c>
       <c r="AE49">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
         <v>1.99</v>
       </c>
       <c r="AG49">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9114,28 +9114,28 @@
         <v>2.9</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q54">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S54">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T54">
         <v>2.63</v>
       </c>
       <c r="U54">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="V54">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
         <v>1.02</v>
@@ -9150,7 +9150,7 @@
         <v>2.92</v>
       </c>
       <c r="AA54">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AB54">
         <v>1.71</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,25 +9277,25 @@
         <v>2.95</v>
       </c>
       <c r="O55">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P55">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="R55">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S55">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T55">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="U55">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V55">
         <v>1.27</v>
@@ -9304,7 +9304,7 @@
         <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
         <v>1.38</v>
@@ -9313,10 +9313,10 @@
         <v>2.68</v>
       </c>
       <c r="AA55">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB55">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC55">
         <v>4</v>
@@ -9347,7 +9347,7 @@
         <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q56">
         <v>2.98</v>
@@ -9452,16 +9452,16 @@
         <v>1.86</v>
       </c>
       <c r="S56">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T56">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="U56">
         <v>3.2</v>
       </c>
       <c r="V56">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
         <v>1</v>
@@ -9479,7 +9479,7 @@
         <v>2.36</v>
       </c>
       <c r="AB56">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC56">
         <v>4.2</v>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O57">
         <v>2.9</v>
       </c>
       <c r="P57">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="R57">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="S57">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T57">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="U57">
         <v>3.34</v>
@@ -9627,25 +9627,25 @@
         <v>1.25</v>
       </c>
       <c r="W57">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X57">
         <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z57">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA57">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AB57">
         <v>1.51</v>
       </c>
       <c r="AC57">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD57">
         <v>1.14</v>
@@ -9657,7 +9657,7 @@
         <v>1.95</v>
       </c>
       <c r="AG57">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL57">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1299,19 +1299,19 @@
         <v>4.1</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.11</v>
@@ -1332,10 +1332,10 @@
         <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AD6">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
         <v>1.15</v>
@@ -1453,22 +1453,22 @@
         <v>4.4</v>
       </c>
       <c r="O7">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>2.41</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U7">
         <v>2.1</v>
@@ -1477,7 +1477,7 @@
         <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
         <v>1</v>
@@ -1489,25 +1489,25 @@
         <v>5.45</v>
       </c>
       <c r="AA7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB7">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AC7">
         <v>2.08</v>
       </c>
       <c r="AD7">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE7">
         <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG7">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z12">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AA12">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
         <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3089,19 +3089,19 @@
         <v>2</v>
       </c>
       <c r="Q17">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T17">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
         <v>1.37</v>
@@ -3110,22 +3110,22 @@
         <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="AA17">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB17">
         <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
         <v>1.26</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z21">
         <v>2.58</v>
       </c>
       <c r="AA21">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AB21">
         <v>1.49</v>
@@ -3805,7 +3805,7 @@
         <v>1.37</v>
       </c>
       <c r="AK21">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P22">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q22">
-        <v>4.52</v>
+        <v>4.75</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
         <v>1.34</v>
@@ -3916,43 +3916,43 @@
         <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AD22">
         <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
         <v>1.14</v>
@@ -4058,55 +4058,55 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="O23">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q23">
         <v>1.98</v>
       </c>
       <c r="R23">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="U23">
         <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA23">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC23">
         <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AE23">
         <v>1.17</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,49 +4224,49 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q24">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="R24">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U24">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y24">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z24">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AB24">
         <v>1.83</v>
       </c>
       <c r="AC24">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD24">
         <v>1.24</v>
@@ -4275,10 +4275,10 @@
         <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG24">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK24">
         <v>1.1</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q25">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R25">
         <v>2.1</v>
@@ -4402,13 +4402,13 @@
         <v>1.4</v>
       </c>
       <c r="T25">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U25">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
         <v>1.05</v>
@@ -4426,7 +4426,7 @@
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
         <v>3.42</v>
@@ -4438,10 +4438,10 @@
         <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG25">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -4568,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -4580,31 +4580,31 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O27">
         <v>3.38</v>
@@ -4719,46 +4719,46 @@
         <v>4.88</v>
       </c>
       <c r="Q27">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R27">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
         <v>2.75</v>
       </c>
       <c r="U27">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
         <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
         <v>3.25</v>
       </c>
       <c r="AA27">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC27">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,19 +4879,19 @@
         <v>3.1</v>
       </c>
       <c r="P28">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>4.86</v>
+        <v>4.4</v>
       </c>
       <c r="R28">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U28">
         <v>3.3</v>
@@ -4900,34 +4900,34 @@
         <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z28">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA28">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC28">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG28">
         <v>1.7</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,22 +5045,22 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
         <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="U29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W29">
         <v>1.13</v>
@@ -5072,7 +5072,7 @@
         <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA29">
         <v>1.5</v>
@@ -5087,10 +5087,10 @@
         <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF29">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
         <v>2.23</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
         <v>2.3</v>
@@ -5365,10 +5365,10 @@
         <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P31">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>2.16</v>
       </c>
       <c r="Q32">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R32">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
         <v>1.36</v>
@@ -5546,7 +5546,7 @@
         <v>2.84</v>
       </c>
       <c r="U32">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V32">
         <v>1.39</v>
@@ -5558,7 +5558,7 @@
         <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
         <v>3.65</v>
@@ -5579,7 +5579,7 @@
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
         <v>2.05</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AK32">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
         <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q33">
         <v>2.38</v>
@@ -5703,46 +5703,46 @@
         <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="U33">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA33">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AC33">
         <v>2.25</v>
       </c>
       <c r="AD33">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF33">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AG33">
         <v>2.55</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,25 +5854,25 @@
         <v>1.6</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
         <v>1.5</v>
@@ -5884,31 +5884,31 @@
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB34">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
         <v>2.65</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="P35">
-        <v>5.41</v>
+        <v>5.1</v>
       </c>
       <c r="Q35">
         <v>1.91</v>
       </c>
       <c r="R35">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="S35">
         <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
         <v>1.13</v>
@@ -6053,13 +6053,13 @@
         <v>4.8</v>
       </c>
       <c r="AA35">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB35">
         <v>2.38</v>
       </c>
       <c r="AC35">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD35">
         <v>1.57</v>
@@ -6068,10 +6068,10 @@
         <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,46 +6177,46 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O36">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="P36">
-        <v>7.35</v>
+        <v>6.6</v>
       </c>
       <c r="Q36">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R36">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T36">
         <v>3.58</v>
       </c>
       <c r="U36">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V36">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W36">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA36">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB36">
         <v>2.7</v>
@@ -6225,16 +6225,16 @@
         <v>2.14</v>
       </c>
       <c r="AD36">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE36">
         <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AK36">
         <v>2.98</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="O37">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="P37">
         <v>13.5</v>
       </c>
       <c r="Q37">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="R37">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="S37">
         <v>1.2</v>
@@ -6361,10 +6361,10 @@
         <v>4</v>
       </c>
       <c r="U37">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
         <v>1.2</v>
@@ -6379,10 +6379,10 @@
         <v>5.65</v>
       </c>
       <c r="AA37">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AC37">
         <v>2.01</v>
@@ -6394,10 +6394,10 @@
         <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG37">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6509,13 +6509,13 @@
         <v>3</v>
       </c>
       <c r="P38">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q38">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="R38">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S38">
         <v>1.64</v>
@@ -6524,16 +6524,16 @@
         <v>2.28</v>
       </c>
       <c r="U38">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W38">
         <v>1.01</v>
       </c>
       <c r="X38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y38">
         <v>1.62</v>
@@ -6542,25 +6542,25 @@
         <v>2.31</v>
       </c>
       <c r="AA38">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="AB38">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC38">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD38">
         <v>1.1</v>
       </c>
       <c r="AE38">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AG38">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AK38">
         <v>1.67</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
         <v>3.75</v>
       </c>
       <c r="Q40">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
         <v>2.43</v>
@@ -6847,25 +6847,25 @@
         <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V40">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5.41</v>
+        <v>5.25</v>
       </c>
       <c r="AA40">
         <v>1.4</v>
@@ -6874,7 +6874,7 @@
         <v>2.56</v>
       </c>
       <c r="AC40">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD40">
         <v>1.63</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="O43">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="Q43">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R43">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V43">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X43">
         <v>0</v>
@@ -7363,19 +7363,19 @@
         <v>3.1</v>
       </c>
       <c r="AC43">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AD43">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG43">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
         <v>1.98</v>
@@ -7813,40 +7813,40 @@
         <v>3.6</v>
       </c>
       <c r="P46">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q46">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R46">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="S46">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T46">
         <v>2.47</v>
       </c>
       <c r="U46">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="V46">
         <v>1.3</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
         <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z46">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA46">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AB46">
         <v>1.6</v>
@@ -7858,13 +7858,13 @@
         <v>1.17</v>
       </c>
       <c r="AE46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AG46">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>3.6</v>
+      </c>
+      <c r="O47">
+        <v>3.7</v>
+      </c>
+      <c r="P47">
+        <v>1.93</v>
+      </c>
+      <c r="Q47">
+        <v>3.88</v>
+      </c>
+      <c r="R47">
+        <v>2.39</v>
+      </c>
+      <c r="S47">
+        <v>1.3</v>
+      </c>
+      <c r="T47">
+        <v>3.2</v>
+      </c>
+      <c r="U47">
+        <v>2.5</v>
+      </c>
+      <c r="V47">
         <v>1.47</v>
-      </c>
-      <c r="O47">
-        <v>4.2</v>
-      </c>
-      <c r="P47">
-        <v>6.5</v>
-      </c>
-      <c r="Q47">
-        <v>1.95</v>
-      </c>
-      <c r="R47">
-        <v>2.34</v>
-      </c>
-      <c r="S47">
-        <v>1.33</v>
-      </c>
-      <c r="T47">
-        <v>3.02</v>
-      </c>
-      <c r="U47">
-        <v>2.6</v>
-      </c>
-      <c r="V47">
-        <v>1.42</v>
       </c>
       <c r="W47">
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC47">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="AD47">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF47">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.63</v>
+        <v>1.28</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.25</v>
+        <v>1.47</v>
       </c>
       <c r="O48">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="P48">
-        <v>2.01</v>
+        <v>6.5</v>
       </c>
       <c r="Q48">
-        <v>3.88</v>
+        <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z48">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AC48">
+        <v>2.94</v>
+      </c>
+      <c r="AD48">
+        <v>1.36</v>
+      </c>
+      <c r="AE48">
+        <v>1.09</v>
+      </c>
+      <c r="AF48">
+        <v>2</v>
+      </c>
+      <c r="AG48">
+        <v>1.76</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.22</v>
+      </c>
+      <c r="AK48">
         <v>2.63</v>
-      </c>
-      <c r="AD48">
-        <v>1.48</v>
-      </c>
-      <c r="AE48">
-        <v>1.13</v>
-      </c>
-      <c r="AF48">
-        <v>1.57</v>
-      </c>
-      <c r="AG48">
-        <v>2.21</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.29</v>
-      </c>
-      <c r="AK48">
-        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
         <v>1.8</v>
       </c>
       <c r="Q50">
-        <v>4.79</v>
+        <v>3.92</v>
       </c>
       <c r="R50">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
         <v>1.34</v>
@@ -8489,22 +8489,22 @@
         <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y50">
         <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="AA50">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
         <v>1.83</v>
       </c>
       <c r="AC50">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD50">
         <v>1.26</v>
@@ -8513,10 +8513,10 @@
         <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.22</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
         <v>4</v>
@@ -8634,37 +8634,37 @@
         <v>2.47</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
         <v>3.09</v>
       </c>
       <c r="U51">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA51">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB51">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AC51">
         <v>3.26</v>
@@ -8673,13 +8673,13 @@
         <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
         <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="O52">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="P52">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q52">
         <v>4.74</v>
@@ -8800,22 +8800,22 @@
         <v>2.18</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T52">
         <v>3</v>
       </c>
       <c r="U52">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.24</v>
@@ -8827,22 +8827,22 @@
         <v>1.78</v>
       </c>
       <c r="AB52">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE52">
         <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG52">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>2.41</v>
       </c>
       <c r="AK52">
         <v>1.13</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P53">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q53">
-        <v>4.5</v>
+        <v>6.03</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="U53">
         <v>2.75</v>
@@ -8978,31 +8978,31 @@
         <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA53">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AB53">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC53">
         <v>2.92</v>
       </c>
       <c r="AD53">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE53">
         <v>1.08</v>
       </c>
       <c r="AF53">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG53">
         <v>1.83</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>4</v>
       </c>
       <c r="P58">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -9781,13 +9781,13 @@
         <v>1.14</v>
       </c>
       <c r="T58">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="U58">
         <v>1.8</v>
       </c>
       <c r="V58">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="W58">
         <v>1.25</v>
@@ -9805,16 +9805,16 @@
         <v>1.28</v>
       </c>
       <c r="AB58">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC58">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AD58">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AE58">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AF58">
         <v>1.25</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
         <v>1.82</v>
@@ -9926,43 +9926,43 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="O59">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="P59">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q59">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R59">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="S59">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T59">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U59">
         <v>1.85</v>
       </c>
       <c r="V59">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W59">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="AA59">
         <v>1.33</v>
@@ -9971,19 +9971,19 @@
         <v>2.87</v>
       </c>
       <c r="AC59">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AD59">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE59">
         <v>1.3</v>
       </c>
       <c r="AF59">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG59">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AK59">
         <v>5</v>
@@ -10092,28 +10092,28 @@
         <v>1.75</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
         <v>4.5</v>
       </c>
       <c r="Q60">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="R60">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="S60">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U60">
         <v>2.63</v>
       </c>
       <c r="V60">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W60">
         <v>1.04</v>
@@ -10128,25 +10128,25 @@
         <v>3.3</v>
       </c>
       <c r="AA60">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB60">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC60">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="AD60">
         <v>1.3</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
         <v>1.8</v>
       </c>
       <c r="AG60">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK60">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,13 +10261,13 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R61">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
         <v>3.15</v>
@@ -10276,7 +10276,7 @@
         <v>2.47</v>
       </c>
       <c r="V61">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W61">
         <v>1.07</v>
@@ -10288,13 +10288,13 @@
         <v>1.18</v>
       </c>
       <c r="Z61">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA61">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB61">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC61">
         <v>2.88</v>
@@ -10309,7 +10309,7 @@
         <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>2.01</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,31 +10415,31 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O62">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="P62">
         <v>12</v>
       </c>
       <c r="Q62">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="R62">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U62">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V62">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W62">
         <v>1.21</v>
@@ -10451,13 +10451,13 @@
         <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="AA62">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB62">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="AC62">
         <v>1.92</v>
@@ -10466,14 +10466,14 @@
         <v>1.94</v>
       </c>
       <c r="AE62">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AF62">
+        <v>2.05</v>
+      </c>
+      <c r="AG62">
         <v>1.85</v>
       </c>
-      <c r="AG62">
-        <v>1.87</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK62">
-        <v>4.68</v>
+        <v>5.05</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O63">
         <v>3.3</v>
@@ -10587,22 +10587,22 @@
         <v>6.97</v>
       </c>
       <c r="Q63">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R63">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T63">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V63">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W63">
         <v>1.04</v>
@@ -10617,19 +10617,19 @@
         <v>2.36</v>
       </c>
       <c r="AA63">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="AB63">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AC63">
-        <v>5.1</v>
+        <v>5.17</v>
       </c>
       <c r="AD63">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE63">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
         <v>2.5</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="O64">
         <v>3.25</v>
@@ -10750,28 +10750,28 @@
         <v>3.05</v>
       </c>
       <c r="Q64">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R64">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S64">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T64">
         <v>3</v>
       </c>
       <c r="U64">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V64">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W64">
         <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
         <v>1.25</v>
@@ -10786,19 +10786,19 @@
         <v>1.93</v>
       </c>
       <c r="AC64">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD64">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF64">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG64">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.33</v>
       </c>
       <c r="AK64">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>1.68</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
         <v>5</v>
@@ -10916,37 +10916,37 @@
         <v>2.25</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T65">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U65">
         <v>2.95</v>
       </c>
       <c r="V65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y65">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
         <v>2.13</v>
       </c>
       <c r="AB65">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
         <v>3.6</v>
@@ -10955,7 +10955,7 @@
         <v>1.26</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
         <v>2</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK65">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="O67">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q67">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="R67">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U67">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB67">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD67">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK67">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,43 +11396,43 @@
         <v>1.76</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q68">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R68">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T68">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U68">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="V68">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y68">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z68">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AA68">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AB68">
         <v>1.58</v>
@@ -11447,10 +11447,10 @@
         <v>1.02</v>
       </c>
       <c r="AF68">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG68">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O69">
         <v>3</v>
       </c>
       <c r="P69">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11725,16 +11725,16 @@
         <v>3.6</v>
       </c>
       <c r="P70">
-        <v>3.8</v>
+        <v>4.12</v>
       </c>
       <c r="Q70">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R70">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
         <v>3.2</v>
@@ -11749,28 +11749,28 @@
         <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z70">
-        <v>4.08</v>
+        <v>3.95</v>
       </c>
       <c r="AA70">
         <v>1.76</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC70">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD70">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE70">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF70">
         <v>1.68</v>
@@ -11792,7 +11792,7 @@
         <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -3107,7 +3107,7 @@
         <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -4224,28 +4224,28 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
         <v>1.5</v>
       </c>
       <c r="Q24">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
         <v>2.8</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4254,25 +4254,25 @@
         <v>1.07</v>
       </c>
       <c r="Y24">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA24">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB24">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="AD24">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
         <v>2.2</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O31">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="P31">
-        <v>5.09</v>
+        <v>4.35</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
         <v>3</v>
@@ -6512,10 +6512,10 @@
         <v>3.95</v>
       </c>
       <c r="Q38">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="S38">
         <v>1.64</v>
@@ -6548,13 +6548,13 @@
         <v>1.42</v>
       </c>
       <c r="AC38">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD38">
         <v>1.1</v>
       </c>
       <c r="AE38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF38">
         <v>2.29</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P47">
         <v>1.93</v>
       </c>
       <c r="Q47">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="R47">
         <v>2.39</v>
@@ -8145,7 +8145,7 @@
         <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S48">
         <v>1.33</v>
@@ -8190,7 +8190,7 @@
         <v>2</v>
       </c>
       <c r="AG48">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
         <v>4</v>
@@ -8637,28 +8637,28 @@
         <v>2.06</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T51">
         <v>3.09</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA51">
         <v>1.97</v>
@@ -8673,13 +8673,13 @@
         <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
         <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="O52">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P52">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q52">
-        <v>4.74</v>
+        <v>5.5</v>
       </c>
       <c r="R52">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
         <v>1.38</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U52">
         <v>2.76</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.08</v>
@@ -8818,22 +8818,22 @@
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z52">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA52">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB52">
         <v>2.06</v>
       </c>
       <c r="AC52">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
         <v>1.1</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>2.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>7</v>
+        <v>5.85</v>
       </c>
       <c r="AA59">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB59">
         <v>2.87</v>
@@ -9974,7 +9974,7 @@
         <v>2.03</v>
       </c>
       <c r="AD59">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE59">
         <v>1.3</v>
@@ -10095,7 +10095,7 @@
         <v>3.7</v>
       </c>
       <c r="P60">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q60">
         <v>2.25</v>
@@ -10110,13 +10110,13 @@
         <v>2.9</v>
       </c>
       <c r="U60">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="V60">
         <v>1.41</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10128,19 +10128,19 @@
         <v>3.3</v>
       </c>
       <c r="AA60">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB60">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC60">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AD60">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
         <v>1.8</v>
@@ -10264,7 +10264,7 @@
         <v>4.5</v>
       </c>
       <c r="R61">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
         <v>1.33</v>
@@ -10273,13 +10273,13 @@
         <v>3.15</v>
       </c>
       <c r="U61">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V61">
         <v>1.48</v>
       </c>
       <c r="W61">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.05</v>
@@ -10288,7 +10288,7 @@
         <v>1.18</v>
       </c>
       <c r="Z61">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AA61">
         <v>1.86</v>
@@ -10424,13 +10424,13 @@
         <v>12</v>
       </c>
       <c r="Q62">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R62">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T62">
         <v>4.2</v>
@@ -10454,19 +10454,19 @@
         <v>6.55</v>
       </c>
       <c r="AA62">
+        <v>1.32</v>
+      </c>
+      <c r="AB62">
+        <v>3.04</v>
+      </c>
+      <c r="AC62">
+        <v>1.93</v>
+      </c>
+      <c r="AD62">
+        <v>1.83</v>
+      </c>
+      <c r="AE62">
         <v>1.34</v>
-      </c>
-      <c r="AB62">
-        <v>2.89</v>
-      </c>
-      <c r="AC62">
-        <v>1.92</v>
-      </c>
-      <c r="AD62">
-        <v>1.94</v>
-      </c>
-      <c r="AE62">
-        <v>1.37</v>
       </c>
       <c r="AF62">
         <v>2.05</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK62">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q66">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="U66">
         <v>3.05</v>
       </c>
       <c r="V66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
         <v>1.07</v>
@@ -11100,25 +11100,25 @@
         <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z66">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AA66">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB66">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC66">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD66">
         <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF66">
         <v>1.85</v>
@@ -11140,7 +11140,7 @@
         <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL66">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q33">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S33">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>5.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AB33">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AD33">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AE33">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
+        <v>1.51</v>
+      </c>
+      <c r="O34">
+        <v>4.55</v>
+      </c>
+      <c r="P34">
+        <v>5.1</v>
+      </c>
+      <c r="Q34">
+        <v>1.91</v>
+      </c>
+      <c r="R34">
+        <v>2.49</v>
+      </c>
+      <c r="S34">
+        <v>1.25</v>
+      </c>
+      <c r="T34">
+        <v>3.6</v>
+      </c>
+      <c r="U34">
+        <v>2.25</v>
+      </c>
+      <c r="V34">
         <v>1.6</v>
       </c>
-      <c r="O34">
-        <v>3.7</v>
-      </c>
-      <c r="P34">
+      <c r="W34">
+        <v>1.13</v>
+      </c>
+      <c r="X34">
+        <v>1.02</v>
+      </c>
+      <c r="Y34">
+        <v>1.14</v>
+      </c>
+      <c r="Z34">
         <v>4.8</v>
       </c>
-      <c r="Q34">
+      <c r="AA34">
+        <v>1.55</v>
+      </c>
+      <c r="AB34">
+        <v>2.38</v>
+      </c>
+      <c r="AC34">
+        <v>2.4</v>
+      </c>
+      <c r="AD34">
+        <v>1.57</v>
+      </c>
+      <c r="AE34">
+        <v>1.18</v>
+      </c>
+      <c r="AF34">
+        <v>1.62</v>
+      </c>
+      <c r="AG34">
         <v>2.08</v>
       </c>
-      <c r="R34">
-        <v>2.48</v>
-      </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>3.2</v>
-      </c>
-      <c r="U34">
-        <v>2.4</v>
-      </c>
-      <c r="V34">
-        <v>1.5</v>
-      </c>
-      <c r="W34">
-        <v>1.11</v>
-      </c>
-      <c r="X34">
-        <v>1.04</v>
-      </c>
-      <c r="Y34">
-        <v>1.17</v>
-      </c>
-      <c r="Z34">
-        <v>4.33</v>
-      </c>
-      <c r="AA34">
-        <v>1.67</v>
-      </c>
-      <c r="AB34">
-        <v>2.15</v>
-      </c>
-      <c r="AC34">
-        <v>2.65</v>
-      </c>
-      <c r="AD34">
-        <v>1.48</v>
-      </c>
-      <c r="AE34">
-        <v>1.17</v>
-      </c>
-      <c r="AF34">
-        <v>1.67</v>
-      </c>
-      <c r="AG34">
-        <v>2.05</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK34">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="O35">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="R35">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="V35">
         <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="AA35">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC35">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AG35">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O64">
         <v>3.25</v>
@@ -10750,10 +10750,10 @@
         <v>3.05</v>
       </c>
       <c r="Q64">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="R64">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
         <v>1.35</v>
@@ -10771,19 +10771,19 @@
         <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y64">
         <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AA64">
         <v>1.89</v>
       </c>
       <c r="AB64">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC64">
         <v>2.92</v>
@@ -10792,13 +10792,13 @@
         <v>1.31</v>
       </c>
       <c r="AE64">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
         <v>1.65</v>
       </c>
       <c r="AG64">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,10 +10907,10 @@
         <v>1.68</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q65">
         <v>2.25</v>
@@ -10919,43 +10919,43 @@
         <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="V65">
         <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
         <v>1.07</v>
       </c>
       <c r="Y65">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z65">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA65">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB65">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD65">
         <v>1.26</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
         <v>2</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
         <v>1.94</v>
@@ -11719,19 +11719,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P70">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="Q70">
         <v>2.3</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S70">
         <v>1.3</v>
@@ -11749,7 +11749,7 @@
         <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
         <v>1.21</v>
@@ -11761,7 +11761,7 @@
         <v>1.76</v>
       </c>
       <c r="AB70">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC70">
         <v>2.75</v>
@@ -11773,7 +11773,7 @@
         <v>1.09</v>
       </c>
       <c r="AF70">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG70">
         <v>2.05</v>
@@ -11792,7 +11792,7 @@
         <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O27">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="Q27">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
         <v>1.06</v>
@@ -4764,7 +4764,7 @@
         <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
         <v>1.74</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>2</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T28">
         <v>2.6</v>
@@ -4900,28 +4900,28 @@
         <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AA28">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AB28">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
         <v>4.1</v>
       </c>
       <c r="AD28">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
         <v>1.03</v>
@@ -4930,7 +4930,7 @@
         <v>1.91</v>
       </c>
       <c r="AG28">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="O37">
-        <v>5.95</v>
+        <v>7</v>
       </c>
       <c r="P37">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Q37">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R37">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V37">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W37">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6394,7 +6394,7 @@
         <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG37">
         <v>1.65</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK37">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>2.62</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
         <v>2.65</v>
@@ -7007,13 +7007,13 @@
         <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="U41">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
         <v>1.35</v>
@@ -7025,10 +7025,10 @@
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AA41">
         <v>1.97</v>
@@ -7037,19 +7037,19 @@
         <v>1.72</v>
       </c>
       <c r="AC41">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="AD41">
         <v>1.25</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="O45">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P45">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P49">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q49">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R49">
         <v>1.95</v>
       </c>
       <c r="S49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T49">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U49">
         <v>3.2</v>
       </c>
       <c r="V49">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W49">
         <v>1.02</v>
@@ -8332,28 +8332,28 @@
         <v>1.4</v>
       </c>
       <c r="Z49">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA49">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AB49">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC49">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD49">
         <v>1.14</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF49">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AG49">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9114,28 +9114,28 @@
         <v>2.9</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q54">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R54">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T54">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U54">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="V54">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W54">
         <v>1.02</v>
@@ -9150,10 +9150,10 @@
         <v>2.92</v>
       </c>
       <c r="AA54">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AB54">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC54">
         <v>3.72</v>
@@ -9165,10 +9165,10 @@
         <v>1.03</v>
       </c>
       <c r="AF54">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG54">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AK54">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,22 +9277,22 @@
         <v>2.95</v>
       </c>
       <c r="O55">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P55">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>3.69</v>
+        <v>3.85</v>
       </c>
       <c r="R55">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="S55">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T55">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U55">
         <v>3.1</v>
@@ -9301,19 +9301,19 @@
         <v>1.27</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
         <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
         <v>2.68</v>
       </c>
       <c r="AA55">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB55">
         <v>1.56</v>
@@ -9328,10 +9328,10 @@
         <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG55">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK55">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O56">
         <v>2.9</v>
       </c>
       <c r="P56">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q56">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="R56">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T56">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="U56">
         <v>3.2</v>
@@ -9467,34 +9467,34 @@
         <v>1</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.37</v>
       </c>
       <c r="Z56">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AA56">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB56">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC56">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD56">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE56">
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG56">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O57">
         <v>2.9</v>
       </c>
       <c r="P57">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q57">
-        <v>3.69</v>
+        <v>3.44</v>
       </c>
       <c r="R57">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="S57">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U57">
         <v>3.34</v>
@@ -9627,16 +9627,16 @@
         <v>1.25</v>
       </c>
       <c r="W57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
         <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Z57">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AA57">
         <v>2.36</v>
@@ -9645,7 +9645,7 @@
         <v>1.51</v>
       </c>
       <c r="AC57">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD57">
         <v>1.14</v>
@@ -9654,7 +9654,7 @@
         <v>1.01</v>
       </c>
       <c r="AF57">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG57">
         <v>1.72</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O63">
         <v>3.3</v>
@@ -10587,46 +10587,46 @@
         <v>6.97</v>
       </c>
       <c r="Q63">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T63">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="U63">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="V63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W63">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X63">
         <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z63">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AA63">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AB63">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC63">
-        <v>5.17</v>
+        <v>5.5</v>
       </c>
       <c r="AD63">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE63">
         <v>1.04</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P68">
-        <v>4.2</v>
+        <v>4.72</v>
       </c>
       <c r="Q68">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R68">
         <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T68">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U68">
         <v>3.28</v>
@@ -11420,7 +11420,7 @@
         <v>1.31</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
         <v>1.05</v>
@@ -11450,7 +11450,7 @@
         <v>2</v>
       </c>
       <c r="AG68">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O69">
         <v>3</v>
       </c>
       <c r="P69">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q69">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1296,25 +1296,25 @@
         <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="U6">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.02</v>
@@ -1323,10 +1323,10 @@
         <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="AA6">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
         <v>2.05</v>
@@ -1341,7 +1341,7 @@
         <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG6">
         <v>2.12</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,22 +1459,22 @@
         <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R7">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="S7">
         <v>1.21</v>
       </c>
       <c r="T7">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
         <v>1.12</v>
@@ -1501,13 +1501,13 @@
         <v>1.61</v>
       </c>
       <c r="AE7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AG7">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="AK7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O12">
         <v>3.1</v>
@@ -2274,7 +2274,7 @@
         <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R12">
         <v>1.98</v>
@@ -2286,7 +2286,7 @@
         <v>2.6</v>
       </c>
       <c r="U12">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
         <v>1.37</v>
@@ -2304,16 +2304,16 @@
         <v>3.21</v>
       </c>
       <c r="AA12">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB12">
         <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
         <v>1.05</v>
@@ -2322,7 +2322,7 @@
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
         <v>1.56</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O17">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q17">
         <v>4.15</v>
@@ -3095,10 +3095,10 @@
         <v>2.01</v>
       </c>
       <c r="S17">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="U17">
         <v>2.88</v>
@@ -3107,19 +3107,19 @@
         <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z17">
         <v>3.14</v>
       </c>
       <c r="AA17">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB17">
         <v>1.8</v>
@@ -3131,7 +3131,7 @@
         <v>1.26</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
         <v>1.75</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AK17">
         <v>1.27</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="O21">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="P21">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="Q21">
         <v>3.18</v>
@@ -3771,16 +3771,16 @@
         <v>2.58</v>
       </c>
       <c r="AA21">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AB21">
         <v>1.49</v>
       </c>
       <c r="AC21">
-        <v>4.65</v>
+        <v>4.87</v>
       </c>
       <c r="AD21">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE21">
         <v>1</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>1.62</v>
       </c>
       <c r="Q22">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.34</v>
@@ -3916,31 +3916,31 @@
         <v>2.99</v>
       </c>
       <c r="U22">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AB22">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC22">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AD22">
         <v>1.3</v>
@@ -3952,7 +3952,7 @@
         <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
         <v>1.14</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O23">
         <v>4.2</v>
       </c>
       <c r="P23">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q23">
         <v>1.98</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="S23">
         <v>1.24</v>
@@ -4091,7 +4091,7 @@
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
         <v>4.8</v>
@@ -4100,10 +4100,10 @@
         <v>1.57</v>
       </c>
       <c r="AB23">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AD23">
         <v>1.45</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>2.44</v>
+        <v>2.71</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>1.5</v>
       </c>
       <c r="Q24">
-        <v>6.75</v>
+        <v>5.61</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U24">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
         <v>3.3</v>
       </c>
       <c r="AA24">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AB24">
         <v>1.87</v>
       </c>
       <c r="AC24">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AD24">
         <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG24">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,22 +4393,22 @@
         <v>2.61</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
         <v>2.62</v>
       </c>
       <c r="U25">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
         <v>1.05</v>
@@ -4426,7 +4426,7 @@
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC25">
         <v>3.42</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5045,10 +5045,10 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S29">
         <v>1.25</v>
@@ -5072,16 +5072,16 @@
         <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA29">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB29">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC29">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD29">
         <v>1.5</v>
@@ -5090,10 +5090,10 @@
         <v>1.23</v>
       </c>
       <c r="AF29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG29">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="P31">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="O32">
         <v>3.3</v>
       </c>
       <c r="P32">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
         <v>2.84</v>
       </c>
       <c r="U32">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V32">
         <v>1.39</v>
@@ -5558,7 +5558,7 @@
         <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
         <v>3.65</v>
@@ -5567,22 +5567,22 @@
         <v>1.86</v>
       </c>
       <c r="AB32">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
         <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
         <v>1.36</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
         <v>4.8</v>
@@ -5700,22 +5700,22 @@
         <v>2.08</v>
       </c>
       <c r="R33">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U33">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V33">
         <v>1.5</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.04</v>
@@ -5724,28 +5724,28 @@
         <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
         <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD33">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
         <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK33">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5857,37 +5857,37 @@
         <v>4.55</v>
       </c>
       <c r="P34">
-        <v>5.1</v>
+        <v>5.41</v>
       </c>
       <c r="Q34">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="R34">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S34">
         <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="U34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
         <v>1.6</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z34">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA34">
         <v>1.55</v>
@@ -5896,7 +5896,7 @@
         <v>2.38</v>
       </c>
       <c r="AC34">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD34">
         <v>1.57</v>
@@ -5905,10 +5905,10 @@
         <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6017,10 +6017,10 @@
         <v>1.83</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q35">
         <v>2.38</v>
@@ -6038,7 +6038,7 @@
         <v>2.08</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
         <v>1.12</v>
@@ -6059,19 +6059,19 @@
         <v>2.6</v>
       </c>
       <c r="AC35">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD35">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE35">
         <v>1.25</v>
       </c>
       <c r="AF35">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O36">
         <v>4.85</v>
@@ -6189,7 +6189,7 @@
         <v>1.75</v>
       </c>
       <c r="R36">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="S36">
         <v>1.17</v>
@@ -6213,28 +6213,28 @@
         <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="AA36">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AC36">
         <v>2.14</v>
       </c>
       <c r="AD36">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE36">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF36">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6509,19 +6509,19 @@
         <v>3</v>
       </c>
       <c r="P38">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R38">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="T38">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="U38">
         <v>4.33</v>
@@ -6530,7 +6530,7 @@
         <v>1.22</v>
       </c>
       <c r="W38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X38">
         <v>1.08</v>
@@ -6539,7 +6539,7 @@
         <v>1.62</v>
       </c>
       <c r="Z38">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AA38">
         <v>2.91</v>
@@ -6548,13 +6548,13 @@
         <v>1.42</v>
       </c>
       <c r="AC38">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AD38">
         <v>1.1</v>
       </c>
       <c r="AE38">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
         <v>2.29</v>
@@ -6576,7 +6576,7 @@
         <v>1.42</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q39">
         <v>1.46</v>
@@ -6841,22 +6841,22 @@
         <v>2.15</v>
       </c>
       <c r="R40">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="U40">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V40">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6865,16 +6865,16 @@
         <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC40">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD40">
         <v>1.63</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
         <v>2.1</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O43">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="Q43">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="R43">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="S43">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="U43">
+        <v>1.86</v>
+      </c>
+      <c r="V43">
         <v>1.87</v>
       </c>
-      <c r="V43">
-        <v>1.8</v>
-      </c>
       <c r="W43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z43">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA43">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AB43">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="AC43">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD43">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AE43">
+        <v>1.4</v>
+      </c>
+      <c r="AF43">
         <v>1.35</v>
       </c>
-      <c r="AF43">
-        <v>1.33</v>
-      </c>
       <c r="AG43">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,40 +7807,40 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="Q46">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
         <v>1.44</v>
       </c>
       <c r="T46">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U46">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="V46">
         <v>1.3</v>
       </c>
       <c r="W46">
+        <v>1.02</v>
+      </c>
+      <c r="X46">
         <v>1.05</v>
       </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
       <c r="Y46">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z46">
         <v>2.62</v>
@@ -7849,13 +7849,13 @@
         <v>2.27</v>
       </c>
       <c r="AB46">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC46">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE46">
         <v>1.02</v>
@@ -7864,7 +7864,7 @@
         <v>2.33</v>
       </c>
       <c r="AG46">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>2.26</v>
+        <v>2.41</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7982,13 +7982,13 @@
         <v>3.9</v>
       </c>
       <c r="R47">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
         <v>2.5</v>
@@ -8018,16 +8018,16 @@
         <v>2.63</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
         <v>1.18</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8145,7 +8145,7 @@
         <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
         <v>1.33</v>
@@ -8154,13 +8154,13 @@
         <v>3.02</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
         <v>1.05</v>
@@ -8459,28 +8459,28 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O50">
         <v>3.6</v>
       </c>
       <c r="P50">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q50">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="V50">
         <v>1.4</v>
@@ -8492,10 +8492,10 @@
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AA50">
         <v>1.94</v>
@@ -8504,19 +8504,19 @@
         <v>1.83</v>
       </c>
       <c r="AC50">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD50">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE50">
         <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG50">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8625,22 +8625,22 @@
         <v>1.91</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q51">
         <v>2.47</v>
       </c>
       <c r="R51">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.35</v>
       </c>
       <c r="T51">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="U51">
         <v>2.7</v>
@@ -8652,13 +8652,13 @@
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA51">
         <v>1.97</v>
@@ -8667,19 +8667,19 @@
         <v>1.89</v>
       </c>
       <c r="AC51">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE51">
         <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG51">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O52">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P52">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q52">
-        <v>5.5</v>
+        <v>4.74</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
         <v>1.38</v>
@@ -8806,13 +8806,13 @@
         <v>3.05</v>
       </c>
       <c r="U52">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="V52">
         <v>1.45</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,10 +8821,10 @@
         <v>1.23</v>
       </c>
       <c r="Z52">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA52">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
         <v>2.06</v>
@@ -8833,7 +8833,7 @@
         <v>2.88</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
         <v>1.1</v>
@@ -8842,7 +8842,7 @@
         <v>1.87</v>
       </c>
       <c r="AG52">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,55 +8948,55 @@
         </is>
       </c>
       <c r="N53">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="O53">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q53">
-        <v>6.03</v>
+        <v>4.84</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S53">
         <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V53">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W53">
         <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA53">
         <v>1.92</v>
       </c>
       <c r="AB53">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AD53">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE53">
         <v>1.08</v>
@@ -9005,7 +9005,7 @@
         <v>1.85</v>
       </c>
       <c r="AG53">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK53">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9781,13 +9781,13 @@
         <v>1.14</v>
       </c>
       <c r="T58">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="U58">
         <v>1.8</v>
       </c>
       <c r="V58">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="W58">
         <v>1.25</v>
@@ -9802,19 +9802,19 @@
         <v>7.5</v>
       </c>
       <c r="AA58">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB58">
         <v>3.8</v>
       </c>
       <c r="AC58">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AD58">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AE58">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AF58">
         <v>1.25</v>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="O59">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="P59">
         <v>12</v>
       </c>
       <c r="Q59">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="R59">
         <v>2.88</v>
@@ -9962,7 +9962,7 @@
         <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="AA59">
         <v>1.4</v>
@@ -9980,10 +9980,10 @@
         <v>1.3</v>
       </c>
       <c r="AF59">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG59">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1</v>
       </c>
       <c r="AK59">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,10 +10098,10 @@
         <v>4.4</v>
       </c>
       <c r="Q60">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R60">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S60">
         <v>1.36</v>
@@ -10110,43 +10110,43 @@
         <v>2.9</v>
       </c>
       <c r="U60">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="V60">
         <v>1.41</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z60">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA60">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB60">
         <v>1.83</v>
       </c>
       <c r="AC60">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AD60">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF60">
         <v>1.8</v>
       </c>
       <c r="AG60">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,49 +10261,49 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U61">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="V61">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z61">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA61">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AB61">
-        <v>1.96</v>
+        <v>2.27</v>
       </c>
       <c r="AC61">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
         <v>1.67</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK61">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,16 +10415,16 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O62">
         <v>7.5</v>
       </c>
       <c r="P62">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q62">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="R62">
         <v>3.1</v>
@@ -10433,13 +10433,13 @@
         <v>1.19</v>
       </c>
       <c r="T62">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="U62">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V62">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W62">
         <v>1.21</v>
@@ -10448,22 +10448,22 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6.55</v>
+        <v>6.6</v>
       </c>
       <c r="AA62">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AC62">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AD62">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AE62">
         <v>1.34</v>
@@ -10472,7 +10472,7 @@
         <v>2.05</v>
       </c>
       <c r="AG62">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK62">
-        <v>4.8</v>
+        <v>4.37</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10584,10 +10584,10 @@
         <v>3.3</v>
       </c>
       <c r="P63">
-        <v>6.97</v>
+        <v>5.3</v>
       </c>
       <c r="Q63">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="R63">
         <v>2.05</v>
@@ -10596,7 +10596,7 @@
         <v>1.56</v>
       </c>
       <c r="T63">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
         <v>3.7</v>
@@ -10623,13 +10623,13 @@
         <v>1.47</v>
       </c>
       <c r="AC63">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD63">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF63">
         <v>2.5</v>
@@ -10744,7 +10744,7 @@
         <v>2.1</v>
       </c>
       <c r="O64">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
         <v>3.05</v>
@@ -10753,19 +10753,19 @@
         <v>2.53</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U64">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V64">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W64">
         <v>1.1</v>
@@ -10777,13 +10777,13 @@
         <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA64">
         <v>1.89</v>
       </c>
       <c r="AB64">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC64">
         <v>2.92</v>
@@ -10798,7 +10798,7 @@
         <v>1.65</v>
       </c>
       <c r="AG64">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
         <v>1.55</v>
@@ -10907,22 +10907,22 @@
         <v>1.68</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q65">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R65">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U65">
         <v>2.98</v>
@@ -10934,28 +10934,28 @@
         <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
         <v>2.92</v>
       </c>
       <c r="AA65">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB65">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC65">
         <v>3.5</v>
       </c>
       <c r="AD65">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
         <v>2</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q66">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
         <v>1.42</v>
@@ -11088,43 +11088,43 @@
         <v>2.65</v>
       </c>
       <c r="U66">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="V66">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W66">
         <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA66">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB66">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC66">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG66">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O67">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q67">
         <v>2.55</v>
       </c>
       <c r="R67">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="S67">
         <v>1.35</v>
@@ -11254,10 +11254,10 @@
         <v>2.78</v>
       </c>
       <c r="V67">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1.01</v>
@@ -11269,10 +11269,10 @@
         <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC67">
         <v>3.2</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11399,13 +11399,13 @@
         <v>3.45</v>
       </c>
       <c r="P68">
-        <v>4.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S68">
         <v>1.47</v>
@@ -11420,19 +11420,19 @@
         <v>1.31</v>
       </c>
       <c r="W68">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z68">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AA68">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AB68">
         <v>1.58</v>
@@ -11444,7 +11444,7 @@
         <v>1.18</v>
       </c>
       <c r="AE68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
         <v>2</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="P69">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11728,7 +11728,7 @@
         <v>4</v>
       </c>
       <c r="Q70">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R70">
         <v>2.23</v>
@@ -11755,22 +11755,22 @@
         <v>1.21</v>
       </c>
       <c r="Z70">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="AA70">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC70">
         <v>2.75</v>
       </c>
       <c r="AD70">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE70">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
         <v>1.67</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK70">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU70"/>
+  <dimension ref="A1:AU71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.3</v>
+        <v>7.7</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="P17">
-        <v>2.07</v>
+        <v>1.2</v>
       </c>
       <c r="Q17">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-08-31 13:15:00</t>
+          <t>2026-08-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-08-31 13:30:00</t>
+          <t>2026-08-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="P22">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="Q22">
-        <v>5.25</v>
+        <v>3.18</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="S22">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
-        <v>2.99</v>
+        <v>2.33</v>
       </c>
       <c r="U22">
-        <v>2.69</v>
+        <v>3.44</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="AA22">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="AB22">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AC22">
-        <v>3.13</v>
+        <v>4.87</v>
       </c>
       <c r="AD22">
+        <v>1.16</v>
+      </c>
+      <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AF22">
+        <v>2.06</v>
+      </c>
+      <c r="AG22">
+        <v>1.68</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.3</v>
       </c>
-      <c r="AE22">
-        <v>1.11</v>
-      </c>
-      <c r="AF22">
-        <v>1.8</v>
-      </c>
-      <c r="AG22">
-        <v>1.91</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.23</v>
-      </c>
       <c r="AK22">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="Q23">
-        <v>1.98</v>
+        <v>5.25</v>
       </c>
       <c r="R23">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="V23">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
+        <v>1.04</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>3.4</v>
+      </c>
+      <c r="AA23">
+        <v>1.89</v>
+      </c>
+      <c r="AB23">
+        <v>1.93</v>
+      </c>
+      <c r="AC23">
+        <v>3.13</v>
+      </c>
+      <c r="AD23">
+        <v>1.3</v>
+      </c>
+      <c r="AE23">
         <v>1.11</v>
       </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
+      <c r="AF23">
+        <v>1.8</v>
+      </c>
+      <c r="AG23">
+        <v>1.91</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.23</v>
+      </c>
+      <c r="AK23">
         <v>1.14</v>
-      </c>
-      <c r="Z23">
-        <v>4.8</v>
-      </c>
-      <c r="AA23">
-        <v>1.57</v>
-      </c>
-      <c r="AB23">
-        <v>2.21</v>
-      </c>
-      <c r="AC23">
-        <v>2.43</v>
-      </c>
-      <c r="AD23">
-        <v>1.45</v>
-      </c>
-      <c r="AE23">
-        <v>1.17</v>
-      </c>
-      <c r="AF23">
-        <v>1.7</v>
-      </c>
-      <c r="AG23">
-        <v>2</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.13</v>
-      </c>
-      <c r="AK23">
-        <v>2.71</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>7</v>
+        <v>1.44</v>
       </c>
       <c r="O24">
         <v>4.2</v>
       </c>
       <c r="P24">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q24">
-        <v>5.61</v>
+        <v>1.98</v>
       </c>
       <c r="R24">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S24">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="T24">
-        <v>2.6</v>
+        <v>3.44</v>
       </c>
       <c r="U24">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA24">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>3.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD24">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>1.06</v>
+        <v>2.71</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.35</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>2.61</v>
+        <v>1.5</v>
       </c>
       <c r="Q25">
-        <v>3.04</v>
+        <v>5.61</v>
       </c>
       <c r="R25">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U25">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
         <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AA25">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AB25">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD25">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF25">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="AG25">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-31 14:00:00</t>
+          <t>2026-08-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="Q26">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26">
-        <v>2.43</v>
+        <v>2.91</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AC26">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AG26">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R27">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>3.14</v>
+        <v>2.43</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="Z27">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD27">
+        <v>1.3</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>1.56</v>
+      </c>
+      <c r="AG27">
+        <v>2.02</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.22</v>
       </c>
-      <c r="AE27">
-        <v>1.05</v>
-      </c>
-      <c r="AF27">
-        <v>1.85</v>
-      </c>
-      <c r="AG27">
-        <v>1.74</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.23</v>
-      </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.9</v>
+        <v>1.66</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S28">
         <v>1.43</v>
       </c>
       <c r="T28">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U28">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y28">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z28">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="AA28">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AC28">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>1.2</v>
+        <v>1.99</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q29">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="R29">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="T29">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="U29">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="Z29">
-        <v>4.75</v>
+        <v>2.81</v>
       </c>
       <c r="AA29">
-        <v>1.52</v>
+        <v>2.31</v>
       </c>
       <c r="AB29">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD29">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AE29">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
+        <v>1.3</v>
+      </c>
+      <c r="AK29">
         <v>1.2</v>
-      </c>
-      <c r="AK29">
-        <v>2.06</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
@@ -5208,55 +5208,55 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,17 +5358,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N31">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P32">
+        <v>4.4</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
         <v>2.15</v>
       </c>
-      <c r="Q32">
-        <v>3.4</v>
-      </c>
-      <c r="R32">
-        <v>2.09</v>
-      </c>
-      <c r="S32">
-        <v>1.35</v>
-      </c>
-      <c r="T32">
-        <v>2.84</v>
-      </c>
-      <c r="U32">
-        <v>2.62</v>
-      </c>
-      <c r="V32">
-        <v>1.39</v>
-      </c>
-      <c r="W32">
-        <v>1.04</v>
-      </c>
-      <c r="X32">
-        <v>1.05</v>
-      </c>
-      <c r="Y32">
-        <v>1.22</v>
-      </c>
-      <c r="Z32">
-        <v>3.65</v>
-      </c>
-      <c r="AA32">
-        <v>1.86</v>
-      </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="O33">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA33">
+        <v>1.86</v>
+      </c>
+      <c r="AB33">
+        <v>1.9</v>
+      </c>
+      <c r="AC33">
+        <v>3.04</v>
+      </c>
+      <c r="AD33">
+        <v>1.35</v>
+      </c>
+      <c r="AE33">
+        <v>1.07</v>
+      </c>
+      <c r="AF33">
         <v>1.66</v>
       </c>
-      <c r="AB33">
-        <v>2.15</v>
-      </c>
-      <c r="AC33">
-        <v>2.51</v>
-      </c>
-      <c r="AD33">
-        <v>1.42</v>
-      </c>
-      <c r="AE33">
-        <v>1.14</v>
-      </c>
-      <c r="AF33">
-        <v>1.67</v>
-      </c>
       <c r="AG33">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="O34">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>5.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q34">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="U34">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="V34">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="AD34">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK34">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="O35">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="P35">
-        <v>3.3</v>
+        <v>5.41</v>
       </c>
       <c r="Q35">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S35">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="U35">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
         <v>1.12</v>
@@ -6047,31 +6047,31 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA35">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB35">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AC35">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>1.88</v>
+        <v>2.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.39</v>
+        <v>1.83</v>
       </c>
       <c r="O36">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
       <c r="P36">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q36">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="R36">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T36">
         <v>3.58</v>
       </c>
       <c r="U36">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V36">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>5.68</v>
+        <v>5.15</v>
       </c>
       <c r="AA36">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AC36">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AD36">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AE36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>2.98</v>
+        <v>1.88</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="O37">
-        <v>7</v>
+        <v>4.85</v>
       </c>
       <c r="P37">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="Q37">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="R37">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S37">
         <v>1.17</v>
       </c>
       <c r="T37">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="U37">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V37">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W37">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>5.65</v>
+        <v>5.68</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AC37">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE37">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF37">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK37">
-        <v>4.8</v>
+        <v>2.98</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>1.13</v>
       </c>
       <c r="O38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="Q38">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="R38">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="S38">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="T38">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="U38">
-        <v>4.33</v>
+        <v>2.08</v>
       </c>
       <c r="V38">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="W38">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
         <v>1.08</v>
       </c>
-      <c r="Y38">
-        <v>1.62</v>
-      </c>
       <c r="Z38">
-        <v>2.38</v>
+        <v>5.65</v>
       </c>
       <c r="AA38">
-        <v>2.91</v>
+        <v>1.44</v>
       </c>
       <c r="AB38">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="AC38">
-        <v>6.5</v>
+        <v>2.01</v>
       </c>
       <c r="AD38">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AF38">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="AG38">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
-        <v>1.71</v>
+        <v>4.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-31 14:30:00</t>
+          <t>2026-08-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.14</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="P39">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="Q39">
-        <v>1.46</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U39">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="V39">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA39">
-        <v>1.27</v>
+        <v>2.91</v>
       </c>
       <c r="AB39">
-        <v>3.15</v>
+        <v>1.42</v>
       </c>
       <c r="AC39">
-        <v>1.72</v>
+        <v>6.5</v>
       </c>
       <c r="AD39">
-        <v>1.92</v>
+        <v>1.1</v>
       </c>
       <c r="AE39">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="AG39">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AK39">
-        <v>3.95</v>
+        <v>1.71</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>1.14</v>
+      </c>
+      <c r="O40">
+        <v>6.8</v>
+      </c>
+      <c r="P40">
+        <v>13</v>
+      </c>
+      <c r="Q40">
+        <v>1.46</v>
+      </c>
+      <c r="R40">
+        <v>3.25</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>1.74</v>
+      </c>
+      <c r="V40">
+        <v>1.85</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>1.27</v>
+      </c>
+      <c r="AB40">
+        <v>3.15</v>
+      </c>
+      <c r="AC40">
         <v>1.72</v>
       </c>
-      <c r="O40">
-        <v>3.9</v>
-      </c>
-      <c r="P40">
-        <v>3.75</v>
-      </c>
-      <c r="Q40">
-        <v>2.15</v>
-      </c>
-      <c r="R40">
-        <v>2.62</v>
-      </c>
-      <c r="S40">
-        <v>1.21</v>
-      </c>
-      <c r="T40">
-        <v>3.68</v>
-      </c>
-      <c r="U40">
-        <v>2.12</v>
-      </c>
-      <c r="V40">
-        <v>1.66</v>
-      </c>
-      <c r="W40">
-        <v>1.13</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.08</v>
-      </c>
-      <c r="Z40">
-        <v>5.5</v>
-      </c>
-      <c r="AA40">
-        <v>1.47</v>
-      </c>
-      <c r="AB40">
-        <v>2.6</v>
-      </c>
-      <c r="AC40">
-        <v>2.14</v>
-      </c>
       <c r="AD40">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF40">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AG40">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK40">
-        <v>2.1</v>
+        <v>3.95</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>1.72</v>
+      </c>
+      <c r="O41">
+        <v>3.9</v>
+      </c>
+      <c r="P41">
+        <v>3.75</v>
+      </c>
+      <c r="Q41">
+        <v>2.15</v>
+      </c>
+      <c r="R41">
         <v>2.62</v>
       </c>
-      <c r="O41">
-        <v>3.25</v>
-      </c>
-      <c r="P41">
-        <v>2.65</v>
-      </c>
-      <c r="Q41">
-        <v>3.54</v>
-      </c>
-      <c r="R41">
-        <v>2.06</v>
-      </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="T41">
-        <v>2.84</v>
+        <v>3.68</v>
       </c>
       <c r="U41">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="V41">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>3.04</v>
+        <v>5.5</v>
       </c>
       <c r="AA41">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="AB41">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AC41">
-        <v>3.59</v>
+        <v>2.14</v>
       </c>
       <c r="AD41">
+        <v>1.63</v>
+      </c>
+      <c r="AE41">
         <v>1.25</v>
       </c>
-      <c r="AE41">
-        <v>1.05</v>
-      </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-31 15:00:00</t>
+          <t>2026-08-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O44">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>4.69</v>
+        <v>4.4</v>
       </c>
       <c r="Q44">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R44">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="S44">
         <v>1.17</v>
       </c>
       <c r="T44">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="U44">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="V44">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="W44">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z44">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA44">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AB44">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
       <c r="AC44">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AD44">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AE44">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF44">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AG44">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="O45">
-        <v>3.48</v>
+        <v>4.55</v>
       </c>
       <c r="P45">
-        <v>2</v>
+        <v>4.69</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-08-31 15:15:00</t>
+          <t>2026-08-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.42</v>
+        <v>3.2</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>3.48</v>
       </c>
       <c r="P46">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="Q46">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.48</v>
+        <v>1.42</v>
       </c>
       <c r="O47">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="P47">
-        <v>1.93</v>
+        <v>7.8</v>
       </c>
       <c r="Q47">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V47">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="AC47">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="AG47">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.21</v>
+        <v>2.41</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-08-31 15:30:00</t>
+          <t>2026-08-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>3.48</v>
+      </c>
+      <c r="O48">
+        <v>3.66</v>
+      </c>
+      <c r="P48">
+        <v>1.93</v>
+      </c>
+      <c r="Q48">
+        <v>3.9</v>
+      </c>
+      <c r="R48">
+        <v>2.21</v>
+      </c>
+      <c r="S48">
+        <v>1.29</v>
+      </c>
+      <c r="T48">
+        <v>3.3</v>
+      </c>
+      <c r="U48">
+        <v>2.5</v>
+      </c>
+      <c r="V48">
         <v>1.47</v>
-      </c>
-      <c r="O48">
-        <v>4.33</v>
-      </c>
-      <c r="P48">
-        <v>6.5</v>
-      </c>
-      <c r="Q48">
-        <v>1.95</v>
-      </c>
-      <c r="R48">
-        <v>2.15</v>
-      </c>
-      <c r="S48">
-        <v>1.33</v>
-      </c>
-      <c r="T48">
-        <v>3.02</v>
-      </c>
-      <c r="U48">
-        <v>2.48</v>
-      </c>
-      <c r="V48">
-        <v>1.46</v>
       </c>
       <c r="W48">
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AB48">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>2.63</v>
+        <v>1.21</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="O49">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="P49">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q49">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="R49">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>2.29</v>
+        <v>3.02</v>
       </c>
       <c r="U49">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="V49">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>2.56</v>
+        <v>3.44</v>
       </c>
       <c r="AA49">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="AB49">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="AC49">
-        <v>4.45</v>
+        <v>2.94</v>
       </c>
       <c r="AD49">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG49">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="P50">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="R50">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S50">
+        <v>1.51</v>
+      </c>
+      <c r="T50">
+        <v>2.29</v>
+      </c>
+      <c r="U50">
+        <v>3.2</v>
+      </c>
+      <c r="V50">
+        <v>1.24</v>
+      </c>
+      <c r="W50">
+        <v>1.02</v>
+      </c>
+      <c r="X50">
+        <v>1.04</v>
+      </c>
+      <c r="Y50">
         <v>1.4</v>
       </c>
-      <c r="T50">
-        <v>3</v>
-      </c>
-      <c r="U50">
-        <v>2.66</v>
-      </c>
-      <c r="V50">
-        <v>1.4</v>
-      </c>
-      <c r="W50">
-        <v>1.04</v>
-      </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
-      <c r="Y50">
-        <v>1.26</v>
-      </c>
       <c r="Z50">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="AB50">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AC50">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD50">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF50">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-08-31 15:45:00</t>
+          <t>2026-08-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="O51">
         <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q51">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V51">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -8658,28 +8658,28 @@
         <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AA51">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB51">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD51">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG51">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.93</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>5.5</v>
+        <v>1.91</v>
       </c>
       <c r="O52">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>1.53</v>
+        <v>3.7</v>
       </c>
       <c r="Q52">
-        <v>4.74</v>
+        <v>2.47</v>
       </c>
       <c r="R52">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W52">
+        <v>1.08</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>1.26</v>
+      </c>
+      <c r="Z52">
+        <v>3.58</v>
+      </c>
+      <c r="AA52">
+        <v>1.97</v>
+      </c>
+      <c r="AB52">
+        <v>1.89</v>
+      </c>
+      <c r="AC52">
+        <v>3.28</v>
+      </c>
+      <c r="AD52">
+        <v>1.31</v>
+      </c>
+      <c r="AE52">
         <v>1.07</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.23</v>
-      </c>
-      <c r="Z52">
-        <v>3.35</v>
-      </c>
-      <c r="AA52">
-        <v>1.8</v>
-      </c>
-      <c r="AB52">
-        <v>2.06</v>
-      </c>
-      <c r="AC52">
-        <v>2.88</v>
-      </c>
-      <c r="AD52">
-        <v>1.35</v>
-      </c>
-      <c r="AE52">
-        <v>1.1</v>
-      </c>
       <c r="AF52">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AG52">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00:00</t>
+          <t>2026-08-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P53">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q53">
-        <v>4.84</v>
+        <v>4.74</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="U53">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="V53">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AA53">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AC53">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG53">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>2.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="Q54">
-        <v>3.6</v>
+        <v>4.84</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U54">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="V54">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
+        <v>1.22</v>
+      </c>
+      <c r="Z54">
+        <v>3.42</v>
+      </c>
+      <c r="AA54">
+        <v>1.92</v>
+      </c>
+      <c r="AB54">
+        <v>1.9</v>
+      </c>
+      <c r="AC54">
+        <v>3.25</v>
+      </c>
+      <c r="AD54">
         <v>1.31</v>
       </c>
-      <c r="Z54">
-        <v>2.92</v>
-      </c>
-      <c r="AA54">
-        <v>2.06</v>
-      </c>
-      <c r="AB54">
-        <v>1.67</v>
-      </c>
-      <c r="AC54">
-        <v>3.72</v>
-      </c>
-      <c r="AD54">
-        <v>1.2</v>
-      </c>
       <c r="AE54">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG54">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AK54">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O55">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R55">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T55">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U55">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="V55">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z55">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="AA55">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AB55">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC55">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="AD55">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE55">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG55">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK55">
         <v>1.33</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="O56">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P56">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S56">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T56">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V56">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W56">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z56">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AA56">
         <v>2.25</v>
       </c>
       <c r="AB56">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AC56">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AD56">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF56">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG56">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK56">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O57">
         <v>2.9</v>
       </c>
       <c r="P57">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q57">
-        <v>3.44</v>
+        <v>2.62</v>
       </c>
       <c r="R57">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T57">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="U57">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="V57">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Z57">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="AA57">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB57">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AC57">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AD57">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE57">
         <v>1.01</v>
       </c>
       <c r="AF57">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG57">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="O58">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q58">
-        <v>2.38</v>
+        <v>3.44</v>
       </c>
       <c r="R58">
-        <v>2.56</v>
+        <v>1.88</v>
       </c>
       <c r="S58">
+        <v>1.44</v>
+      </c>
+      <c r="T58">
+        <v>2.45</v>
+      </c>
+      <c r="U58">
+        <v>3.34</v>
+      </c>
+      <c r="V58">
+        <v>1.25</v>
+      </c>
+      <c r="W58">
+        <v>1.05</v>
+      </c>
+      <c r="X58">
+        <v>1.05</v>
+      </c>
+      <c r="Y58">
+        <v>1.43</v>
+      </c>
+      <c r="Z58">
+        <v>2.46</v>
+      </c>
+      <c r="AA58">
+        <v>2.36</v>
+      </c>
+      <c r="AB58">
+        <v>1.51</v>
+      </c>
+      <c r="AC58">
+        <v>4.4</v>
+      </c>
+      <c r="AD58">
         <v>1.14</v>
       </c>
-      <c r="T58">
-        <v>4.55</v>
-      </c>
-      <c r="U58">
-        <v>1.8</v>
-      </c>
-      <c r="V58">
-        <v>1.93</v>
-      </c>
-      <c r="W58">
-        <v>1.25</v>
-      </c>
-      <c r="X58">
+      <c r="AE58">
         <v>1.01</v>
       </c>
-      <c r="Y58">
-        <v>1.03</v>
-      </c>
-      <c r="Z58">
-        <v>7.5</v>
-      </c>
-      <c r="AA58">
-        <v>1.24</v>
-      </c>
-      <c r="AB58">
-        <v>3.8</v>
-      </c>
-      <c r="AC58">
-        <v>1.7</v>
-      </c>
-      <c r="AD58">
-        <v>2.09</v>
-      </c>
-      <c r="AE58">
-        <v>1.49</v>
-      </c>
       <c r="AF58">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AG58">
-        <v>3.5</v>
+        <v>1.72</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK58">
-        <v>1.82</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-31 16:15:00</t>
+          <t>2026-08-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,31 +9926,31 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.16</v>
+        <v>1.91</v>
       </c>
       <c r="O59">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>12</v>
+        <v>3.1</v>
       </c>
       <c r="Q59">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="R59">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="S59">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="U59">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V59">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="W59">
         <v>1.25</v>
@@ -9959,31 +9959,31 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z59">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AB59">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="AC59">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AD59">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AE59">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AF59">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AG59">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
-        <v>5.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="P60">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="Q60">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="R60">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="V60">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>3.44</v>
+        <v>5.9</v>
       </c>
       <c r="AA60">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>1.83</v>
+        <v>2.87</v>
       </c>
       <c r="AC60">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="AD60">
-        <v>1.31</v>
+        <v>1.86</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG60">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AK60">
-        <v>2.06</v>
+        <v>5.2</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>4.3</v>
+        <v>2.27</v>
       </c>
       <c r="R61">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="U61">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="V61">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W61">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X61">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z61">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA61">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AB61">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AC61">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD61">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-31 16:30:00</t>
+          <t>2026-08-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>4.3</v>
+      </c>
+      <c r="R62">
+        <v>2.34</v>
+      </c>
+      <c r="S62">
+        <v>1.3</v>
+      </c>
+      <c r="T62">
+        <v>3.17</v>
+      </c>
+      <c r="U62">
+        <v>2.37</v>
+      </c>
+      <c r="V62">
+        <v>1.5</v>
+      </c>
+      <c r="W62">
+        <v>1.09</v>
+      </c>
+      <c r="X62">
+        <v>1.05</v>
+      </c>
+      <c r="Y62">
+        <v>1.23</v>
+      </c>
+      <c r="Z62">
+        <v>3.7</v>
+      </c>
+      <c r="AA62">
+        <v>1.66</v>
+      </c>
+      <c r="AB62">
+        <v>2.27</v>
+      </c>
+      <c r="AC62">
+        <v>2.7</v>
+      </c>
+      <c r="AD62">
+        <v>1.44</v>
+      </c>
+      <c r="AE62">
+        <v>1.14</v>
+      </c>
+      <c r="AF62">
+        <v>1.67</v>
+      </c>
+      <c r="AG62">
+        <v>2.1</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.23</v>
+      </c>
+      <c r="AK62">
         <v>1.18</v>
-      </c>
-      <c r="O62">
-        <v>7.5</v>
-      </c>
-      <c r="P62">
-        <v>13</v>
-      </c>
-      <c r="Q62">
-        <v>1.55</v>
-      </c>
-      <c r="R62">
-        <v>3.1</v>
-      </c>
-      <c r="S62">
-        <v>1.19</v>
-      </c>
-      <c r="T62">
-        <v>4.6</v>
-      </c>
-      <c r="U62">
-        <v>2.01</v>
-      </c>
-      <c r="V62">
-        <v>1.83</v>
-      </c>
-      <c r="W62">
-        <v>1.21</v>
-      </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.08</v>
-      </c>
-      <c r="Z62">
-        <v>6.6</v>
-      </c>
-      <c r="AA62">
-        <v>1.33</v>
-      </c>
-      <c r="AB62">
-        <v>3.4</v>
-      </c>
-      <c r="AC62">
-        <v>1.97</v>
-      </c>
-      <c r="AD62">
-        <v>1.97</v>
-      </c>
-      <c r="AE62">
-        <v>1.34</v>
-      </c>
-      <c r="AF62">
-        <v>2.05</v>
-      </c>
-      <c r="AG62">
-        <v>1.77</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.1</v>
-      </c>
-      <c r="AK62">
-        <v>4.37</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="P63">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="Q63">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="R63">
+        <v>3.1</v>
+      </c>
+      <c r="S63">
+        <v>1.19</v>
+      </c>
+      <c r="T63">
+        <v>4.6</v>
+      </c>
+      <c r="U63">
+        <v>2.01</v>
+      </c>
+      <c r="V63">
+        <v>1.83</v>
+      </c>
+      <c r="W63">
+        <v>1.21</v>
+      </c>
+      <c r="X63">
+        <v>1.01</v>
+      </c>
+      <c r="Y63">
+        <v>1.08</v>
+      </c>
+      <c r="Z63">
+        <v>6.6</v>
+      </c>
+      <c r="AA63">
+        <v>1.33</v>
+      </c>
+      <c r="AB63">
+        <v>3.4</v>
+      </c>
+      <c r="AC63">
+        <v>1.97</v>
+      </c>
+      <c r="AD63">
+        <v>1.97</v>
+      </c>
+      <c r="AE63">
+        <v>1.34</v>
+      </c>
+      <c r="AF63">
         <v>2.05</v>
       </c>
-      <c r="S63">
-        <v>1.56</v>
-      </c>
-      <c r="T63">
-        <v>2.5</v>
-      </c>
-      <c r="U63">
-        <v>3.7</v>
-      </c>
-      <c r="V63">
-        <v>1.2</v>
-      </c>
-      <c r="W63">
-        <v>1.01</v>
-      </c>
-      <c r="X63">
-        <v>1.06</v>
-      </c>
-      <c r="Y63">
-        <v>1.53</v>
-      </c>
-      <c r="Z63">
-        <v>2.34</v>
-      </c>
-      <c r="AA63">
-        <v>2.68</v>
-      </c>
-      <c r="AB63">
-        <v>1.47</v>
-      </c>
-      <c r="AC63">
-        <v>5.2</v>
-      </c>
-      <c r="AD63">
-        <v>1.14</v>
-      </c>
-      <c r="AE63">
-        <v>1.01</v>
-      </c>
-      <c r="AF63">
-        <v>2.5</v>
-      </c>
       <c r="AG63">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK63">
-        <v>2.25</v>
+        <v>4.37</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-31 19:00:00</t>
+          <t>2026-08-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P64">
-        <v>3.05</v>
+        <v>6.97</v>
       </c>
       <c r="Q64">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="R64">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="T64">
-        <v>2.85</v>
+        <v>2.26</v>
       </c>
       <c r="U64">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="V64">
+        <v>1.25</v>
+      </c>
+      <c r="W64">
+        <v>1.01</v>
+      </c>
+      <c r="X64">
+        <v>1.06</v>
+      </c>
+      <c r="Y64">
+        <v>1.56</v>
+      </c>
+      <c r="Z64">
+        <v>2.38</v>
+      </c>
+      <c r="AA64">
+        <v>2.68</v>
+      </c>
+      <c r="AB64">
         <v>1.4</v>
       </c>
-      <c r="W64">
+      <c r="AC64">
+        <v>5.2</v>
+      </c>
+      <c r="AD64">
         <v>1.1</v>
       </c>
-      <c r="X64">
-        <v>1</v>
-      </c>
-      <c r="Y64">
-        <v>1.25</v>
-      </c>
-      <c r="Z64">
-        <v>3.6</v>
-      </c>
-      <c r="AA64">
-        <v>1.89</v>
-      </c>
-      <c r="AB64">
-        <v>1.9</v>
-      </c>
-      <c r="AC64">
-        <v>2.92</v>
-      </c>
-      <c r="AD64">
-        <v>1.31</v>
-      </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF64">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="AG64">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-08-31 19:15:00</t>
+          <t>2026-08-31 19:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="Q65">
-        <v>2.22</v>
+        <v>2.53</v>
       </c>
       <c r="R65">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S65">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U65">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="V65">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
+        <v>3.6</v>
+      </c>
+      <c r="AA65">
+        <v>1.89</v>
+      </c>
+      <c r="AB65">
+        <v>1.9</v>
+      </c>
+      <c r="AC65">
         <v>2.92</v>
       </c>
-      <c r="AA65">
-        <v>2.1</v>
-      </c>
-      <c r="AB65">
-        <v>1.7</v>
-      </c>
-      <c r="AC65">
-        <v>3.5</v>
-      </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:00</t>
+          <t>2026-08-31 19:15:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="Q66">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="R66">
+        <v>2</v>
+      </c>
+      <c r="S66">
+        <v>1.43</v>
+      </c>
+      <c r="T66">
+        <v>2.76</v>
+      </c>
+      <c r="U66">
+        <v>2.98</v>
+      </c>
+      <c r="V66">
+        <v>1.33</v>
+      </c>
+      <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.33</v>
+      </c>
+      <c r="Z66">
+        <v>2.92</v>
+      </c>
+      <c r="AA66">
         <v>2.1</v>
       </c>
-      <c r="S66">
-        <v>1.42</v>
-      </c>
-      <c r="T66">
-        <v>2.65</v>
-      </c>
-      <c r="U66">
-        <v>2.85</v>
-      </c>
-      <c r="V66">
-        <v>1.36</v>
-      </c>
-      <c r="W66">
-        <v>1.07</v>
-      </c>
-      <c r="X66">
-        <v>1.06</v>
-      </c>
-      <c r="Y66">
-        <v>1.3</v>
-      </c>
-      <c r="Z66">
-        <v>3.2</v>
-      </c>
-      <c r="AA66">
-        <v>2.05</v>
-      </c>
       <c r="AB66">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC66">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
         <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG66">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK66">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-08-31 20:00:00</t>
+          <t>2026-08-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,61 +11230,61 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q67">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T67">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U67">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="V67">
         <v>1.36</v>
       </c>
       <c r="W67">
+        <v>1.07</v>
+      </c>
+      <c r="X67">
+        <v>1.06</v>
+      </c>
+      <c r="Y67">
+        <v>1.3</v>
+      </c>
+      <c r="Z67">
+        <v>3.2</v>
+      </c>
+      <c r="AA67">
+        <v>2.05</v>
+      </c>
+      <c r="AB67">
+        <v>1.68</v>
+      </c>
+      <c r="AC67">
+        <v>3.6</v>
+      </c>
+      <c r="AD67">
+        <v>1.3</v>
+      </c>
+      <c r="AE67">
         <v>1.08</v>
       </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.28</v>
-      </c>
-      <c r="Z67">
-        <v>3.1</v>
-      </c>
-      <c r="AA67">
-        <v>1.9</v>
-      </c>
-      <c r="AB67">
-        <v>1.84</v>
-      </c>
-      <c r="AC67">
-        <v>3.2</v>
-      </c>
-      <c r="AD67">
-        <v>1.26</v>
-      </c>
-      <c r="AE67">
-        <v>1.06</v>
-      </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG67">
         <v>1.93</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
         <v>1.74</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-08-31 21:00:00</t>
+          <t>2026-08-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="O68">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q68">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R68">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S68">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="U68">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="V68">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z68">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AA68">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AC68">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD68">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE68">
         <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="O69">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11672,156 +11672,319 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Boston Legacy W</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N70">
+        <v>2.7</v>
+      </c>
+      <c r="O70">
+        <v>3.26</v>
+      </c>
+      <c r="P70">
+        <v>2.45</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>21:45</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Universidad Católica</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>O'Higgins</t>
         </is>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N70">
+      <c r="N71">
         <v>1.8</v>
       </c>
-      <c r="O70">
+      <c r="O71">
         <v>3.75</v>
       </c>
-      <c r="P70">
+      <c r="P71">
         <v>4</v>
       </c>
-      <c r="Q70">
+      <c r="Q71">
         <v>2.29</v>
       </c>
-      <c r="R70">
+      <c r="R71">
         <v>2.23</v>
       </c>
-      <c r="S70">
+      <c r="S71">
         <v>1.3</v>
       </c>
-      <c r="T70">
+      <c r="T71">
         <v>3.2</v>
       </c>
-      <c r="U70">
+      <c r="U71">
         <v>2.63</v>
       </c>
-      <c r="V70">
+      <c r="V71">
         <v>1.44</v>
       </c>
-      <c r="W70">
+      <c r="W71">
         <v>1.11</v>
       </c>
-      <c r="X70">
+      <c r="X71">
         <v>1.04</v>
       </c>
-      <c r="Y70">
+      <c r="Y71">
         <v>1.21</v>
       </c>
-      <c r="Z70">
+      <c r="Z71">
         <v>3.68</v>
       </c>
-      <c r="AA70">
+      <c r="AA71">
         <v>1.72</v>
       </c>
-      <c r="AB70">
+      <c r="AB71">
         <v>2.07</v>
       </c>
-      <c r="AC70">
+      <c r="AC71">
         <v>2.75</v>
       </c>
-      <c r="AD70">
+      <c r="AD71">
         <v>1.38</v>
       </c>
-      <c r="AE70">
+      <c r="AE71">
         <v>1.11</v>
       </c>
-      <c r="AF70">
+      <c r="AF71">
         <v>1.67</v>
       </c>
-      <c r="AG70">
+      <c r="AG71">
         <v>2.05</v>
       </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
         <v>1.16</v>
       </c>
-      <c r="AK70">
+      <c r="AK71">
         <v>1.83</v>
       </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>-1</v>
-      </c>
-      <c r="AN70">
-        <v>-1</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>-1</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>2026-08-31 21:45:00</t>
         </is>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1456,16 +1456,16 @@
         <v>4.2</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q7">
         <v>4.5</v>
       </c>
       <c r="R7">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
         <v>4</v>
@@ -1483,10 +1483,10 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AA7">
         <v>1.43</v>
@@ -1504,7 +1504,7 @@
         <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AG7">
         <v>2.35</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK7">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         <v>3.4</v>
       </c>
       <c r="R33">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
         <v>1.35</v>
       </c>
       <c r="T33">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="U33">
         <v>2.62</v>
@@ -5721,25 +5721,25 @@
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
         <v>3.65</v>
       </c>
       <c r="AA33">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC33">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
         <v>1.66</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8954,28 +8954,28 @@
         <v>4.2</v>
       </c>
       <c r="P53">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q53">
-        <v>4.74</v>
+        <v>6.57</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
         <v>3.05</v>
       </c>
       <c r="U53">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.01</v>
@@ -8984,28 +8984,28 @@
         <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
         <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC53">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE53">
         <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG53">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK53">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1302,10 +1302,10 @@
         <v>2.24</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="U6">
         <v>2.63</v>
@@ -1317,7 +1317,7 @@
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.27</v>
@@ -1332,13 +1332,13 @@
         <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
         <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
         <v>1.66</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
         <v>4.5</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK7">
         <v>1.13</v>
@@ -3249,58 +3249,58 @@
         <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
         <v>2.66</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V18">
         <v>1.37</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA18">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC18">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
         <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="O22">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="P22">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="Q22">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="R22">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S22">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T22">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U22">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="V22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X22">
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z22">
-        <v>2.58</v>
+        <v>2.47</v>
       </c>
       <c r="AA22">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AB22">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AC22">
-        <v>4.87</v>
+        <v>4.8</v>
       </c>
       <c r="AD22">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK22">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P23">
         <v>1.62</v>
       </c>
       <c r="Q23">
-        <v>5.25</v>
+        <v>5.54</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U23">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
         <v>1.04</v>
@@ -4103,13 +4103,13 @@
         <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AD23">
         <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
         <v>1.8</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4393,28 +4393,28 @@
         <v>1.5</v>
       </c>
       <c r="Q25">
-        <v>5.61</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="U25">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
         <v>1.33</v>
@@ -4423,25 +4423,25 @@
         <v>3.3</v>
       </c>
       <c r="AA25">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         <v>2.61</v>
       </c>
       <c r="Q26">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="S26">
         <v>1.36</v>
@@ -4574,28 +4574,28 @@
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA26">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
         <v>1.05</v>
@@ -4620,7 +4620,7 @@
         <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4876,13 +4876,13 @@
         <v>1.66</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>4.88</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
         <v>2.19</v>
@@ -4900,37 +4900,37 @@
         <v>1.33</v>
       </c>
       <c r="W28">
+        <v>1.02</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.31</v>
+      </c>
+      <c r="Z28">
+        <v>2.92</v>
+      </c>
+      <c r="AA28">
+        <v>2.12</v>
+      </c>
+      <c r="AB28">
+        <v>1.7</v>
+      </c>
+      <c r="AC28">
+        <v>3.58</v>
+      </c>
+      <c r="AD28">
+        <v>1.25</v>
+      </c>
+      <c r="AE28">
         <v>1.04</v>
       </c>
-      <c r="X28">
-        <v>1.06</v>
-      </c>
-      <c r="Y28">
-        <v>1.36</v>
-      </c>
-      <c r="Z28">
-        <v>3.25</v>
-      </c>
-      <c r="AA28">
+      <c r="AF28">
         <v>1.95</v>
       </c>
-      <c r="AB28">
-        <v>1.67</v>
-      </c>
-      <c r="AC28">
-        <v>3.5</v>
-      </c>
-      <c r="AD28">
-        <v>1.22</v>
-      </c>
-      <c r="AE28">
-        <v>1.05</v>
-      </c>
-      <c r="AF28">
-        <v>1.85</v>
-      </c>
       <c r="AG28">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,22 +5036,22 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O29">
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Q29">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T29">
         <v>2.6</v>
@@ -5063,37 +5063,37 @@
         <v>1.29</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X29">
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z29">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AA29">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC29">
         <v>4.1</v>
       </c>
       <c r="AD29">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG29">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB32">
         <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="P34">
         <v>4.8</v>
@@ -5863,16 +5863,16 @@
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
         <v>1.5</v>
@@ -5884,25 +5884,25 @@
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC34">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AD34">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,16 +6023,16 @@
         <v>5.41</v>
       </c>
       <c r="Q35">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S35">
         <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
         <v>2.2</v>
@@ -6041,10 +6041,10 @@
         <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.11</v>
@@ -6062,10 +6062,10 @@
         <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
         <v>1.6</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,31 +6180,31 @@
         <v>1.83</v>
       </c>
       <c r="O36">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q36">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="V36">
         <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6213,16 +6213,16 @@
         <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="AA36">
         <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AC36">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD36">
         <v>1.62</v>
@@ -6231,10 +6231,10 @@
         <v>1.25</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
         <v>1.88</v>
@@ -6343,61 +6343,61 @@
         <v>1.39</v>
       </c>
       <c r="O37">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="P37">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q37">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R37">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T37">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V37">
         <v>1.66</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>5.68</v>
+        <v>5.35</v>
       </c>
       <c r="AA37">
         <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AC37">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD37">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE37">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK37">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,13 +6506,13 @@
         <v>1.13</v>
       </c>
       <c r="O38">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="P38">
         <v>11</v>
       </c>
       <c r="Q38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R38">
         <v>2.88</v>
@@ -6521,16 +6521,16 @@
         <v>1.17</v>
       </c>
       <c r="T38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V38">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6545,22 +6545,22 @@
         <v>1.44</v>
       </c>
       <c r="AB38">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC38">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD38">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE38">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF38">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG38">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="O42">
         <v>3.25</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q42">
         <v>3.54</v>
       </c>
       <c r="R42">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
         <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="AA42">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB42">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC42">
         <v>3.59</v>
       </c>
       <c r="AD42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE42">
         <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>1.55</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P44">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q44">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R44">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="S44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T44">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="U44">
+        <v>1.85</v>
+      </c>
+      <c r="V44">
         <v>1.86</v>
-      </c>
-      <c r="V44">
-        <v>1.87</v>
       </c>
       <c r="W44">
         <v>1.25</v>
@@ -7514,10 +7514,10 @@
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z44">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AA44">
         <v>1.29</v>
@@ -7529,13 +7529,13 @@
         <v>1.75</v>
       </c>
       <c r="AD44">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AE44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG44">
         <v>2.94</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O45">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="P45">
-        <v>4.69</v>
+        <v>4.6</v>
       </c>
       <c r="Q45">
         <v>1.99</v>
@@ -7665,7 +7665,7 @@
         <v>4.15</v>
       </c>
       <c r="U45">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V45">
         <v>1.79</v>
@@ -7677,10 +7677,10 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA45">
         <v>1.31</v>
@@ -7692,7 +7692,7 @@
         <v>1.88</v>
       </c>
       <c r="AD45">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE45">
         <v>1.33</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O46">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,49 +7979,49 @@
         <v>7.8</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S47">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T47">
         <v>2.6</v>
       </c>
       <c r="U47">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V47">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
         <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z47">
         <v>2.62</v>
       </c>
       <c r="AA47">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AB47">
         <v>1.59</v>
       </c>
       <c r="AC47">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
         <v>2.33</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK47">
         <v>2.41</v>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="O48">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q48">
         <v>3.9</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
         <v>2.5</v>
@@ -8181,16 +8181,16 @@
         <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
         <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="AK48">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>1.95</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="V49">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA49">
         <v>1.84</v>
@@ -8341,10 +8341,10 @@
         <v>1.98</v>
       </c>
       <c r="AC49">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
         <v>1.09</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK49">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R50">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="S50">
         <v>1.51</v>
@@ -8483,25 +8483,25 @@
         <v>3.2</v>
       </c>
       <c r="V50">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X50">
         <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z50">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AA50">
         <v>2.36</v>
       </c>
       <c r="AB50">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AC50">
         <v>4.45</v>
@@ -8510,13 +8510,13 @@
         <v>1.14</v>
       </c>
       <c r="AE50">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF50">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AG50">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>3.6</v>
@@ -8631,22 +8631,22 @@
         <v>1.83</v>
       </c>
       <c r="Q51">
-        <v>4.6</v>
+        <v>4.79</v>
       </c>
       <c r="R51">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8655,10 +8655,10 @@
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA51">
         <v>1.94</v>
@@ -8667,16 +8667,16 @@
         <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD51">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE51">
         <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
         <v>1.9</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O52">
         <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="Q52">
         <v>2.47</v>
       </c>
       <c r="R52">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
         <v>1.35</v>
@@ -8815,34 +8815,34 @@
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA52">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB52">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AC52">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="AD52">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
         <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="O53">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="P53">
         <v>1.52</v>
@@ -8960,7 +8960,7 @@
         <v>6.57</v>
       </c>
       <c r="R53">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
         <v>1.36</v>
@@ -8996,7 +8996,7 @@
         <v>2.8</v>
       </c>
       <c r="AD53">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
         <v>1.1</v>
@@ -9280,7 +9280,7 @@
         <v>3.1</v>
       </c>
       <c r="P55">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -9292,16 +9292,16 @@
         <v>1.38</v>
       </c>
       <c r="T55">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="U55">
         <v>2.97</v>
       </c>
       <c r="V55">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9313,13 +9313,13 @@
         <v>2.92</v>
       </c>
       <c r="AA55">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB55">
         <v>1.67</v>
       </c>
       <c r="AC55">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AD55">
         <v>1.2</v>
@@ -9331,7 +9331,7 @@
         <v>1.81</v>
       </c>
       <c r="AG55">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O56">
         <v>2.8</v>
@@ -9446,25 +9446,25 @@
         <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>3.85</v>
+        <v>4.03</v>
       </c>
       <c r="R56">
         <v>1.89</v>
       </c>
       <c r="S56">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T56">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U56">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V56">
         <v>1.27</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
         <v>1.05</v>
@@ -9473,7 +9473,7 @@
         <v>1.4</v>
       </c>
       <c r="Z56">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="AA56">
         <v>2.25</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>2.15</v>
       </c>
       <c r="O57">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S57">
         <v>1.49</v>
@@ -9621,7 +9621,7 @@
         <v>2.34</v>
       </c>
       <c r="U57">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V57">
         <v>1.3</v>
@@ -9636,13 +9636,13 @@
         <v>1.37</v>
       </c>
       <c r="Z57">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AA57">
         <v>2.25</v>
       </c>
       <c r="AB57">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC57">
         <v>4.15</v>
@@ -9673,7 +9673,7 @@
         <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,16 +9772,16 @@
         <v>2.5</v>
       </c>
       <c r="Q58">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="R58">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T58">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="U58">
         <v>3.34</v>
@@ -9790,16 +9790,16 @@
         <v>1.25</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X58">
         <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Z58">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA58">
         <v>2.36</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK58">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10092,19 +10092,19 @@
         <v>1.16</v>
       </c>
       <c r="O60">
-        <v>7.7</v>
+        <v>7.05</v>
       </c>
       <c r="P60">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R60">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
         <v>4.5</v>
@@ -10128,25 +10128,25 @@
         <v>5.9</v>
       </c>
       <c r="AA60">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AB60">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="AC60">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AD60">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE60">
         <v>1.3</v>
       </c>
       <c r="AF60">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG60">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="AK60">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,22 +10261,22 @@
         <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R61">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S61">
+        <v>1.4</v>
+      </c>
+      <c r="T61">
+        <v>2.63</v>
+      </c>
+      <c r="U61">
+        <v>2.93</v>
+      </c>
+      <c r="V61">
         <v>1.36</v>
-      </c>
-      <c r="T61">
-        <v>2.9</v>
-      </c>
-      <c r="U61">
-        <v>2.88</v>
-      </c>
-      <c r="V61">
-        <v>1.41</v>
       </c>
       <c r="W61">
         <v>1.04</v>
@@ -10285,25 +10285,25 @@
         <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z61">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA61">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB61">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC61">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AD61">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE61">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
         <v>1.8</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK61">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q62">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="R62">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T62">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="U62">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W62">
         <v>1.09</v>
       </c>
       <c r="X62">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
         <v>3.7</v>
       </c>
       <c r="AA62">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AB62">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AC62">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF62">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG62">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -2265,49 +2265,49 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O12">
         <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U12">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC12">
         <v>3.2</v>
@@ -2316,13 +2316,13 @@
         <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P17">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3270,7 +3270,7 @@
         <v>1.37</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3282,16 +3282,16 @@
         <v>3.3</v>
       </c>
       <c r="AA18">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC18">
         <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AK18">
         <v>1.27</v>
@@ -4221,58 +4221,58 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P24">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="Q24">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="R24">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="S24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
         <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
         <v>1.7</v>
@@ -4294,7 +4294,7 @@
         <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>1.5</v>
       </c>
       <c r="Q25">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
         <v>1.42</v>
@@ -4423,16 +4423,16 @@
         <v>3.3</v>
       </c>
       <c r="AA25">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB25">
         <v>1.8</v>
       </c>
       <c r="AC25">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
         <v>1.04</v>
@@ -4457,7 +4457,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4876,16 +4876,16 @@
         <v>1.66</v>
       </c>
       <c r="O28">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="R28">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="S28">
         <v>1.43</v>
@@ -4921,16 +4921,16 @@
         <v>3.58</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
         <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>2.17</v>
       </c>
       <c r="AB29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
         <v>4.1</v>
@@ -5090,7 +5090,7 @@
         <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
         <v>1.7</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q30">
         <v>2.18</v>
@@ -5217,19 +5217,19 @@
         <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V30">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.17</v>
@@ -5238,13 +5238,13 @@
         <v>4.75</v>
       </c>
       <c r="AA30">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB30">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC30">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD30">
         <v>1.5</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O35">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
-        <v>5.41</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
         <v>1.95</v>
@@ -6056,7 +6056,7 @@
         <v>1.55</v>
       </c>
       <c r="AB35">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AC35">
         <v>2.35</v>
@@ -6087,7 +6087,7 @@
         <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6225,16 +6225,16 @@
         <v>2.25</v>
       </c>
       <c r="AD36">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE36">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF36">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6672,22 +6672,22 @@
         <v>3</v>
       </c>
       <c r="P39">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="S39">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T39">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U39">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="V39">
         <v>1.22</v>
@@ -6696,28 +6696,28 @@
         <v>1</v>
       </c>
       <c r="X39">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y39">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z39">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AA39">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="AB39">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC39">
         <v>6.5</v>
       </c>
       <c r="AD39">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE39">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF39">
         <v>2.29</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AK39">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="O40">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="P40">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q40">
         <v>1.46</v>
@@ -6844,10 +6844,10 @@
         <v>3.25</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>1.74</v>
@@ -6856,16 +6856,16 @@
         <v>1.85</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X40">
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
         <v>1.27</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="O41">
+        <v>4.1</v>
+      </c>
+      <c r="P41">
         <v>3.9</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
+        <v>2.14</v>
+      </c>
+      <c r="R41">
+        <v>2.5</v>
+      </c>
+      <c r="S41">
+        <v>1.22</v>
+      </c>
+      <c r="T41">
         <v>3.75</v>
       </c>
-      <c r="Q41">
-        <v>2.15</v>
-      </c>
-      <c r="R41">
-        <v>2.62</v>
-      </c>
-      <c r="S41">
-        <v>1.21</v>
-      </c>
-      <c r="T41">
-        <v>3.68</v>
-      </c>
       <c r="U41">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V41">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,25 +7031,25 @@
         <v>5.5</v>
       </c>
       <c r="AA41">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB41">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC41">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
         <v>1.63</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF41">
         <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
         <v>2.1</v>
@@ -7164,7 +7164,7 @@
         <v>2.3</v>
       </c>
       <c r="Q42">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="R42">
         <v>2.15</v>
@@ -7179,7 +7179,7 @@
         <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W42">
         <v>1.05</v>
@@ -7212,7 +7212,7 @@
         <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O44">
         <v>4.4</v>
       </c>
       <c r="P44">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q44">
         <v>1.94</v>
@@ -7532,7 +7532,7 @@
         <v>2.05</v>
       </c>
       <c r="AE44">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF44">
         <v>1.36</v>
@@ -7647,10 +7647,10 @@
         <v>1.55</v>
       </c>
       <c r="O45">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P45">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q45">
         <v>1.99</v>
@@ -7683,10 +7683,10 @@
         <v>6.5</v>
       </c>
       <c r="AA45">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB45">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC45">
         <v>1.88</v>
@@ -7717,7 +7717,7 @@
         <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8003,25 +8003,25 @@
         <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z47">
         <v>2.62</v>
       </c>
       <c r="AA47">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AB47">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC47">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
         <v>2.33</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
         <v>2.41</v>
@@ -8631,7 +8631,7 @@
         <v>1.83</v>
       </c>
       <c r="Q51">
-        <v>4.79</v>
+        <v>3.92</v>
       </c>
       <c r="R51">
         <v>2.13</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O52">
         <v>3.6</v>
@@ -8797,34 +8797,34 @@
         <v>2.47</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
         <v>3.08</v>
       </c>
       <c r="U52">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y52">
         <v>1.29</v>
       </c>
       <c r="Z52">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
         <v>1.96</v>
@@ -8833,7 +8833,7 @@
         <v>3.12</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE52">
         <v>1.07</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,28 +8948,28 @@
         </is>
       </c>
       <c r="N53">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="O53">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="P53">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Q53">
-        <v>6.57</v>
+        <v>6.63</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
         <v>3.05</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V53">
         <v>1.46</v>
@@ -8987,13 +8987,13 @@
         <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC53">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD53">
         <v>1.35</v>
@@ -9114,61 +9114,61 @@
         <v>4.8</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P54">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q54">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="R54">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
+        <v>2.8</v>
+      </c>
+      <c r="U54">
         <v>2.7</v>
       </c>
-      <c r="U54">
-        <v>2.86</v>
-      </c>
       <c r="V54">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z54">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA54">
         <v>1.92</v>
       </c>
       <c r="AB54">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC54">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD54">
         <v>1.31</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF54">
         <v>1.85</v>
       </c>
       <c r="AG54">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK54">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9926,31 +9926,31 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P59">
         <v>3.1</v>
       </c>
       <c r="Q59">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R59">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="S59">
         <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="U59">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V59">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="W59">
         <v>1.25</v>
@@ -9962,25 +9962,25 @@
         <v>1.03</v>
       </c>
       <c r="Z59">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA59">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AB59">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AC59">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AD59">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AE59">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AF59">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AG59">
         <v>3.5</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
         <v>1.82</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O60">
-        <v>7.05</v>
+        <v>7.25</v>
       </c>
       <c r="P60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q60">
         <v>1.45</v>
@@ -10104,7 +10104,7 @@
         <v>3.11</v>
       </c>
       <c r="S60">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
         <v>4.5</v>
@@ -10282,7 +10282,7 @@
         <v>1.04</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.29</v>
@@ -10297,10 +10297,10 @@
         <v>1.82</v>
       </c>
       <c r="AC61">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="AD61">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE61">
         <v>1.06</v>
@@ -10309,7 +10309,7 @@
         <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="O63">
         <v>7.5</v>
@@ -10590,7 +10590,7 @@
         <v>1.55</v>
       </c>
       <c r="R63">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="S63">
         <v>1.19</v>
@@ -10599,13 +10599,13 @@
         <v>4.6</v>
       </c>
       <c r="U63">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="V63">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="W63">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10614,28 +10614,28 @@
         <v>1.08</v>
       </c>
       <c r="Z63">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AA63">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB63">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC63">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AD63">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AE63">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF63">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG63">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.1</v>
       </c>
       <c r="AK63">
-        <v>4.37</v>
+        <v>5.25</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,19 +10750,19 @@
         <v>6.97</v>
       </c>
       <c r="Q64">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R64">
         <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T64">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U64">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="V64">
         <v>1.25</v>
@@ -10783,13 +10783,13 @@
         <v>2.68</v>
       </c>
       <c r="AB64">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC64">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD64">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE64">
         <v>1.04</v>
@@ -10907,16 +10907,16 @@
         <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P65">
         <v>3.05</v>
       </c>
       <c r="Q65">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="R65">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
         <v>1.33</v>
@@ -10925,25 +10925,25 @@
         <v>2.85</v>
       </c>
       <c r="U65">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
         <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA65">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB65">
         <v>1.9</v>
@@ -10955,13 +10955,13 @@
         <v>1.31</v>
       </c>
       <c r="AE65">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
         <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK65">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,61 +11070,61 @@
         <v>1.68</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q66">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S66">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U66">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="V66">
         <v>1.33</v>
       </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y66">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z66">
         <v>2.92</v>
       </c>
       <c r="AA66">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB66">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC66">
         <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE66">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
         <v>2</v>
       </c>
       <c r="AG66">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK66">
         <v>2.06</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O67">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="Q67">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S67">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T67">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U67">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z67">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="AA67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB67">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC67">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG67">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O68">
         <v>3.35</v>
       </c>
       <c r="P68">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q68">
         <v>2.55</v>
@@ -11408,16 +11408,16 @@
         <v>2.06</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T68">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U68">
         <v>2.78</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W68">
         <v>1.08</v>
@@ -11432,16 +11432,16 @@
         <v>3.1</v>
       </c>
       <c r="AA68">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB68">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC68">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD68">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE68">
         <v>1.06</v>
@@ -11450,7 +11450,7 @@
         <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
         <v>4.2</v>
       </c>
       <c r="Q69">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="R69">
         <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T69">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="U69">
         <v>3.28</v>
@@ -11583,19 +11583,19 @@
         <v>1.31</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y69">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z69">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AA69">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AB69">
         <v>1.58</v>
@@ -11607,13 +11607,13 @@
         <v>1.18</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
         <v>2</v>
       </c>
       <c r="AG69">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>4</v>
       </c>
       <c r="Q71">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R71">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S71">
         <v>1.3</v>
@@ -11906,19 +11906,19 @@
         <v>2.63</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W71">
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z71">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA71">
         <v>1.72</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL71">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4067,13 +4067,13 @@
         <v>1.62</v>
       </c>
       <c r="Q23">
-        <v>5.54</v>
+        <v>5.25</v>
       </c>
       <c r="R23">
         <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
         <v>2.77</v>
@@ -4106,7 +4106,7 @@
         <v>2.9</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE23">
         <v>1.13</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="O24">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P24">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="Q24">
         <v>1.88</v>
@@ -4272,7 +4272,7 @@
         <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
         <v>1.7</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>1.58</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5253,10 +5253,10 @@
         <v>1.23</v>
       </c>
       <c r="AF30">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
         <v>1.98</v>
@@ -5543,43 +5543,43 @@
         <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U32">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
         <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AA32">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AB32">
         <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AD32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG32">
         <v>1.68</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -8181,7 +8181,7 @@
         <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
         <v>1.18</v>
@@ -8305,19 +8305,19 @@
         <v>6.5</v>
       </c>
       <c r="Q49">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R49">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="V49">
         <v>1.43</v>
@@ -8326,7 +8326,7 @@
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
@@ -8350,7 +8350,7 @@
         <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG49">
         <v>1.75</v>
@@ -9138,7 +9138,7 @@
         <v>1.4</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
         <v>1</v>
@@ -9150,7 +9150,7 @@
         <v>3.5</v>
       </c>
       <c r="AA54">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AB54">
         <v>1.86</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10427,7 +10427,7 @@
         <v>4.5</v>
       </c>
       <c r="R62">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
         <v>1.28</v>
@@ -10436,10 +10436,10 @@
         <v>3.3</v>
       </c>
       <c r="U62">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="V62">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W62">
         <v>1.09</v>
@@ -10596,13 +10596,13 @@
         <v>1.19</v>
       </c>
       <c r="T63">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
         <v>1.92</v>
       </c>
       <c r="V63">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W63">
         <v>1.22</v>
@@ -10651,7 +10651,7 @@
         <v>1.1</v>
       </c>
       <c r="AK63">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11079,16 +11079,16 @@
         <v>2.29</v>
       </c>
       <c r="R66">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T66">
         <v>2.59</v>
       </c>
       <c r="U66">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="V66">
         <v>1.33</v>
@@ -11115,13 +11115,13 @@
         <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
         <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG66">
         <v>1.73</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
         <v>2.06</v>
@@ -11411,7 +11411,7 @@
         <v>1.38</v>
       </c>
       <c r="T68">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="U68">
         <v>2.78</v>
@@ -11432,7 +11432,7 @@
         <v>3.1</v>
       </c>
       <c r="AA68">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB68">
         <v>1.8</v>
@@ -11450,7 +11450,7 @@
         <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="O71">
+        <v>3.6</v>
+      </c>
+      <c r="P71">
         <v>3.75</v>
-      </c>
-      <c r="P71">
-        <v>4</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -11903,16 +11903,16 @@
         <v>3.2</v>
       </c>
       <c r="U71">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="V71">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W71">
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y71">
         <v>1.22</v>
@@ -11936,7 +11936,7 @@
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG71">
         <v>2.05</v>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL71">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -10750,19 +10750,19 @@
         <v>6.97</v>
       </c>
       <c r="Q64">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R64">
         <v>2.05</v>
       </c>
       <c r="S64">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T64">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U64">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="V64">
         <v>1.25</v>
@@ -10771,7 +10771,7 @@
         <v>1.01</v>
       </c>
       <c r="X64">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y64">
         <v>1.56</v>
@@ -10783,13 +10783,13 @@
         <v>2.68</v>
       </c>
       <c r="AB64">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AC64">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AD64">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE64">
         <v>1.04</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK64">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11230,43 +11230,43 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
         <v>3.25</v>
       </c>
       <c r="P67">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="Q67">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="R67">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T67">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U67">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="V67">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y67">
         <v>1.32</v>
       </c>
       <c r="Z67">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AA67">
         <v>2.1</v>
@@ -11284,10 +11284,10 @@
         <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG67">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11568,13 +11568,13 @@
         <v>2.47</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="U69">
         <v>3.28</v>
@@ -11586,7 +11586,7 @@
         <v>1.04</v>
       </c>
       <c r="X69">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
         <v>1.44</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O70">
         <v>3.26</v>
       </c>
       <c r="P70">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -3255,7 +3255,7 @@
         <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S18">
         <v>1.41</v>
@@ -3264,7 +3264,7 @@
         <v>2.66</v>
       </c>
       <c r="U18">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="V18">
         <v>1.37</v>
@@ -3282,7 +3282,7 @@
         <v>3.3</v>
       </c>
       <c r="AA18">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB18">
         <v>1.87</v>
@@ -3291,7 +3291,7 @@
         <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
@@ -3904,10 +3904,10 @@
         <v>2.88</v>
       </c>
       <c r="Q22">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="R22">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="S22">
         <v>1.56</v>
@@ -3968,7 +3968,7 @@
         <v>1.38</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O23">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="P23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q23">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
         <v>1.04</v>
@@ -4094,7 +4094,7 @@
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA23">
         <v>1.89</v>
@@ -4103,19 +4103,19 @@
         <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
         <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG23">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,40 +4221,40 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O24">
         <v>4.2</v>
       </c>
       <c r="P24">
-        <v>5.3</v>
+        <v>6.12</v>
       </c>
       <c r="Q24">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="R24">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
         <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
         <v>4.75</v>
@@ -4263,13 +4263,13 @@
         <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC24">
         <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE24">
         <v>1.17</v>
@@ -4294,7 +4294,7 @@
         <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>4.2</v>
       </c>
       <c r="P25">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q25">
         <v>6.5</v>
@@ -4402,19 +4402,19 @@
         <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="U25">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.33</v>
@@ -4423,16 +4423,16 @@
         <v>3.3</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
         <v>1.04</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R26">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
         <v>2.91</v>
@@ -4574,7 +4574,7 @@
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4589,22 +4589,22 @@
         <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC26">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AD26">
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="R28">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
         <v>1.43</v>
@@ -4894,13 +4894,13 @@
         <v>2.53</v>
       </c>
       <c r="U28">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
         <v>1.02</v>
@@ -4909,28 +4909,28 @@
         <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AA28">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AB28">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC28">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5042,13 +5042,13 @@
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q29">
-        <v>4.6</v>
+        <v>4.86</v>
       </c>
       <c r="R29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S29">
         <v>1.5</v>
@@ -5066,34 +5066,34 @@
         <v>1</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
         <v>1.38</v>
       </c>
       <c r="Z29">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA29">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB29">
         <v>1.57</v>
       </c>
       <c r="AC29">
-        <v>4.1</v>
+        <v>4.21</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE29">
         <v>1.01</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG29">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,46 +5202,46 @@
         <v>1.63</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P30">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
       <c r="Q30">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R30">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U30">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="V30">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA30">
         <v>1.55</v>
       </c>
       <c r="AB30">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC30">
         <v>2.3</v>
@@ -5250,13 +5250,13 @@
         <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK30">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5528,61 +5528,61 @@
         <v>1.67</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="P32">
         <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
         <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U32">
         <v>2.99</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
         <v>3.08</v>
       </c>
       <c r="AA32">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB32">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC32">
-        <v>3.38</v>
+        <v>3.49</v>
       </c>
       <c r="AD32">
         <v>1.21</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
         <v>2</v>
       </c>
       <c r="AG32">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O37">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="P37">
-        <v>6.5</v>
+        <v>7.43</v>
       </c>
       <c r="Q37">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="S37">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
         <v>4</v>
@@ -6364,40 +6364,40 @@
         <v>2.12</v>
       </c>
       <c r="V37">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.35</v>
+        <v>5.41</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AB37">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AC37">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AD37">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE37">
         <v>1.25</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="O38">
-        <v>5.95</v>
+        <v>6.9</v>
       </c>
       <c r="P38">
         <v>11</v>
       </c>
       <c r="Q38">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R38">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="S38">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V38">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W38">
         <v>1.2</v>
@@ -6536,31 +6536,31 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>5.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB38">
         <v>2.66</v>
       </c>
       <c r="AC38">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD38">
         <v>1.75</v>
       </c>
       <c r="AE38">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF38">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG38">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6672,58 +6672,58 @@
         <v>3</v>
       </c>
       <c r="P39">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R39">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S39">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="T39">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="U39">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="V39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y39">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z39">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AA39">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AB39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC39">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE39">
         <v>1</v>
       </c>
       <c r="AF39">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AG39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O41">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q41">
         <v>2.14</v>
       </c>
       <c r="R41">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
         <v>1.22</v>
       </c>
       <c r="T41">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U41">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V41">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7028,19 +7028,19 @@
         <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB41">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC41">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD41">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE41">
         <v>1.28</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
         <v>2.1</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="O42">
         <v>3.25</v>
@@ -7170,13 +7170,13 @@
         <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T42">
         <v>2.69</v>
       </c>
       <c r="U42">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V42">
         <v>1.35</v>
@@ -7185,34 +7185,34 @@
         <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AA42">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB42">
         <v>1.76</v>
       </c>
       <c r="AC42">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD42">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
         <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O44">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="P44">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="Q44">
         <v>1.94</v>
@@ -7499,16 +7499,16 @@
         <v>1.14</v>
       </c>
       <c r="T44">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="U44">
         <v>1.85</v>
       </c>
       <c r="V44">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7532,7 +7532,7 @@
         <v>2.05</v>
       </c>
       <c r="AE44">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF44">
         <v>1.36</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O45">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P45">
         <v>4.4</v>
@@ -7656,43 +7656,43 @@
         <v>1.99</v>
       </c>
       <c r="R45">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T45">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="U45">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V45">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
         <v>6.5</v>
       </c>
       <c r="AA45">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB45">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AC45">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD45">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AE45">
         <v>1.33</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
         <v>3.6</v>
       </c>
       <c r="P46">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q46">
         <v>3.7</v>
@@ -7822,28 +7822,28 @@
         <v>2.51</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="AA46">
         <v>1.46</v>
@@ -7852,7 +7852,7 @@
         <v>2.38</v>
       </c>
       <c r="AC46">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD46">
         <v>1.59</v>
@@ -7864,7 +7864,7 @@
         <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="O47">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
         <v>7.8</v>
       </c>
       <c r="Q47">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="R47">
         <v>2.05</v>
       </c>
       <c r="S47">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T47">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U47">
         <v>3.1</v>
@@ -8009,19 +8009,19 @@
         <v>2.62</v>
       </c>
       <c r="AA47">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB47">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC47">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
         <v>2.33</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="P48">
         <v>2.03</v>
       </c>
       <c r="Q48">
-        <v>3.9</v>
+        <v>4.04</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="S48">
         <v>1.3</v>
@@ -8163,7 +8163,7 @@
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.17</v>
@@ -8187,10 +8187,10 @@
         <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="O49">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P49">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="Q49">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R49">
         <v>2.38</v>
@@ -8317,7 +8317,7 @@
         <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V49">
         <v>1.43</v>
@@ -8326,7 +8326,7 @@
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
@@ -8341,7 +8341,7 @@
         <v>1.98</v>
       </c>
       <c r="AC49">
-        <v>3.13</v>
+        <v>2.89</v>
       </c>
       <c r="AD49">
         <v>1.32</v>
@@ -8350,10 +8350,10 @@
         <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG49">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK49">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,49 +8459,49 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O50">
         <v>3</v>
       </c>
       <c r="P50">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="Q50">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R50">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="S50">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T50">
         <v>2.29</v>
       </c>
       <c r="U50">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="V50">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
         <v>1.45</v>
       </c>
       <c r="Z50">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AA50">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AB50">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC50">
         <v>4.45</v>
@@ -8510,13 +8510,13 @@
         <v>1.14</v>
       </c>
       <c r="AE50">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF50">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG50">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
         <v>1.63</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
         <v>1.83</v>
@@ -8637,10 +8637,10 @@
         <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U51">
         <v>2.81</v>
@@ -8661,10 +8661,10 @@
         <v>3.4</v>
       </c>
       <c r="AA51">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
         <v>3.24</v>
@@ -8673,7 +8673,7 @@
         <v>1.26</v>
       </c>
       <c r="AE51">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
         <v>1.75</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AK51">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,16 +8794,16 @@
         <v>4.08</v>
       </c>
       <c r="Q52">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R52">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
         <v>1.36</v>
       </c>
       <c r="T52">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="U52">
         <v>2.75</v>
@@ -8815,10 +8815,10 @@
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
         <v>3.65</v>
@@ -8833,13 +8833,13 @@
         <v>3.12</v>
       </c>
       <c r="AD52">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
         <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG52">
         <v>2</v>
@@ -9114,55 +9114,55 @@
         <v>4.8</v>
       </c>
       <c r="O54">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
         <v>1.55</v>
       </c>
       <c r="Q54">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="R54">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T54">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U54">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
         <v>1.29</v>
       </c>
       <c r="Z54">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA54">
         <v>1.84</v>
       </c>
       <c r="AB54">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC54">
         <v>2.92</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
         <v>1.85</v>
@@ -9280,31 +9280,31 @@
         <v>3.1</v>
       </c>
       <c r="P55">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S55">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T55">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U55">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="V55">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
         <v>1.31</v>
@@ -9319,7 +9319,7 @@
         <v>1.67</v>
       </c>
       <c r="AC55">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD55">
         <v>1.2</v>
@@ -9331,7 +9331,7 @@
         <v>1.81</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>3.1</v>
       </c>
       <c r="O56">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P56">
         <v>2.25</v>
@@ -9449,13 +9449,13 @@
         <v>4.03</v>
       </c>
       <c r="R56">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T56">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U56">
         <v>3.2</v>
@@ -9473,25 +9473,25 @@
         <v>1.4</v>
       </c>
       <c r="Z56">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA56">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB56">
         <v>1.56</v>
       </c>
       <c r="AC56">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD56">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE56">
         <v>1.02</v>
       </c>
       <c r="AF56">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG56">
         <v>1.77</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>3.2</v>
       </c>
       <c r="Q57">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R57">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S57">
         <v>1.49</v>
@@ -9621,40 +9621,40 @@
         <v>2.34</v>
       </c>
       <c r="U57">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="V57">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W57">
         <v>1</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
         <v>1.37</v>
       </c>
       <c r="Z57">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AA57">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB57">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC57">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD57">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE57">
         <v>1.01</v>
       </c>
       <c r="AF57">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG57">
         <v>1.73</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O58">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q58">
         <v>3.52</v>
@@ -9787,25 +9787,25 @@
         <v>3.34</v>
       </c>
       <c r="V58">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W58">
         <v>1.01</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z58">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AA58">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AB58">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC58">
         <v>4.4</v>
@@ -9817,10 +9817,10 @@
         <v>1.01</v>
       </c>
       <c r="AF58">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AG58">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="O60">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="P60">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q60">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="R60">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U60">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V60">
         <v>1.73</v>
       </c>
       <c r="W60">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10128,25 +10128,25 @@
         <v>5.9</v>
       </c>
       <c r="AA60">
+        <v>1.33</v>
+      </c>
+      <c r="AB60">
+        <v>2.8</v>
+      </c>
+      <c r="AC60">
+        <v>2.01</v>
+      </c>
+      <c r="AD60">
+        <v>1.88</v>
+      </c>
+      <c r="AE60">
         <v>1.29</v>
       </c>
-      <c r="AB60">
-        <v>3.15</v>
-      </c>
-      <c r="AC60">
-        <v>1.9</v>
-      </c>
-      <c r="AD60">
-        <v>1.92</v>
-      </c>
-      <c r="AE60">
-        <v>1.3</v>
-      </c>
       <c r="AF60">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG60">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="AK60">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,58 +10258,58 @@
         <v>3.7</v>
       </c>
       <c r="P61">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q61">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R61">
         <v>2.15</v>
       </c>
       <c r="S61">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T61">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U61">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="V61">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W61">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z61">
-        <v>3.3</v>
+        <v>3.69</v>
       </c>
       <c r="AA61">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB61">
         <v>1.82</v>
       </c>
       <c r="AC61">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="AD61">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE61">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF61">
         <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,55 +10418,55 @@
         <v>4.16</v>
       </c>
       <c r="O62">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P62">
         <v>1.79</v>
       </c>
       <c r="Q62">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U62">
         <v>2.68</v>
       </c>
       <c r="V62">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W62">
         <v>1.09</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
         <v>3.7</v>
       </c>
       <c r="AA62">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC62">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF62">
         <v>1.62</v>
@@ -10488,7 +10488,7 @@
         <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,58 +10578,58 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="O63">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="P63">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q63">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R63">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="S63">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="U63">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V63">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="W63">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA63">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC63">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AD63">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AE63">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF63">
         <v>1.85</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AK63">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O65">
         <v>3.25</v>
@@ -10913,7 +10913,7 @@
         <v>3.05</v>
       </c>
       <c r="Q65">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
         <v>2.25</v>
@@ -10931,7 +10931,7 @@
         <v>1.42</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
         <v>1.04</v>
@@ -10940,7 +10940,7 @@
         <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA65">
         <v>1.85</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="Q68">
         <v>2.55</v>
       </c>
       <c r="R68">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U68">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V68">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y68">
         <v>1.28</v>
       </c>
       <c r="Z68">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AA68">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB68">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC68">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD68">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF68">
         <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11894,13 +11894,13 @@
         <v>2.3</v>
       </c>
       <c r="R71">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T71">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U71">
         <v>2.39</v>
@@ -11915,22 +11915,22 @@
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="AA71">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB71">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC71">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE71">
         <v>1.11</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1290,10 +1290,10 @@
         <v>3.61</v>
       </c>
       <c r="O6">
-        <v>4.01</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
         <v>4.3</v>
@@ -1305,7 +1305,7 @@
         <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
         <v>2.63</v>
@@ -1329,13 +1329,13 @@
         <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
         <v>1.13</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.6</v>
+        <v>5.06</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U7">
         <v>2.11</v>
@@ -1489,22 +1489,22 @@
         <v>5.4</v>
       </c>
       <c r="AA7">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AB7">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AC7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD7">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AG7">
         <v>2.35</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G9">
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U12">
         <v>2.75</v>
@@ -2298,22 +2298,22 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
         <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
         <v>1.78</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
@@ -2338,7 +2338,7 @@
         <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.41</v>
+        <v>3.9</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="O17">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="P17">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="P22">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="Q22">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R22">
         <v>1.86</v>
       </c>
       <c r="S22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T22">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U22">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
         <v>1</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
         <v>1.52</v>
       </c>
       <c r="Z22">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AA22">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AB22">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC22">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AD22">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AG22">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.38</v>
       </c>
       <c r="AK22">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="O24">
         <v>4.2</v>
       </c>
       <c r="P24">
-        <v>6.12</v>
+        <v>5.5</v>
       </c>
       <c r="Q24">
         <v>1.98</v>
       </c>
       <c r="R24">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="S24">
         <v>1.24</v>
@@ -4251,7 +4251,7 @@
         <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.15</v>
@@ -4260,25 +4260,25 @@
         <v>4.75</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
         <v>2.28</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD24">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
         <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK24">
         <v>2.63</v>
@@ -5697,19 +5697,19 @@
         <v>2.15</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="U33">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V33">
         <v>1.39</v>
@@ -5718,28 +5718,28 @@
         <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
         <v>1.89</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD33">
         <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
         <v>1.66</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK33">
         <v>1.33</v>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O34">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
         <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
         <v>1.5</v>
@@ -5881,34 +5881,34 @@
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
         <v>2.17</v>
       </c>
       <c r="AC34">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD34">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,37 +6014,37 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>5.31</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W35">
         <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.11</v>
@@ -6053,22 +6053,22 @@
         <v>4.95</v>
       </c>
       <c r="AA35">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AC35">
         <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG35">
         <v>2.2</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
         <v>2.38</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O36">
         <v>3.6</v>
       </c>
       <c r="P36">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="Q36">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="R36">
         <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="U36">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
         <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB36">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AC36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD36">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF36">
         <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>1.46</v>
       </c>
       <c r="R40">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S40">
         <v>1.14</v>
@@ -6853,7 +6853,7 @@
         <v>1.74</v>
       </c>
       <c r="V40">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W40">
         <v>1.25</v>
@@ -6862,10 +6862,10 @@
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z40">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>1.27</v>
@@ -6883,10 +6883,10 @@
         <v>1.38</v>
       </c>
       <c r="AF40">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AG40">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK40">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O44">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>4.69</v>
+        <v>4.4</v>
       </c>
       <c r="Q44">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R44">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="S44">
         <v>1.14</v>
       </c>
       <c r="T44">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U44">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="V44">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="W44">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z44">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA44">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AB44">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="AC44">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD44">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AE44">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AF44">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG44">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="P45">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="Q45">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R45">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="S45">
         <v>1.14</v>
       </c>
       <c r="T45">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U45">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V45">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="W45">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z45">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA45">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AB45">
-        <v>2.95</v>
+        <v>3.41</v>
       </c>
       <c r="AC45">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AD45">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AE45">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AF45">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG45">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8142,10 +8142,10 @@
         <v>2.03</v>
       </c>
       <c r="Q48">
-        <v>4.04</v>
+        <v>3.35</v>
       </c>
       <c r="R48">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="S48">
         <v>1.3</v>
@@ -8154,10 +8154,10 @@
         <v>3.25</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
         <v>1.06</v>
@@ -8169,22 +8169,22 @@
         <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA48">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC48">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AD48">
         <v>1.38</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
         <v>1.58</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="O49">
         <v>4.5</v>
@@ -8305,19 +8305,19 @@
         <v>6.51</v>
       </c>
       <c r="Q49">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R49">
         <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U49">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="V49">
         <v>1.43</v>
@@ -8335,7 +8335,7 @@
         <v>3.52</v>
       </c>
       <c r="AA49">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB49">
         <v>1.98</v>
@@ -8344,16 +8344,16 @@
         <v>2.89</v>
       </c>
       <c r="AD49">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
         <v>1.94</v>
       </c>
       <c r="AG49">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
         <v>2.71</v>
@@ -8948,52 +8948,52 @@
         </is>
       </c>
       <c r="N53">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O53">
         <v>4.3</v>
       </c>
       <c r="P53">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q53">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
       <c r="R53">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="U53">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="V53">
         <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA53">
         <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
         <v>1.35</v>
@@ -9002,10 +9002,10 @@
         <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG53">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9123,13 +9123,13 @@
         <v>4.84</v>
       </c>
       <c r="R54">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S54">
         <v>1.37</v>
       </c>
       <c r="T54">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U54">
         <v>2.75</v>
@@ -9153,22 +9153,22 @@
         <v>1.84</v>
       </c>
       <c r="AB54">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC54">
         <v>2.92</v>
       </c>
       <c r="AD54">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF54">
         <v>1.85</v>
       </c>
       <c r="AG54">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9929,16 +9929,16 @@
         <v>1.9</v>
       </c>
       <c r="O59">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P59">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="Q59">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="R59">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="S59">
         <v>1.14</v>
@@ -9947,10 +9947,10 @@
         <v>5</v>
       </c>
       <c r="U59">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V59">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="W59">
         <v>1.25</v>
@@ -9959,31 +9959,31 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z59">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="AA59">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AB59">
         <v>3.42</v>
       </c>
       <c r="AC59">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AD59">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AE59">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AF59">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AG59">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK59">
         <v>1.82</v>
@@ -10089,43 +10089,43 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="O60">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="P60">
         <v>12</v>
       </c>
       <c r="Q60">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z60">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA60">
         <v>1.33</v>
@@ -10140,10 +10140,10 @@
         <v>1.88</v>
       </c>
       <c r="AE60">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG60">
         <v>1.71</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK60">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,43 +10261,43 @@
         <v>4.5</v>
       </c>
       <c r="Q61">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U61">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V61">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W61">
+        <v>1.05</v>
+      </c>
+      <c r="X61">
         <v>1.06</v>
       </c>
-      <c r="X61">
-        <v>1</v>
-      </c>
       <c r="Y61">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z61">
         <v>3.69</v>
       </c>
       <c r="AA61">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AB61">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AC61">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AD61">
         <v>1.29</v>
@@ -10306,10 +10306,10 @@
         <v>1.08</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG61">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>3.3</v>
       </c>
       <c r="P64">
-        <v>6.97</v>
+        <v>5.3</v>
       </c>
       <c r="Q64">
         <v>2.24</v>
@@ -10765,7 +10765,7 @@
         <v>3.7</v>
       </c>
       <c r="V64">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W64">
         <v>1.01</v>
@@ -10777,16 +10777,16 @@
         <v>1.56</v>
       </c>
       <c r="Z64">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AA64">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AB64">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AC64">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD64">
         <v>1.14</v>
@@ -10795,7 +10795,7 @@
         <v>1.04</v>
       </c>
       <c r="AF64">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AG64">
         <v>1.5</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
         <v>3.25</v>
@@ -10916,7 +10916,7 @@
         <v>2.8</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
         <v>1.33</v>
@@ -10925,10 +10925,10 @@
         <v>2.85</v>
       </c>
       <c r="U65">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V65">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W65">
         <v>1.09</v>
@@ -10940,10 +10940,10 @@
         <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA65">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB65">
         <v>1.9</v>
@@ -10955,7 +10955,7 @@
         <v>1.31</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF65">
         <v>1.65</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="O66">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q66">
         <v>2.29</v>
@@ -11085,10 +11085,10 @@
         <v>1.43</v>
       </c>
       <c r="T66">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U66">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="V66">
         <v>1.33</v>
@@ -11097,10 +11097,10 @@
         <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
         <v>2.92</v>
@@ -11115,13 +11115,13 @@
         <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AG66">
         <v>1.73</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK66">
         <v>2.06</v>
@@ -11233,40 +11233,40 @@
         <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="Q67">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
         <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T67">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U67">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="V67">
+        <v>1.32</v>
+      </c>
+      <c r="W67">
+        <v>1.04</v>
+      </c>
+      <c r="X67">
+        <v>1.08</v>
+      </c>
+      <c r="Y67">
         <v>1.36</v>
       </c>
-      <c r="W67">
-        <v>1.07</v>
-      </c>
-      <c r="X67">
-        <v>1.06</v>
-      </c>
-      <c r="Y67">
-        <v>1.32</v>
-      </c>
       <c r="Z67">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA67">
         <v>2.1</v>
@@ -11275,19 +11275,19 @@
         <v>1.73</v>
       </c>
       <c r="AC67">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD67">
         <v>1.22</v>
       </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P68">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q68">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R68">
         <v>2.1</v>
@@ -11414,7 +11414,7 @@
         <v>2.77</v>
       </c>
       <c r="U68">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V68">
         <v>1.4</v>
@@ -11426,10 +11426,10 @@
         <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA68">
         <v>1.87</v>
@@ -11438,7 +11438,7 @@
         <v>1.83</v>
       </c>
       <c r="AC68">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD68">
         <v>1.28</v>
@@ -11447,7 +11447,7 @@
         <v>1.07</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG68">
         <v>1.9</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
         <v>4.2</v>
       </c>
       <c r="Q69">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R69">
         <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T69">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="U69">
         <v>3.28</v>
@@ -11592,10 +11592,10 @@
         <v>1.44</v>
       </c>
       <c r="Z69">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AA69">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="AB69">
         <v>1.58</v>
@@ -11613,7 +11613,7 @@
         <v>2</v>
       </c>
       <c r="AG69">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
         <v>1.87</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.26</v>
+        <v>3.42</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11891,46 +11891,46 @@
         <v>3.75</v>
       </c>
       <c r="Q71">
+        <v>2.27</v>
+      </c>
+      <c r="R71">
         <v>2.3</v>
       </c>
-      <c r="R71">
-        <v>2.25</v>
-      </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T71">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U71">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V71">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W71">
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z71">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="AA71">
         <v>1.76</v>
       </c>
       <c r="AB71">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC71">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AD71">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
         <v>1.11</v>
@@ -11939,7 +11939,7 @@
         <v>1.68</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
         <v>4.3</v>
@@ -1308,43 +1308,43 @@
         <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB6">
         <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -5691,43 +5691,43 @@
         <v>2.9</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
         <v>2.15</v>
       </c>
       <c r="Q33">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="U33">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V33">
         <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB33">
         <v>1.89</v>
@@ -5736,16 +5736,16 @@
         <v>3.04</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.66</v>
       </c>
       <c r="AG33">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AK33">
         <v>1.33</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q44">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="R44">
-        <v>2.78</v>
+        <v>2.61</v>
       </c>
       <c r="S44">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T44">
         <v>4.1</v>
       </c>
       <c r="U44">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V44">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7520,25 +7520,25 @@
         <v>6.5</v>
       </c>
       <c r="AA44">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AB44">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AC44">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD44">
         <v>1.82</v>
       </c>
       <c r="AE44">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
         <v>1.41</v>
       </c>
       <c r="AG44">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,55 +7644,55 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O45">
         <v>4.65</v>
       </c>
       <c r="P45">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="Q45">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R45">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="S45">
         <v>1.14</v>
       </c>
       <c r="T45">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="U45">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V45">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z45">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AA45">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB45">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="AC45">
         <v>1.75</v>
       </c>
       <c r="AD45">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE45">
         <v>1.45</v>
@@ -7701,7 +7701,7 @@
         <v>1.36</v>
       </c>
       <c r="AG45">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O53">
-        <v>4.3</v>
+        <v>1.12</v>
       </c>
       <c r="P53">
         <v>1.5</v>
       </c>
       <c r="Q53">
-        <v>6.64</v>
+        <v>6.76</v>
       </c>
       <c r="R53">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="U53">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V53">
         <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="AA53">
         <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC53">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG53">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -11722,10 +11722,10 @@
         <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="P70">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="Q70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1459,19 +1459,19 @@
         <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="R7">
         <v>2.4</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
         <v>1.63</v>
@@ -1483,10 +1483,10 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA7">
         <v>1.41</v>
@@ -1501,7 +1501,7 @@
         <v>1.64</v>
       </c>
       <c r="AE7">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
         <v>1.48</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="O22">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="P22">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="Q22">
         <v>3.18</v>
@@ -3928,10 +3928,10 @@
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z22">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AA22">
         <v>2.62</v>
@@ -3952,7 +3952,7 @@
         <v>2.13</v>
       </c>
       <c r="AG22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -5857,13 +5857,13 @@
         <v>3.7</v>
       </c>
       <c r="P34">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S34">
         <v>1.25</v>
@@ -5872,7 +5872,7 @@
         <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V34">
         <v>1.5</v>
@@ -5881,50 +5881,50 @@
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="AA34">
         <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC34">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
       </c>
       <c r="AG34">
+        <v>2.08</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.18</v>
+      </c>
+      <c r="AK34">
         <v>2.15</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.23</v>
-      </c>
-      <c r="AK34">
-        <v>2.19</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P35">
         <v>5.31</v>
@@ -6026,7 +6026,7 @@
         <v>2</v>
       </c>
       <c r="R35">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S35">
         <v>1.22</v>
@@ -6035,43 +6035,43 @@
         <v>3.66</v>
       </c>
       <c r="U35">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
         <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA35">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB35">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AC35">
         <v>2.35</v>
       </c>
       <c r="AD35">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="Q36">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
         <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U36">
         <v>2.1</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6216,10 +6216,10 @@
         <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AC36">
         <v>2.3</v>
@@ -6228,7 +6228,7 @@
         <v>1.6</v>
       </c>
       <c r="AE36">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
         <v>1.44</v>
@@ -6343,10 +6343,10 @@
         <v>1.36</v>
       </c>
       <c r="O37">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="P37">
-        <v>7.43</v>
+        <v>7.35</v>
       </c>
       <c r="Q37">
         <v>1.8</v>
@@ -6361,43 +6361,43 @@
         <v>4</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>5.41</v>
+        <v>5.8</v>
       </c>
       <c r="AA37">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB37">
         <v>2.63</v>
       </c>
       <c r="AC37">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="O42">
         <v>3.25</v>
       </c>
       <c r="P42">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q42">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="R42">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
         <v>1.42</v>
@@ -7176,10 +7176,10 @@
         <v>2.69</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
         <v>1.05</v>
@@ -7188,31 +7188,31 @@
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z42">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA42">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AB42">
         <v>1.76</v>
       </c>
       <c r="AC42">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD42">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
         <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="P43">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA43">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
         <v>1.72</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G44">
@@ -7484,61 +7484,61 @@
         <v>1.55</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P44">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="Q44">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R44">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="S44">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T44">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="U44">
+        <v>1.8</v>
+      </c>
+      <c r="V44">
         <v>1.91</v>
       </c>
-      <c r="V44">
-        <v>1.85</v>
-      </c>
       <c r="W44">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z44">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA44">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AB44">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AC44">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AD44">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AE44">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF44">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG44">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G45">
@@ -7647,61 +7647,61 @@
         <v>1.55</v>
       </c>
       <c r="O45">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="Q45">
+        <v>2.01</v>
+      </c>
+      <c r="R45">
+        <v>2.61</v>
+      </c>
+      <c r="S45">
+        <v>1.18</v>
+      </c>
+      <c r="T45">
+        <v>4.1</v>
+      </c>
+      <c r="U45">
         <v>1.91</v>
       </c>
-      <c r="R45">
-        <v>2.8</v>
-      </c>
-      <c r="S45">
-        <v>1.14</v>
-      </c>
-      <c r="T45">
-        <v>5.2</v>
-      </c>
-      <c r="U45">
-        <v>1.8</v>
-      </c>
       <c r="V45">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W45">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA45">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AB45">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AC45">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AD45">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AE45">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG45">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>3</v>
       </c>
       <c r="P50">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R50">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S50">
         <v>1.52</v>
@@ -8489,34 +8489,34 @@
         <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
         <v>1.45</v>
       </c>
       <c r="Z50">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AA50">
         <v>2.34</v>
       </c>
       <c r="AB50">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC50">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AD50">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF50">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG50">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,16 +8631,16 @@
         <v>1.83</v>
       </c>
       <c r="Q51">
-        <v>3.92</v>
+        <v>4.65</v>
       </c>
       <c r="R51">
         <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U51">
         <v>2.81</v>
@@ -8652,28 +8652,28 @@
         <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
         <v>3.4</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB51">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC51">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
         <v>1.75</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O55">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P55">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R55">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="S55">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T55">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U55">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V55">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W55">
         <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="AA55">
         <v>2.2</v>
       </c>
       <c r="AB55">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AC55">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AD55">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG55">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>2.9</v>
+      </c>
+      <c r="O56">
         <v>3.1</v>
       </c>
-      <c r="O56">
-        <v>2.85</v>
-      </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
-        <v>4.03</v>
+        <v>3.44</v>
       </c>
       <c r="R56">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T56">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U56">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="V56">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W56">
         <v>1.02</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z56">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AA56">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AB56">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC56">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD56">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG56">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
+        <v>1.25</v>
+      </c>
+      <c r="AK56">
         <v>1.33</v>
-      </c>
-      <c r="AK56">
-        <v>1.29</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>2.15</v>
       </c>
       <c r="O57">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P57">
         <v>3.2</v>
@@ -9612,16 +9612,16 @@
         <v>2.8</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S57">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T57">
         <v>2.34</v>
       </c>
       <c r="U57">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V57">
         <v>1.26</v>
@@ -9630,31 +9630,31 @@
         <v>1</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z57">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AA57">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB57">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC57">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD57">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE57">
         <v>1.01</v>
       </c>
       <c r="AF57">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG57">
         <v>1.73</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P58">
         <v>2.63</v>
       </c>
       <c r="Q58">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R58">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S58">
         <v>1.5</v>
@@ -9784,10 +9784,10 @@
         <v>2.31</v>
       </c>
       <c r="U58">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V58">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W58">
         <v>1.01</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK58">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10092,61 +10092,61 @@
         <v>1.16</v>
       </c>
       <c r="O60">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="P60">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q60">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R60">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S60">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="U60">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V60">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W60">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
         <v>2.8</v>
       </c>
       <c r="AC60">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AD60">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AE60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF60">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG60">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK60">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,61 +10255,61 @@
         <v>1.75</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R61">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S61">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T61">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U61">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V61">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z61">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="AA61">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB61">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC61">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="AD61">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF61">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK61">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2298,10 +2298,10 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
         <v>1.91</v>
@@ -2322,7 +2322,7 @@
         <v>1.71</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="O13">
         <v>3.4</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O18">
         <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18">
-        <v>4.2</v>
+        <v>3.43</v>
       </c>
       <c r="R18">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="U18">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA18">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB18">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG18">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.55</v>
+        <v>5.03</v>
       </c>
       <c r="O23">
         <v>3.92</v>
@@ -4067,55 +4067,55 @@
         <v>1.63</v>
       </c>
       <c r="Q23">
-        <v>5.31</v>
+        <v>4.7</v>
       </c>
       <c r="R23">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
         <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AB23">
         <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
         <v>1.14</v>
@@ -4224,25 +4224,25 @@
         <v>1.38</v>
       </c>
       <c r="O24">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>5.5</v>
+        <v>6.12</v>
       </c>
       <c r="Q24">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="R24">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
         <v>1.58</v>
@@ -4251,34 +4251,34 @@
         <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
         <v>4.75</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD24">
         <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4390,22 +4390,22 @@
         <v>4.2</v>
       </c>
       <c r="P25">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q25">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="U25">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="V25">
         <v>1.38</v>
@@ -4414,7 +4414,7 @@
         <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
         <v>1.33</v>
@@ -4423,22 +4423,22 @@
         <v>3.3</v>
       </c>
       <c r="AA25">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
         <v>3.6</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG25">
         <v>1.62</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
+        <v>2.78</v>
+      </c>
+      <c r="Q26">
         <v>3.1</v>
       </c>
-      <c r="P26">
-        <v>2.62</v>
-      </c>
-      <c r="Q26">
-        <v>3.05</v>
-      </c>
       <c r="R26">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S26">
         <v>1.41</v>
@@ -4568,7 +4568,7 @@
         <v>2.7</v>
       </c>
       <c r="U26">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V26">
         <v>1.33</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O28">
         <v>3.4</v>
@@ -4882,10 +4882,10 @@
         <v>4.33</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.43</v>
@@ -4894,13 +4894,13 @@
         <v>2.53</v>
       </c>
       <c r="U28">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.02</v>
@@ -4909,28 +4909,28 @@
         <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA28">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC28">
         <v>3.5</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
         <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>1.9</v>
       </c>
       <c r="Q29">
-        <v>4.86</v>
+        <v>4.4</v>
       </c>
       <c r="R29">
         <v>2</v>
@@ -5066,34 +5066,34 @@
         <v>1</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y29">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z29">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AA29">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB29">
         <v>1.57</v>
       </c>
       <c r="AC29">
-        <v>4.21</v>
+        <v>3.95</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG29">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,19 +5205,19 @@
         <v>3.95</v>
       </c>
       <c r="P30">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R30">
         <v>2.4</v>
       </c>
       <c r="S30">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
         <v>1.92</v>
@@ -5226,7 +5226,7 @@
         <v>1.47</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5235,16 +5235,16 @@
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA30">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AB30">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AD30">
         <v>1.5</v>
@@ -5256,7 +5256,7 @@
         <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O32">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S32">
         <v>1.45</v>
@@ -5549,40 +5549,40 @@
         <v>2.99</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y32">
         <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA32">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC32">
-        <v>3.49</v>
+        <v>4.2</v>
       </c>
       <c r="AD32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
         <v>2</v>
       </c>
       <c r="AG32">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>4.8</v>
+        <v>4.35</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
@@ -6044,13 +6044,13 @@
         <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA35">
         <v>1.47</v>
@@ -6198,7 +6198,7 @@
         <v>3.75</v>
       </c>
       <c r="U36">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V36">
         <v>1.62</v>
@@ -6219,7 +6219,7 @@
         <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AC36">
         <v>2.3</v>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="O38">
         <v>6.9</v>
       </c>
       <c r="P38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q38">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R38">
         <v>2.76</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
         <v>2.07</v>
@@ -6536,28 +6536,28 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>6.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA38">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB38">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC38">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD38">
         <v>1.75</v>
       </c>
       <c r="AE38">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF38">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG38">
         <v>1.65</v>
@@ -6576,7 +6576,7 @@
         <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O39">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="P39">
         <v>3.84</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="S39">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T39">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U39">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="V39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W39">
         <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Y39">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Z39">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AA39">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AB39">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC39">
         <v>7</v>
       </c>
       <c r="AD39">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE39">
         <v>1</v>
       </c>
       <c r="AF39">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AG39">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>15</v>
       </c>
       <c r="Q40">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="R40">
         <v>3.4</v>
@@ -6853,7 +6853,7 @@
         <v>1.74</v>
       </c>
       <c r="V40">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W40">
         <v>1.25</v>
@@ -6862,22 +6862,22 @@
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AB40">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AC40">
         <v>1.72</v>
       </c>
       <c r="AD40">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AE40">
         <v>1.38</v>
@@ -6998,13 +6998,13 @@
         <v>3.9</v>
       </c>
       <c r="P41">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q41">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S41">
         <v>1.22</v>
@@ -7013,10 +7013,10 @@
         <v>3.9</v>
       </c>
       <c r="U41">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V41">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W41">
         <v>1.17</v>
@@ -7028,16 +7028,16 @@
         <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA41">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB41">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC41">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AD41">
         <v>1.65</v>
@@ -7049,7 +7049,7 @@
         <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>1.91</v>
       </c>
       <c r="R44">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S44">
         <v>1.14</v>
@@ -7517,7 +7517,7 @@
         <v>1.03</v>
       </c>
       <c r="Z44">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA44">
         <v>1.25</v>
@@ -7526,10 +7526,10 @@
         <v>3.28</v>
       </c>
       <c r="AC44">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AD44">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AE44">
         <v>1.45</v>
@@ -7683,16 +7683,16 @@
         <v>6.5</v>
       </c>
       <c r="AA45">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AB45">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AC45">
         <v>1.89</v>
       </c>
       <c r="AD45">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AE45">
         <v>1.3</v>
@@ -7807,43 +7807,43 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q46">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R46">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U46">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
         <v>1.46</v>
@@ -7852,7 +7852,7 @@
         <v>2.38</v>
       </c>
       <c r="AC46">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD46">
         <v>1.59</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7976,28 +7976,28 @@
         <v>3.6</v>
       </c>
       <c r="P47">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q47">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S47">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T47">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U47">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="V47">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
         <v>1.05</v>
@@ -8006,28 +8006,28 @@
         <v>1.4</v>
       </c>
       <c r="Z47">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA47">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC47">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AG47">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AK47">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,77 +8136,77 @@
         <v>3.48</v>
       </c>
       <c r="O48">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Q48">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
+        <v>1.31</v>
+      </c>
+      <c r="T48">
+        <v>3.15</v>
+      </c>
+      <c r="U48">
+        <v>2.5</v>
+      </c>
+      <c r="V48">
+        <v>1.47</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.04</v>
+      </c>
+      <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>4.2</v>
+      </c>
+      <c r="AA48">
+        <v>1.67</v>
+      </c>
+      <c r="AB48">
+        <v>2.2</v>
+      </c>
+      <c r="AC48">
+        <v>2.62</v>
+      </c>
+      <c r="AD48">
+        <v>1.45</v>
+      </c>
+      <c r="AE48">
+        <v>1.18</v>
+      </c>
+      <c r="AF48">
+        <v>1.57</v>
+      </c>
+      <c r="AG48">
+        <v>2.25</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.3</v>
       </c>
-      <c r="T48">
-        <v>3.25</v>
-      </c>
-      <c r="U48">
-        <v>2.4</v>
-      </c>
-      <c r="V48">
-        <v>1.5</v>
-      </c>
-      <c r="W48">
-        <v>1.06</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.17</v>
-      </c>
-      <c r="Z48">
-        <v>4.05</v>
-      </c>
-      <c r="AA48">
-        <v>1.76</v>
-      </c>
-      <c r="AB48">
-        <v>2.16</v>
-      </c>
-      <c r="AC48">
-        <v>2.64</v>
-      </c>
-      <c r="AD48">
-        <v>1.38</v>
-      </c>
-      <c r="AE48">
-        <v>1.11</v>
-      </c>
-      <c r="AF48">
-        <v>1.58</v>
-      </c>
-      <c r="AG48">
-        <v>2.23</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.81</v>
-      </c>
       <c r="AK48">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="O49">
         <v>4.5</v>
@@ -8308,16 +8308,16 @@
         <v>1.95</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
         <v>1.43</v>
@@ -8326,34 +8326,34 @@
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z49">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="AA49">
         <v>1.88</v>
       </c>
       <c r="AB49">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AD49">
         <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG49">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK49">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8788,58 +8788,58 @@
         <v>1.91</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="Q52">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
         <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AA52">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB52">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC52">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
         <v>2</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,22 +8951,22 @@
         <v>6</v>
       </c>
       <c r="O53">
-        <v>1.12</v>
+        <v>4.33</v>
       </c>
       <c r="P53">
         <v>1.5</v>
       </c>
       <c r="Q53">
-        <v>6.76</v>
+        <v>6.56</v>
       </c>
       <c r="R53">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T53">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U53">
         <v>2.7</v>
@@ -8981,22 +8981,22 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AA53">
         <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC53">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
         <v>1.09</v>
@@ -9111,34 +9111,34 @@
         </is>
       </c>
       <c r="N54">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P54">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q54">
         <v>4.84</v>
       </c>
       <c r="R54">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T54">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U54">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V54">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
         <v>1.04</v>
@@ -9147,22 +9147,22 @@
         <v>1.29</v>
       </c>
       <c r="Z54">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA54">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC54">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AD54">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE54">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
         <v>1.85</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P55">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q55">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="R55">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S55">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T55">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="U55">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V55">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
+        <v>1.47</v>
+      </c>
+      <c r="Z55">
+        <v>2.44</v>
+      </c>
+      <c r="AA55">
+        <v>2.38</v>
+      </c>
+      <c r="AB55">
+        <v>1.5</v>
+      </c>
+      <c r="AC55">
+        <v>4.4</v>
+      </c>
+      <c r="AD55">
+        <v>1.14</v>
+      </c>
+      <c r="AE55">
+        <v>1.01</v>
+      </c>
+      <c r="AF55">
+        <v>1.99</v>
+      </c>
+      <c r="AG55">
+        <v>1.7</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>1.36</v>
+      </c>
+      <c r="AK55">
         <v>1.4</v>
-      </c>
-      <c r="Z55">
-        <v>2.68</v>
-      </c>
-      <c r="AA55">
-        <v>2.2</v>
-      </c>
-      <c r="AB55">
-        <v>1.56</v>
-      </c>
-      <c r="AC55">
-        <v>4</v>
-      </c>
-      <c r="AD55">
-        <v>1.25</v>
-      </c>
-      <c r="AE55">
-        <v>1.02</v>
-      </c>
-      <c r="AF55">
-        <v>1.93</v>
-      </c>
-      <c r="AG55">
-        <v>1.78</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.3</v>
-      </c>
-      <c r="AK55">
-        <v>1.29</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O56">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P56">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S56">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T56">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U56">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V56">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W56">
         <v>1.02</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z56">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="AA56">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB56">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AC56">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE56">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF56">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG56">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="O57">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="R57">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T57">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U57">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="V57">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W57">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z57">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AA57">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AB57">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC57">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD57">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE57">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF57">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG57">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="O58">
         <v>2.9</v>
       </c>
       <c r="P58">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="Q58">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R58">
         <v>1.95</v>
@@ -9781,46 +9781,46 @@
         <v>1.5</v>
       </c>
       <c r="T58">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="U58">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V58">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W58">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X58">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z58">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="AA58">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AB58">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AC58">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD58">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE58">
         <v>1.01</v>
       </c>
       <c r="AF58">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AG58">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O59">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P59">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -9941,16 +9941,16 @@
         <v>2.56</v>
       </c>
       <c r="S59">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U59">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="V59">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="W59">
         <v>1.25</v>
@@ -9959,31 +9959,31 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z59">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AB59">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AC59">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AD59">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AE59">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF59">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AG59">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>1.16</v>
       </c>
       <c r="O60">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="P60">
         <v>13</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z61">
         <v>3.3</v>
@@ -10421,10 +10421,10 @@
         <v>3.8</v>
       </c>
       <c r="P62">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q62">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="R62">
         <v>2.29</v>
@@ -10433,16 +10433,16 @@
         <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="V62">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W62">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.02</v>
@@ -10451,28 +10451,28 @@
         <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="AA62">
         <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD62">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
         <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG62">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,31 +10578,31 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O63">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="P63">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q63">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R63">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S63">
         <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="U63">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="V63">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="W63">
         <v>1.24</v>
@@ -10611,32 +10611,32 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z63">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA63">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB63">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="AC63">
+        <v>1.85</v>
+      </c>
+      <c r="AD63">
+        <v>1.91</v>
+      </c>
+      <c r="AE63">
+        <v>1.42</v>
+      </c>
+      <c r="AF63">
+        <v>1.97</v>
+      </c>
+      <c r="AG63">
         <v>1.83</v>
       </c>
-      <c r="AD63">
-        <v>1.92</v>
-      </c>
-      <c r="AE63">
-        <v>1.39</v>
-      </c>
-      <c r="AF63">
-        <v>1.85</v>
-      </c>
-      <c r="AG63">
-        <v>1.91</v>
-      </c>
       <c r="AH63" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK63">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q66">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S66">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="U66">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V66">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W66">
         <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z66">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA66">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB66">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC66">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD66">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
+        <v>1.95</v>
+      </c>
+      <c r="AG66">
+        <v>1.75</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.16</v>
+      </c>
+      <c r="AK66">
         <v>2</v>
-      </c>
-      <c r="AG66">
-        <v>1.73</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.27</v>
-      </c>
-      <c r="AK66">
-        <v>2.06</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O67">
         <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="Q67">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T67">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="U67">
         <v>3.1</v>
@@ -11263,31 +11263,31 @@
         <v>1.08</v>
       </c>
       <c r="Y67">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z67">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA67">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB67">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC67">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD67">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE67">
         <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG67">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q68">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R68">
         <v>2.1</v>
@@ -11411,46 +11411,46 @@
         <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U68">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W68">
         <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z68">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA68">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC68">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD68">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
         <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="O70">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="Q70">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O11">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>4.4</v>
+        <v>4.54</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="O17">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="P17">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3249,19 +3249,19 @@
         <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q18">
         <v>3.43</v>
       </c>
       <c r="R18">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.36</v>
       </c>
       <c r="T18">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="U18">
         <v>2.88</v>
@@ -3279,28 +3279,28 @@
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA18">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
         <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.23</v>
@@ -4097,19 +4097,19 @@
         <v>3.6</v>
       </c>
       <c r="AA23">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
         <v>1.93</v>
       </c>
       <c r="AC23">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
         <v>1.82</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O24">
         <v>4.3</v>
@@ -4230,7 +4230,7 @@
         <v>6.12</v>
       </c>
       <c r="Q24">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R24">
         <v>2.4</v>
@@ -4278,7 +4278,7 @@
         <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4420,13 +4420,13 @@
         <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="AA25">
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
         <v>3.6</v>
@@ -4438,10 +4438,10 @@
         <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4556,25 +4556,25 @@
         <v>2.78</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R26">
         <v>2.02</v>
       </c>
       <c r="S26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
         <v>2.7</v>
       </c>
       <c r="U26">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V26">
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O30">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R30">
         <v>2.4</v>
@@ -5226,34 +5226,34 @@
         <v>1.47</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA30">
         <v>1.43</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC30">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD30">
         <v>1.5</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG30">
         <v>2.23</v>
@@ -5534,10 +5534,10 @@
         <v>4.57</v>
       </c>
       <c r="Q32">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
         <v>1.45</v>
@@ -5546,7 +5546,7 @@
         <v>2.56</v>
       </c>
       <c r="U32">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V32">
         <v>1.3</v>
@@ -5567,7 +5567,7 @@
         <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC32">
         <v>4.2</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P39">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="Q39">
         <v>2.88</v>
       </c>
       <c r="R39">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S39">
         <v>1.68</v>
       </c>
       <c r="T39">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U39">
         <v>4.2</v>
@@ -6696,31 +6696,31 @@
         <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y39">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Z39">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA39">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AB39">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC39">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AD39">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE39">
         <v>1</v>
       </c>
       <c r="AF39">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AG39">
         <v>1.54</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="O41">
         <v>3.9</v>
       </c>
       <c r="P41">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q41">
         <v>2.1</v>
       </c>
       <c r="R41">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="S41">
         <v>1.22</v>
@@ -7013,7 +7013,7 @@
         <v>3.9</v>
       </c>
       <c r="U41">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V41">
         <v>1.65</v>
@@ -7028,7 +7028,7 @@
         <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA41">
         <v>1.47</v>
@@ -7037,7 +7037,7 @@
         <v>2.6</v>
       </c>
       <c r="AC41">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD41">
         <v>1.65</v>
@@ -7049,7 +7049,7 @@
         <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
         <v>3.25</v>
       </c>
       <c r="P42">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q42">
         <v>3.38</v>
@@ -7170,34 +7170,34 @@
         <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
         <v>2.69</v>
       </c>
       <c r="U42">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="AA42">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB42">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC42">
         <v>3.34</v>
@@ -7206,13 +7206,13 @@
         <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
         <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P47">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q47">
+        <v>2.05</v>
+      </c>
+      <c r="R47">
         <v>2.1</v>
-      </c>
-      <c r="R47">
-        <v>2.03</v>
       </c>
       <c r="S47">
         <v>1.48</v>
       </c>
       <c r="T47">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U47">
         <v>3.16</v>
@@ -8163,7 +8163,7 @@
         <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.2</v>
@@ -8181,7 +8181,7 @@
         <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
         <v>1.18</v>
@@ -8299,7 +8299,7 @@
         <v>1.4</v>
       </c>
       <c r="O49">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P49">
         <v>6.51</v>
@@ -8308,37 +8308,37 @@
         <v>1.95</v>
       </c>
       <c r="R49">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
         <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AA49">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC49">
         <v>3.1</v>
@@ -8477,16 +8477,16 @@
         <v>1.52</v>
       </c>
       <c r="T50">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U50">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="V50">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X50">
         <v>1.04</v>
@@ -8498,7 +8498,7 @@
         <v>2.62</v>
       </c>
       <c r="AA50">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AB50">
         <v>1.53</v>
@@ -8513,7 +8513,7 @@
         <v>1</v>
       </c>
       <c r="AF50">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG50">
         <v>1.67</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.67</v>
@@ -8637,10 +8637,10 @@
         <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U51">
         <v>2.81</v>
@@ -8655,7 +8655,7 @@
         <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
         <v>3.4</v>
@@ -8664,16 +8664,16 @@
         <v>1.89</v>
       </c>
       <c r="AB51">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
         <v>3.4</v>
       </c>
       <c r="AD51">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
         <v>1.75</v>
@@ -8797,7 +8797,7 @@
         <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S52">
         <v>1.36</v>
@@ -8806,7 +8806,7 @@
         <v>3</v>
       </c>
       <c r="U52">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
         <v>1.41</v>
@@ -8815,16 +8815,16 @@
         <v>1.06</v>
       </c>
       <c r="X52">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
         <v>3.6</v>
       </c>
       <c r="AA52">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB52">
         <v>1.86</v>
@@ -8833,16 +8833,16 @@
         <v>3.14</v>
       </c>
       <c r="AD52">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
         <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
         <v>1.83</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="O54">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q54">
         <v>4.84</v>
@@ -9126,10 +9126,10 @@
         <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U54">
         <v>2.62</v>
@@ -9156,7 +9156,7 @@
         <v>1.87</v>
       </c>
       <c r="AC54">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AD54">
         <v>1.33</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O55">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P55">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>3.4</v>
+        <v>4.03</v>
       </c>
       <c r="R55">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="S55">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T55">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="U55">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V55">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="AA55">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB55">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC55">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD55">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AG55">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>2.4</v>
+      </c>
+      <c r="O56">
         <v>3.1</v>
       </c>
-      <c r="O56">
-        <v>2.8</v>
-      </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q56">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="R56">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T56">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="U56">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V56">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y56">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z56">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="AA56">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB56">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC56">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AD56">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AG56">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK56">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O57">
         <v>3.1</v>
       </c>
       <c r="P57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q57">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="R57">
         <v>2</v>
@@ -9624,7 +9624,7 @@
         <v>2.97</v>
       </c>
       <c r="V57">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W57">
         <v>1.02</v>
@@ -9633,16 +9633,16 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z57">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA57">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB57">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC57">
         <v>4.1</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AK57">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9784,7 +9784,7 @@
         <v>2.34</v>
       </c>
       <c r="U58">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V58">
         <v>1.26</v>
@@ -9793,7 +9793,7 @@
         <v>1</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.42</v>
@@ -9811,13 +9811,13 @@
         <v>4.2</v>
       </c>
       <c r="AD58">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE58">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG58">
         <v>1.73</v>
@@ -10415,25 +10415,25 @@
         </is>
       </c>
       <c r="N62">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="O62">
         <v>3.8</v>
       </c>
       <c r="P62">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q62">
         <v>4.2</v>
       </c>
       <c r="R62">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S62">
         <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U62">
         <v>2.45</v>
@@ -10451,7 +10451,7 @@
         <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
       <c r="AA62">
         <v>1.7</v>
@@ -10469,7 +10469,7 @@
         <v>1.14</v>
       </c>
       <c r="AF62">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG62">
         <v>1.96</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="O63">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="P63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q63">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R63">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="S63">
         <v>1.17</v>
@@ -10599,10 +10599,10 @@
         <v>4.8</v>
       </c>
       <c r="U63">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V63">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W63">
         <v>1.24</v>
@@ -10614,28 +10614,28 @@
         <v>1.05</v>
       </c>
       <c r="Z63">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA63">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AB63">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="AC63">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD63">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AE63">
         <v>1.42</v>
       </c>
       <c r="AF63">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AG63">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,55 +10741,55 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O64">
         <v>3.3</v>
       </c>
       <c r="P64">
-        <v>5.3</v>
+        <v>6.97</v>
       </c>
       <c r="Q64">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="R64">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T64">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U64">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V64">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W64">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y64">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Z64">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AA64">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC64">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD64">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE64">
         <v>1.04</v>
@@ -10798,7 +10798,7 @@
         <v>2.54</v>
       </c>
       <c r="AG64">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK64">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,16 +10907,16 @@
         <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P65">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
       </c>
       <c r="R65">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S65">
         <v>1.33</v>
@@ -10925,37 +10925,37 @@
         <v>2.85</v>
       </c>
       <c r="U65">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="V65">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W65">
         <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA65">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB65">
         <v>1.9</v>
       </c>
       <c r="AC65">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD65">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
         <v>1.65</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11100,16 +11100,16 @@
         <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z66">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA66">
         <v>2.17</v>
       </c>
       <c r="AB66">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC66">
         <v>3.58</v>
@@ -11236,10 +11236,10 @@
         <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q67">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
         <v>2</v>
@@ -11248,7 +11248,7 @@
         <v>1.47</v>
       </c>
       <c r="T67">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U67">
         <v>3.1</v>
@@ -11287,7 +11287,7 @@
         <v>1.9</v>
       </c>
       <c r="AG67">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
         <v>1.62</v>
@@ -11393,43 +11393,43 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q68">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R68">
         <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T68">
+        <v>2.62</v>
+      </c>
+      <c r="U68">
         <v>2.88</v>
       </c>
-      <c r="U68">
-        <v>2.83</v>
-      </c>
       <c r="V68">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z68">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA68">
         <v>1.95</v>
@@ -11441,16 +11441,16 @@
         <v>3.35</v>
       </c>
       <c r="AD68">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
         <v>4.2</v>
       </c>
       <c r="Q69">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R69">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T69">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="U69">
         <v>3.28</v>
@@ -11589,13 +11589,13 @@
         <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z69">
         <v>2.49</v>
       </c>
       <c r="AA69">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="AB69">
         <v>1.58</v>
@@ -11607,7 +11607,7 @@
         <v>1.18</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF69">
         <v>2</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
         <v>1.87</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O71">
         <v>3.6</v>
@@ -11897,46 +11897,46 @@
         <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U71">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="V71">
         <v>1.47</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA71">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB71">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AC71">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE71">
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG71">
         <v>2.1</v>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL71">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>2.4</v>
+      </c>
+      <c r="O55">
         <v>3.1</v>
       </c>
-      <c r="O55">
-        <v>2.8</v>
-      </c>
       <c r="P55">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q55">
-        <v>4.03</v>
+        <v>3.4</v>
       </c>
       <c r="R55">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S55">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T55">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="U55">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V55">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z55">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="AA55">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AB55">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC55">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AD55">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF55">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AG55">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O56">
         <v>3.1</v>
       </c>
       <c r="P56">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R56">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S56">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T56">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U56">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="V56">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W56">
+        <v>1.02</v>
+      </c>
+      <c r="X56">
         <v>1.01</v>
       </c>
-      <c r="X56">
-        <v>1.06</v>
-      </c>
       <c r="Y56">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="Z56">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="AA56">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AB56">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC56">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD56">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AG56">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
+        <v>1.47</v>
+      </c>
+      <c r="AK56">
         <v>1.36</v>
-      </c>
-      <c r="AK56">
-        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
+        <v>3.1</v>
+      </c>
+      <c r="O57">
         <v>2.8</v>
-      </c>
-      <c r="O57">
-        <v>3.1</v>
       </c>
       <c r="P57">
         <v>2.25</v>
       </c>
       <c r="Q57">
-        <v>3.32</v>
+        <v>4.03</v>
       </c>
       <c r="R57">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S57">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T57">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U57">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V57">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W57">
         <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z57">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AA57">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB57">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC57">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE57">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG57">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9929,16 +9929,16 @@
         <v>1.98</v>
       </c>
       <c r="O59">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P59">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="Q59">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R59">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="S59">
         <v>1.17</v>
@@ -9953,28 +9953,28 @@
         <v>1.95</v>
       </c>
       <c r="W59">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z59">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AA59">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB59">
         <v>3.5</v>
       </c>
       <c r="AC59">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD59">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AE59">
         <v>1.48</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O60">
         <v>8</v>
@@ -10098,16 +10098,16 @@
         <v>13</v>
       </c>
       <c r="Q60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R60">
         <v>3</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T60">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="U60">
         <v>1.95</v>
@@ -10122,25 +10122,25 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AA60">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB60">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AC60">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD60">
         <v>1.8</v>
       </c>
       <c r="AE60">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF60">
         <v>1.95</v>
@@ -10162,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="AK60">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,10 +10261,10 @@
         <v>4.4</v>
       </c>
       <c r="Q61">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
         <v>1.39</v>
@@ -10325,7 +10325,7 @@
         <v>1.11</v>
       </c>
       <c r="AK61">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O64">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P64">
-        <v>6.97</v>
+        <v>5.4</v>
       </c>
       <c r="Q64">
         <v>2.15</v>
@@ -10756,10 +10756,10 @@
         <v>2</v>
       </c>
       <c r="S64">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T64">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U64">
         <v>3.58</v>
@@ -10771,7 +10771,7 @@
         <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y64">
         <v>1.54</v>
@@ -10789,7 +10789,7 @@
         <v>5.5</v>
       </c>
       <c r="AD64">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE64">
         <v>1.04</v>
@@ -10907,13 +10907,13 @@
         <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="R65">
         <v>2.08</v>
@@ -10925,7 +10925,7 @@
         <v>2.85</v>
       </c>
       <c r="U65">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="V65">
         <v>1.43</v>
@@ -10937,25 +10937,25 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z65">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA65">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB65">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC65">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD65">
         <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
         <v>1.65</v>
@@ -10977,7 +10977,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q66">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="R66">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S66">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T66">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U66">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
+        <v>1.04</v>
+      </c>
+      <c r="X66">
         <v>1.03</v>
       </c>
-      <c r="X66">
-        <v>1.04</v>
-      </c>
       <c r="Y66">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z66">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA66">
         <v>2.17</v>
       </c>
       <c r="AB66">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC66">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE66">
         <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG66">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11236,19 +11236,19 @@
         <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="Q67">
         <v>2.63</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
         <v>1.47</v>
       </c>
       <c r="T67">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="U67">
         <v>3.1</v>
@@ -11266,7 +11266,7 @@
         <v>1.4</v>
       </c>
       <c r="Z67">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA67">
         <v>2.25</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
         <v>1.62</v>
@@ -11393,31 +11393,31 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q68">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R68">
         <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T68">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U68">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V68">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W68">
         <v>1.05</v>
@@ -11426,31 +11426,31 @@
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z68">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB68">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC68">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD68">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE68">
         <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK68">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,7 +11559,7 @@
         <v>1.75</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
         <v>4.2</v>
@@ -11568,13 +11568,13 @@
         <v>2.47</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
         <v>1.48</v>
       </c>
       <c r="T69">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U69">
         <v>3.28</v>
@@ -11595,25 +11595,25 @@
         <v>2.49</v>
       </c>
       <c r="AA69">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AB69">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC69">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD69">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE69">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
         <v>2</v>
       </c>
       <c r="AG69">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11882,37 +11882,37 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O71">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P71">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q71">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="R71">
         <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T71">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U71">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="V71">
         <v>1.47</v>
       </c>
       <c r="W71">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.25</v>
@@ -11921,25 +11921,25 @@
         <v>3.7</v>
       </c>
       <c r="AA71">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB71">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC71">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AD71">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE71">
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.68</v>
+        <v>3.7</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>2.26</v>
+        <v>4.4</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T28">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U28">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Z28">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AB28">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AD28">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.7</v>
+        <v>1.68</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>1.9</v>
+        <v>4.33</v>
       </c>
       <c r="Q29">
-        <v>4.4</v>
+        <v>2.26</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U29">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="V29">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z29">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AA29">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC29">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD29">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O55">
         <v>3.1</v>
       </c>
       <c r="P55">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R55">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T55">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U55">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="V55">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W55">
+        <v>1.02</v>
+      </c>
+      <c r="X55">
         <v>1.01</v>
       </c>
-      <c r="X55">
-        <v>1.06</v>
-      </c>
       <c r="Y55">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="Z55">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="AA55">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AB55">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC55">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD55">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF55">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AG55">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
+        <v>1.47</v>
+      </c>
+      <c r="AK55">
         <v>1.36</v>
-      </c>
-      <c r="AK55">
-        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O56">
         <v>3.1</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q56">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T56">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U56">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="V56">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X56">
+        <v>1.06</v>
+      </c>
+      <c r="Y56">
+        <v>1.46</v>
+      </c>
+      <c r="Z56">
+        <v>2.47</v>
+      </c>
+      <c r="AA56">
+        <v>2.38</v>
+      </c>
+      <c r="AB56">
+        <v>1.5</v>
+      </c>
+      <c r="AC56">
+        <v>4.8</v>
+      </c>
+      <c r="AD56">
+        <v>1.14</v>
+      </c>
+      <c r="AE56">
         <v>1.01</v>
       </c>
-      <c r="Y56">
-        <v>1.32</v>
-      </c>
-      <c r="Z56">
-        <v>2.88</v>
-      </c>
-      <c r="AA56">
-        <v>2.07</v>
-      </c>
-      <c r="AB56">
-        <v>1.66</v>
-      </c>
-      <c r="AC56">
-        <v>4.1</v>
-      </c>
-      <c r="AD56">
-        <v>1.22</v>
-      </c>
-      <c r="AE56">
-        <v>1.07</v>
-      </c>
       <c r="AF56">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AG56">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AK56">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q6">
         <v>4.3</v>
       </c>
       <c r="R6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.02</v>
@@ -1323,28 +1323,28 @@
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.06</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="Q7">
-        <v>4.95</v>
+        <v>5.03</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
+        <v>1.25</v>
+      </c>
+      <c r="T7">
+        <v>3.6</v>
+      </c>
+      <c r="U7">
+        <v>2.25</v>
+      </c>
+      <c r="V7">
+        <v>1.61</v>
+      </c>
+      <c r="W7">
+        <v>1.11</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.14</v>
+      </c>
+      <c r="Z7">
+        <v>5.05</v>
+      </c>
+      <c r="AA7">
+        <v>1.5</v>
+      </c>
+      <c r="AB7">
+        <v>2.5</v>
+      </c>
+      <c r="AC7">
+        <v>2.25</v>
+      </c>
+      <c r="AD7">
+        <v>1.57</v>
+      </c>
+      <c r="AE7">
         <v>1.2</v>
       </c>
-      <c r="T7">
-        <v>4</v>
-      </c>
-      <c r="U7">
-        <v>2.1</v>
-      </c>
-      <c r="V7">
-        <v>1.63</v>
-      </c>
-      <c r="W7">
+      <c r="AF7">
+        <v>1.69</v>
+      </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.12</v>
       </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1.08</v>
-      </c>
-      <c r="Z7">
-        <v>5.45</v>
-      </c>
-      <c r="AA7">
-        <v>1.41</v>
-      </c>
-      <c r="AB7">
-        <v>2.52</v>
-      </c>
-      <c r="AC7">
-        <v>2.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.64</v>
-      </c>
-      <c r="AE7">
-        <v>1.28</v>
-      </c>
-      <c r="AF7">
-        <v>1.48</v>
-      </c>
-      <c r="AG7">
-        <v>2.35</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.17</v>
-      </c>
       <c r="AK7">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,61 +2105,61 @@
         <v>1.77</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>4.54</v>
+        <v>4.3</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="R12">
         <v>2.01</v>
@@ -2286,40 +2286,40 @@
         <v>2.85</v>
       </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AD12">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2338,7 +2338,7 @@
         <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.33</v>
+        <v>5.62</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P13">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="Q13">
-        <v>5.42</v>
+        <v>6.17</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U13">
         <v>2.62</v>
@@ -2458,50 +2458,50 @@
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC13">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE13">
+        <v>1.07</v>
+      </c>
+      <c r="AF13">
+        <v>1.91</v>
+      </c>
+      <c r="AG13">
+        <v>1.77</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.18</v>
+      </c>
+      <c r="AK13">
         <v>1.06</v>
-      </c>
-      <c r="AF13">
-        <v>1.81</v>
-      </c>
-      <c r="AG13">
-        <v>1.86</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.29</v>
-      </c>
-      <c r="AK13">
-        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,61 +2757,61 @@
         <v>2.75</v>
       </c>
       <c r="O15">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O16">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q16">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2938,10 +2938,10 @@
         <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -2953,13 +2953,13 @@
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA16">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB16">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC16">
         <v>2.7</v>
@@ -2974,7 +2974,7 @@
         <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="O17">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3249,40 +3249,40 @@
         <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>3.43</v>
+        <v>4.3</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
         <v>1.38</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AA18">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB18">
         <v>1.8</v>
@@ -3291,16 +3291,16 @@
         <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG18">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O22">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="P22">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="Q22">
         <v>3.18</v>
@@ -3913,7 +3913,7 @@
         <v>1.57</v>
       </c>
       <c r="T22">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
         <v>3.6</v>
@@ -3928,13 +3928,13 @@
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z22">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AA22">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB22">
         <v>1.46</v>
@@ -3952,7 +3952,7 @@
         <v>2.13</v>
       </c>
       <c r="AG22">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>5.03</v>
+        <v>5.16</v>
       </c>
       <c r="O23">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="P23">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q23">
-        <v>4.7</v>
+        <v>5.51</v>
       </c>
       <c r="R23">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
         <v>1.35</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4097,25 +4097,25 @@
         <v>3.6</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC23">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE23">
         <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG23">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
         <v>1.14</v>
@@ -4221,37 +4221,37 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P24">
-        <v>6.12</v>
+        <v>5.5</v>
       </c>
       <c r="Q24">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T24">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="U24">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
         <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.12</v>
@@ -4260,19 +4260,19 @@
         <v>4.75</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB24">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC24">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
         <v>1.75</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.48</v>
+        <v>2.71</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O25">
         <v>4.2</v>
@@ -4411,37 +4411,37 @@
         <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.46</v>
+        <v>3.26</v>
       </c>
       <c r="AA25">
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
         <v>3.6</v>
       </c>
       <c r="AD25">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
         <v>2.25</v>
       </c>
       <c r="AG25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
         <v>3</v>
@@ -4556,13 +4556,13 @@
         <v>2.78</v>
       </c>
       <c r="Q26">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="R26">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
         <v>2.7</v>
@@ -4574,25 +4574,25 @@
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z26">
         <v>2.92</v>
       </c>
       <c r="AA26">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
         <v>1.22</v>
@@ -4601,7 +4601,7 @@
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG26">
         <v>1.9</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
         <v>1.44</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
         <v>3.3</v>
@@ -4719,55 +4719,55 @@
         <v>2.85</v>
       </c>
       <c r="Q27">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="R27">
         <v>2.2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC27">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
         <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>1.9</v>
       </c>
       <c r="Q28">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S28">
         <v>1.5</v>
       </c>
       <c r="T28">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U28">
         <v>3.3</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
         <v>1</v>
       </c>
       <c r="X28">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
         <v>1.42</v>
       </c>
       <c r="Z28">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AA28">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC28">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AD28">
         <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG28">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P29">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="U29">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V29">
         <v>1.35</v>
@@ -5066,34 +5066,34 @@
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB29">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC29">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="AD29">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
         <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
         <v>2.02</v>
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>2.05</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
         <v>3.8</v>
       </c>
       <c r="U30">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
+        <v>1.18</v>
+      </c>
+      <c r="Z30">
+        <v>3.3</v>
+      </c>
+      <c r="AA30">
+        <v>1.57</v>
+      </c>
+      <c r="AB30">
+        <v>2.23</v>
+      </c>
+      <c r="AC30">
+        <v>2.41</v>
+      </c>
+      <c r="AD30">
+        <v>1.53</v>
+      </c>
+      <c r="AE30">
+        <v>1.15</v>
+      </c>
+      <c r="AF30">
+        <v>1.61</v>
+      </c>
+      <c r="AG30">
+        <v>2.16</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.17</v>
       </c>
-      <c r="Z30">
-        <v>4.5</v>
-      </c>
-      <c r="AA30">
-        <v>1.43</v>
-      </c>
-      <c r="AB30">
-        <v>1.99</v>
-      </c>
-      <c r="AC30">
-        <v>1.99</v>
-      </c>
-      <c r="AD30">
-        <v>1.5</v>
-      </c>
-      <c r="AE30">
-        <v>1.16</v>
-      </c>
-      <c r="AF30">
-        <v>1.59</v>
-      </c>
-      <c r="AG30">
-        <v>2.23</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.14</v>
-      </c>
       <c r="AK30">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5528,22 +5528,22 @@
         <v>1.72</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R32">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="S32">
         <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U32">
         <v>2.88</v>
@@ -5552,53 +5552,53 @@
         <v>1.3</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
         <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB32">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC32">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD32">
         <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
+        <v>1.95</v>
+      </c>
+      <c r="AG32">
+        <v>1.79</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.25</v>
+      </c>
+      <c r="AK32">
         <v>2</v>
-      </c>
-      <c r="AG32">
-        <v>1.76</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.26</v>
-      </c>
-      <c r="AK32">
-        <v>1.94</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S33">
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="U33">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V33">
         <v>1.39</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AA33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
         <v>3.04</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P34">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="Q34">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
         <v>2.48</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
         <v>2.36</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W34">
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
         <v>3.98</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
         <v>2.14</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AD34">
         <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,16 +6017,16 @@
         <v>1.55</v>
       </c>
       <c r="O35">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
-        <v>5.31</v>
+        <v>5.65</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S35">
         <v>1.22</v>
@@ -6035,7 +6035,7 @@
         <v>3.66</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V35">
         <v>1.6</v>
@@ -6047,22 +6047,22 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA35">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB35">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="AC35">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD35">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
@@ -6071,7 +6071,7 @@
         <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q36">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="S36">
         <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z36">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA36">
         <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC36">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD36">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE36">
         <v>1.21</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG36">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
         <v>1.85</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O37">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="P37">
-        <v>7.35</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q37">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R37">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="S37">
         <v>1.24</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U37">
         <v>2.1</v>
       </c>
       <c r="V37">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W37">
         <v>1.14</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z37">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="AA37">
         <v>1.47</v>
       </c>
       <c r="AB37">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC37">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD37">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK37">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,25 +6506,25 @@
         <v>1.15</v>
       </c>
       <c r="O38">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q38">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R38">
         <v>2.76</v>
       </c>
       <c r="S38">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V38">
         <v>1.71</v>
@@ -6536,10 +6536,10 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>5.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA38">
         <v>1.44</v>
@@ -6548,10 +6548,10 @@
         <v>2.62</v>
       </c>
       <c r="AC38">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AD38">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE38">
         <v>1.27</v>
@@ -6560,7 +6560,7 @@
         <v>2</v>
       </c>
       <c r="AG38">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,52 +6666,52 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O39">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="P39">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R39">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="S39">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="T39">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U39">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="V39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W39">
         <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y39">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Z39">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AA39">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AB39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC39">
-        <v>6.25</v>
+        <v>5.95</v>
       </c>
       <c r="AD39">
         <v>1.09</v>
@@ -6720,10 +6720,10 @@
         <v>1</v>
       </c>
       <c r="AF39">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG39">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="O40">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="P40">
-        <v>15</v>
+        <v>9.25</v>
       </c>
       <c r="Q40">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="R40">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="S40">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="U40">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="V40">
+        <v>1.81</v>
+      </c>
+      <c r="W40">
+        <v>1.19</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.07</v>
+      </c>
+      <c r="Z40">
+        <v>7</v>
+      </c>
+      <c r="AA40">
+        <v>1.31</v>
+      </c>
+      <c r="AB40">
+        <v>2.92</v>
+      </c>
+      <c r="AC40">
+        <v>1.88</v>
+      </c>
+      <c r="AD40">
         <v>1.85</v>
       </c>
-      <c r="W40">
-        <v>1.25</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>1.06</v>
-      </c>
-      <c r="Z40">
-        <v>7.5</v>
-      </c>
-      <c r="AA40">
-        <v>1.29</v>
-      </c>
-      <c r="AB40">
-        <v>3.25</v>
-      </c>
-      <c r="AC40">
-        <v>1.72</v>
-      </c>
-      <c r="AD40">
-        <v>2</v>
-      </c>
       <c r="AE40">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AF40">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AG40">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK40">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,55 +6992,55 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q41">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R41">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="S41">
         <v>1.22</v>
       </c>
       <c r="T41">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
         <v>2.16</v>
       </c>
       <c r="V41">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W41">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z41">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AA41">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB41">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AC41">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AD41">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE41">
         <v>1.28</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,31 +7158,31 @@
         <v>2.6</v>
       </c>
       <c r="O42">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q42">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T42">
         <v>2.69</v>
       </c>
       <c r="U42">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.05</v>
@@ -7197,13 +7197,13 @@
         <v>2.07</v>
       </c>
       <c r="AB42">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC42">
         <v>3.34</v>
       </c>
       <c r="AD42">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE42">
         <v>1.07</v>
@@ -7212,7 +7212,7 @@
         <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
         <v>1.41</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="O43">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="P43">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="Q43">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R43">
         <v>1.87</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T43">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.35</v>
+        <v>2.99</v>
       </c>
       <c r="V43">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB43">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC43">
-        <v>2.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD43">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.11</v>
       </c>
       <c r="AK43">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O44">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="P44">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q44">
         <v>1.91</v>
       </c>
       <c r="R44">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="S44">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T44">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="U44">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V44">
         <v>1.91</v>
       </c>
       <c r="W44">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7520,25 +7520,25 @@
         <v>7.3</v>
       </c>
       <c r="AA44">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB44">
         <v>3.28</v>
       </c>
       <c r="AC44">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD44">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AE44">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AF44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG44">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O45">
         <v>4.5</v>
       </c>
       <c r="P45">
-        <v>4.45</v>
+        <v>4.59</v>
       </c>
       <c r="Q45">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="R45">
         <v>2.61</v>
       </c>
       <c r="S45">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
         <v>4.1</v>
       </c>
       <c r="U45">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="V45">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7680,22 +7680,22 @@
         <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA45">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB45">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC45">
         <v>1.89</v>
       </c>
       <c r="AD45">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF45">
         <v>1.41</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="O46">
+        <v>3.55</v>
+      </c>
+      <c r="P46">
+        <v>2.02</v>
+      </c>
+      <c r="Q46">
+        <v>3.8</v>
+      </c>
+      <c r="R46">
+        <v>2.4</v>
+      </c>
+      <c r="S46">
+        <v>1.24</v>
+      </c>
+      <c r="T46">
         <v>3.5</v>
       </c>
-      <c r="P46">
-        <v>2.03</v>
-      </c>
-      <c r="Q46">
-        <v>3.5</v>
-      </c>
-      <c r="R46">
-        <v>2.3</v>
-      </c>
-      <c r="S46">
-        <v>1.22</v>
-      </c>
-      <c r="T46">
-        <v>3.75</v>
-      </c>
       <c r="U46">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V46">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>5.28</v>
       </c>
       <c r="AA46">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB46">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC46">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD46">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE46">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
         <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O47">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S47">
         <v>1.48</v>
       </c>
       <c r="T47">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U47">
         <v>3.16</v>
@@ -8009,25 +8009,25 @@
         <v>2.75</v>
       </c>
       <c r="AA47">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB47">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC47">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AG47">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="O48">
         <v>3.7</v>
@@ -8142,10 +8142,10 @@
         <v>1.9</v>
       </c>
       <c r="Q48">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
         <v>1.31</v>
@@ -8166,13 +8166,13 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
         <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB48">
         <v>2.2</v>
@@ -8187,10 +8187,10 @@
         <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.82</v>
       </c>
       <c r="AK48">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,16 +8299,16 @@
         <v>1.4</v>
       </c>
       <c r="O49">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P49">
         <v>6.51</v>
       </c>
       <c r="Q49">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.32</v>
@@ -8317,40 +8317,40 @@
         <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA49">
         <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AC49">
         <v>3.1</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
         <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG49">
         <v>1.76</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P50">
         <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="R50">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="S50">
         <v>1.52</v>
       </c>
       <c r="T50">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U50">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="V50">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
         <v>1.04</v>
@@ -8495,22 +8495,22 @@
         <v>1.45</v>
       </c>
       <c r="Z50">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA50">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB50">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC50">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AD50">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE50">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF50">
         <v>2.01</v>
@@ -8532,7 +8532,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="O51">
         <v>3.4</v>
       </c>
       <c r="P51">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q51">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="R51">
         <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
         <v>3</v>
@@ -8652,28 +8652,28 @@
         <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA51">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
         <v>3.4</v>
       </c>
       <c r="AD51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
         <v>1.75</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="AK51">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8788,19 +8788,19 @@
         <v>1.91</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="Q52">
         <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
         <v>3</v>
@@ -8812,19 +8812,19 @@
         <v>1.41</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.29</v>
       </c>
       <c r="Z52">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB52">
         <v>1.86</v>
@@ -8836,13 +8836,13 @@
         <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG52">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK52">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="O53">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P53">
         <v>1.5</v>
       </c>
       <c r="Q53">
-        <v>6.56</v>
+        <v>4.84</v>
       </c>
       <c r="R53">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
         <v>1.37</v>
@@ -8981,19 +8981,19 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
         <v>3.68</v>
       </c>
       <c r="AA53">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB53">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD53">
         <v>1.35</v>
@@ -9002,7 +9002,7 @@
         <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG53">
         <v>1.86</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK53">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>5.65</v>
+        <v>4.8</v>
       </c>
       <c r="O54">
         <v>3.7</v>
       </c>
       <c r="P54">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q54">
         <v>4.84</v>
@@ -9126,50 +9126,50 @@
         <v>2.2</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T54">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U54">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
+        <v>1.08</v>
+      </c>
+      <c r="X54">
         <v>1.05</v>
       </c>
-      <c r="X54">
-        <v>1.04</v>
-      </c>
       <c r="Y54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="AA54">
         <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC54">
         <v>2.97</v>
       </c>
       <c r="AD54">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF54">
+        <v>1.87</v>
+      </c>
+      <c r="AG54">
         <v>1.85</v>
       </c>
-      <c r="AG54">
-        <v>1.88</v>
-      </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,22 +9274,22 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O55">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q55">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S55">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T55">
         <v>2.5</v>
@@ -9298,13 +9298,13 @@
         <v>2.97</v>
       </c>
       <c r="V55">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W55">
         <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
         <v>1.32</v>
@@ -9313,19 +9313,19 @@
         <v>2.88</v>
       </c>
       <c r="AA55">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB55">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC55">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD55">
         <v>1.22</v>
       </c>
       <c r="AE55">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF55">
         <v>1.81</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AK55">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O56">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="P56">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="Q56">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="R56">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S56">
         <v>1.51</v>
@@ -9458,10 +9458,10 @@
         <v>2.29</v>
       </c>
       <c r="U56">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V56">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W56">
         <v>1.01</v>
@@ -9470,10 +9470,10 @@
         <v>1.06</v>
       </c>
       <c r="Y56">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z56">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AA56">
         <v>2.38</v>
@@ -9482,7 +9482,7 @@
         <v>1.5</v>
       </c>
       <c r="AC56">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD56">
         <v>1.14</v>
@@ -9491,10 +9491,10 @@
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG56">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK56">
         <v>1.44</v>
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O57">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>4.03</v>
       </c>
       <c r="R57">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S57">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T57">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="U57">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V57">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
         <v>1.05</v>
@@ -9636,19 +9636,19 @@
         <v>1.4</v>
       </c>
       <c r="Z57">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AA57">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB57">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AC57">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE57">
         <v>1.02</v>
@@ -9657,7 +9657,7 @@
         <v>1.93</v>
       </c>
       <c r="AG57">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
         <v>1.29</v>
@@ -9766,22 +9766,22 @@
         <v>2.15</v>
       </c>
       <c r="O58">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P58">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="Q58">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R58">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="S58">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T58">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="U58">
         <v>3.28</v>
@@ -9790,34 +9790,34 @@
         <v>1.26</v>
       </c>
       <c r="W58">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z58">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AA58">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AB58">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC58">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD58">
         <v>1.16</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF58">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG58">
         <v>1.73</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,34 +9926,34 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O59">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P59">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="Q59">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R59">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="S59">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="U59">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V59">
         <v>1.95</v>
       </c>
       <c r="W59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9965,25 +9965,25 @@
         <v>7.8</v>
       </c>
       <c r="AA59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB59">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AC59">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD59">
         <v>2.15</v>
       </c>
       <c r="AE59">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AF59">
         <v>1.25</v>
       </c>
       <c r="AG59">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK59">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,55 +10089,55 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="O60">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="P60">
-        <v>13</v>
+        <v>11.15</v>
       </c>
       <c r="Q60">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="S60">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="U60">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V60">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="W60">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z60">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB60">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AC60">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD60">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AE60">
         <v>1.31</v>
@@ -10146,7 +10146,7 @@
         <v>1.95</v>
       </c>
       <c r="AG60">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="AK60">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,37 +10258,37 @@
         <v>3.6</v>
       </c>
       <c r="P61">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q61">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="R61">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S61">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T61">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U61">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="V61">
         <v>1.41</v>
       </c>
       <c r="W61">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
         <v>1.29</v>
       </c>
       <c r="Z61">
-        <v>3.3</v>
+        <v>3.73</v>
       </c>
       <c r="AA61">
         <v>1.98</v>
@@ -10297,19 +10297,19 @@
         <v>1.84</v>
       </c>
       <c r="AC61">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AD61">
         <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG61">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,13 +10418,13 @@
         <v>4.22</v>
       </c>
       <c r="O62">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P62">
         <v>1.79</v>
       </c>
       <c r="Q62">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="R62">
         <v>2.27</v>
@@ -10436,43 +10436,43 @@
         <v>3.22</v>
       </c>
       <c r="U62">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="V62">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
         <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA62">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB62">
         <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
         <v>1.58</v>
       </c>
       <c r="AG62">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK62">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O63">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="P63">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q63">
         <v>1.46</v>
       </c>
       <c r="R63">
-        <v>3.26</v>
+        <v>3.59</v>
       </c>
       <c r="S63">
         <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V63">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W63">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA63">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AC63">
+        <v>1.84</v>
+      </c>
+      <c r="AD63">
+        <v>2.11</v>
+      </c>
+      <c r="AE63">
+        <v>1.43</v>
+      </c>
+      <c r="AF63">
+        <v>1.95</v>
+      </c>
+      <c r="AG63">
         <v>1.8</v>
-      </c>
-      <c r="AD63">
-        <v>1.97</v>
-      </c>
-      <c r="AE63">
-        <v>1.42</v>
-      </c>
-      <c r="AF63">
-        <v>1.94</v>
-      </c>
-      <c r="AG63">
-        <v>1.82</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.08</v>
       </c>
       <c r="AK63">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="O64">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P64">
-        <v>5.4</v>
+        <v>6.14</v>
       </c>
       <c r="Q64">
         <v>2.15</v>
@@ -10756,7 +10756,7 @@
         <v>2</v>
       </c>
       <c r="S64">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T64">
         <v>2.38</v>
@@ -10771,28 +10771,28 @@
         <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y64">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z64">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AA64">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB64">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC64">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD64">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE64">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
         <v>2.54</v>
@@ -10814,7 +10814,7 @@
         <v>1.11</v>
       </c>
       <c r="AK64">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O65">
         <v>3.4</v>
@@ -10925,28 +10925,28 @@
         <v>2.85</v>
       </c>
       <c r="U65">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="V65">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
         <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
         <v>3.78</v>
       </c>
       <c r="AA65">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB65">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC65">
         <v>3.2</v>
@@ -10955,7 +10955,7 @@
         <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF65">
         <v>1.65</v>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P66">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q66">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R66">
         <v>2</v>
       </c>
       <c r="S66">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U66">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V66">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X66">
         <v>1.03</v>
@@ -11106,10 +11106,10 @@
         <v>2.78</v>
       </c>
       <c r="AA66">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB66">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC66">
         <v>3.82</v>
@@ -11121,10 +11121,10 @@
         <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG66">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O69">
         <v>3.2</v>
@@ -11571,10 +11571,10 @@
         <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T69">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U69">
         <v>3.28</v>
@@ -11595,10 +11595,10 @@
         <v>2.49</v>
       </c>
       <c r="AA69">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AB69">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC69">
         <v>4.33</v>
@@ -11610,7 +11610,7 @@
         <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG69">
         <v>1.66</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,7 +11722,7 @@
         <v>2.22</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P70">
         <v>2.8</v>
@@ -11882,16 +11882,16 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O71">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="Q71">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R71">
         <v>2.3</v>
@@ -11903,7 +11903,7 @@
         <v>3.1</v>
       </c>
       <c r="U71">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="V71">
         <v>1.47</v>
@@ -11918,16 +11918,16 @@
         <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA71">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB71">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC71">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD71">
         <v>1.41</v>
@@ -11939,7 +11939,7 @@
         <v>1.68</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL71">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
         <v>3.18</v>
@@ -3913,7 +3913,7 @@
         <v>1.57</v>
       </c>
       <c r="T22">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="U22">
         <v>3.6</v>
@@ -3946,7 +3946,7 @@
         <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
         <v>2.13</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O39">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="P39">
         <v>3.8</v>
       </c>
       <c r="Q39">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="R39">
         <v>1.81</v>
@@ -6684,25 +6684,25 @@
         <v>1.6</v>
       </c>
       <c r="T39">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U39">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V39">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W39">
         <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y39">
         <v>1.62</v>
       </c>
       <c r="Z39">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="AA39">
         <v>3.2</v>
@@ -6711,19 +6711,19 @@
         <v>1.36</v>
       </c>
       <c r="AC39">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="AD39">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG39">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AK39">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,80 +9600,80 @@
         </is>
       </c>
       <c r="N57">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="O57">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="P57">
-        <v>2.2</v>
+        <v>3.01</v>
       </c>
       <c r="Q57">
-        <v>4.03</v>
+        <v>2.88</v>
       </c>
       <c r="R57">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="S57">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T57">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="U57">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="V57">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W57">
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
         <v>1.4</v>
       </c>
       <c r="Z57">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AA57">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AB57">
+        <v>1.56</v>
+      </c>
+      <c r="AC57">
+        <v>4.15</v>
+      </c>
+      <c r="AD57">
+        <v>1.16</v>
+      </c>
+      <c r="AE57">
+        <v>1.01</v>
+      </c>
+      <c r="AF57">
+        <v>1.95</v>
+      </c>
+      <c r="AG57">
+        <v>1.73</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>1.31</v>
+      </c>
+      <c r="AK57">
         <v>1.58</v>
-      </c>
-      <c r="AC57">
-        <v>4.4</v>
-      </c>
-      <c r="AD57">
-        <v>1.17</v>
-      </c>
-      <c r="AE57">
-        <v>1.02</v>
-      </c>
-      <c r="AF57">
-        <v>1.93</v>
-      </c>
-      <c r="AG57">
-        <v>1.77</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>1.33</v>
-      </c>
-      <c r="AK57">
-        <v>1.29</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="O58">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>3.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q58">
-        <v>2.88</v>
+        <v>4.03</v>
       </c>
       <c r="R58">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="S58">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T58">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="U58">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V58">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W58">
         <v>1.03</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
         <v>1.4</v>
       </c>
       <c r="Z58">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AA58">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AB58">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AC58">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD58">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG58">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O60">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="P60">
-        <v>11.15</v>
+        <v>19</v>
       </c>
       <c r="Q60">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R60">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="V60">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W60">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA60">
         <v>1.32</v>
       </c>
       <c r="AB60">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AC60">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AD60">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AE60">
         <v>1.31</v>
       </c>
       <c r="AF60">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG60">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AK60">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>3.6</v>
       </c>
       <c r="P61">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q61">
         <v>2.29</v>
@@ -10285,31 +10285,31 @@
         <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z61">
         <v>3.73</v>
       </c>
       <c r="AA61">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AB61">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC61">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD61">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE61">
         <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10578,34 +10578,34 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="O63">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="P63">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q63">
         <v>1.46</v>
       </c>
       <c r="R63">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="S63">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T63">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="U63">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V63">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W63">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X63">
         <v>1.01</v>
@@ -10617,25 +10617,25 @@
         <v>8</v>
       </c>
       <c r="AA63">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB63">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AC63">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AD63">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AE63">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF63">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG63">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK63">
         <v>5.6</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
         <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="Q67">
         <v>2.63</v>
@@ -11251,7 +11251,7 @@
         <v>2.44</v>
       </c>
       <c r="U67">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="V67">
         <v>1.32</v>
@@ -11260,34 +11260,34 @@
         <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z67">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AA67">
         <v>2.25</v>
       </c>
       <c r="AB67">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC67">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="AD67">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE67">
         <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG67">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11411,31 +11411,31 @@
         <v>1.39</v>
       </c>
       <c r="T68">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="U68">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="V68">
         <v>1.35</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z68">
         <v>3.4</v>
       </c>
       <c r="AA68">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC68">
         <v>3.45</v>
@@ -11450,7 +11450,7 @@
         <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-08-31.xlsx
+++ b/jogos_2026-08-31.xlsx
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1283,23 +1283,23 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
         <v>1.31</v>
@@ -1308,31 +1308,31 @@
         <v>3.02</v>
       </c>
       <c r="U6">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA6">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC6">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD6">
         <v>1.33</v>
@@ -1341,10 +1341,10 @@
         <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1353,41 +1353,41 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "36"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,130 +1427,130 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="O7">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P7">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Q7">
-        <v>5.03</v>
+        <v>6.5</v>
       </c>
       <c r="R7">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T7">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U7">
         <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z7">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB7">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC7">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD7">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "27", "58", "65"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="AK7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>4.2</v>
+        <v>1.43</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P8">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>5.19</v>
+        <v>1.84</v>
       </c>
       <c r="R8">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>2.67</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA8">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AB8">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC8">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD8">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AE8">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF8">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AG8">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK8">
-        <v>1.14</v>
+        <v>2.66</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.43</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>5.19</v>
       </c>
       <c r="R9">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>2.67</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
+        <v>1.26</v>
+      </c>
+      <c r="Z9">
+        <v>3.2</v>
+      </c>
+      <c r="AA9">
+        <v>1.89</v>
+      </c>
+      <c r="AB9">
+        <v>1.8</v>
+      </c>
+      <c r="AC9">
+        <v>3.14</v>
+      </c>
+      <c r="AD9">
+        <v>1.27</v>
+      </c>
+      <c r="AE9">
+        <v>1.07</v>
+      </c>
+      <c r="AF9">
+        <v>1.81</v>
+      </c>
+      <c r="AG9">
+        <v>1.86</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.22</v>
+      </c>
+      <c r="AK9">
         <v>1.14</v>
-      </c>
-      <c r="Z9">
-        <v>4.33</v>
-      </c>
-      <c r="AA9">
-        <v>1.5</v>
-      </c>
-      <c r="AB9">
-        <v>2.5</v>
-      </c>
-      <c r="AC9">
-        <v>2.35</v>
-      </c>
-      <c r="AD9">
-        <v>1.47</v>
-      </c>
-      <c r="AE9">
-        <v>1.16</v>
-      </c>
-      <c r="AF9">
-        <v>1.74</v>
-      </c>
-      <c r="AG9">
-        <v>1.94</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.12</v>
-      </c>
-      <c r="AK9">
-        <v>2.66</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2079,54 +2079,54 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O11">
         <v>3.25</v>
       </c>
       <c r="P11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U11">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
         <v>1.04</v>
@@ -2135,74 +2135,74 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB11">
         <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
         <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "76", "79", "87"]</t>
         </is>
       </c>
       <c r="AJ11">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -3220,130 +3220,130 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
         <v>3.2</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="R18">
+        <v>2.15</v>
+      </c>
+      <c r="S18">
+        <v>1.33</v>
+      </c>
+      <c r="T18">
+        <v>2.68</v>
+      </c>
+      <c r="U18">
+        <v>2.75</v>
+      </c>
+      <c r="V18">
+        <v>1.41</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.25</v>
+      </c>
+      <c r="Z18">
+        <v>3.28</v>
+      </c>
+      <c r="AA18">
+        <v>1.93</v>
+      </c>
+      <c r="AB18">
+        <v>1.85</v>
+      </c>
+      <c r="AC18">
+        <v>3.3</v>
+      </c>
+      <c r="AD18">
+        <v>1.28</v>
+      </c>
+      <c r="AE18">
+        <v>1.07</v>
+      </c>
+      <c r="AF18">
+        <v>1.71</v>
+      </c>
+      <c r="AG18">
         <v>2.02</v>
       </c>
-      <c r="S18">
-        <v>1.4</v>
-      </c>
-      <c r="T18">
-        <v>2.88</v>
-      </c>
-      <c r="U18">
-        <v>2.7</v>
-      </c>
-      <c r="V18">
-        <v>1.38</v>
-      </c>
-      <c r="W18">
-        <v>1.04</v>
-      </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.23</v>
-      </c>
-      <c r="Z18">
-        <v>3.6</v>
-      </c>
-      <c r="AA18">
-        <v>1.95</v>
-      </c>
-      <c r="AB18">
-        <v>1.8</v>
-      </c>
-      <c r="AC18">
-        <v>3.4</v>
-      </c>
-      <c r="AD18">
-        <v>1.31</v>
-      </c>
-      <c r="AE18">
-        <v>1.06</v>
-      </c>
-      <c r="AF18">
-        <v>1.74</v>
-      </c>
-      <c r="AG18">
-        <v>1.98</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "64"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "69"]</t>
         </is>
       </c>
       <c r="AJ18">
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -4198,130 +4198,130 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O24">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="P24">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q24">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T24">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="U24">
+        <v>2.2</v>
+      </c>
+      <c r="V24">
+        <v>1.6</v>
+      </c>
+      <c r="W24">
+        <v>1.12</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.18</v>
+      </c>
+      <c r="Z24">
+        <v>5</v>
+      </c>
+      <c r="AA24">
+        <v>1.54</v>
+      </c>
+      <c r="AB24">
         <v>2.27</v>
       </c>
-      <c r="V24">
-        <v>1.55</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.12</v>
-      </c>
-      <c r="Z24">
-        <v>4.75</v>
-      </c>
-      <c r="AA24">
-        <v>1.62</v>
-      </c>
-      <c r="AB24">
-        <v>2.28</v>
-      </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD24">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "55"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4364,81 +4364,81 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
         <v>7.6</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P25">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q25">
         <v>7</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S25">
         <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="AA25">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AD25">
         <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG25">
         <v>1.62</v>
@@ -4450,41 +4450,41 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "23", "25", "65"]</t>
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>2.77</v>
       </c>
       <c r="AK25">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -5828,81 +5828,81 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O34">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
       </c>
       <c r="R34">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U34">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AC34">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="AD34">
         <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
@@ -5912,46 +5912,46 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
+          <t>["22", "34", "67", "77"]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,60 +5991,60 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="O35">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="P35">
-        <v>5.65</v>
+        <v>5.2</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R35">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6053,16 +6053,16 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AB35">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AC35">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AD35">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
@@ -6075,46 +6075,46 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
+          <t>["5", "14", "26", "87"]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK35">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6157,13 +6157,13 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -6173,23 +6173,23 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="P36">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q36">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="R36">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="S36">
         <v>1.22</v>
@@ -6198,43 +6198,43 @@
         <v>3.8</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V36">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="W36">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AB36">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC36">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AD36">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE36">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF36">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6243,41 +6243,41 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,130 +6317,130 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="O37">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="P37">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R37">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="S37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="U37">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA37">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB37">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD37">
         <v>1.64</v>
       </c>
       <c r="AE37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "45+4", "64"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6499,38 +6499,38 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O38">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P38">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q38">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R38">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V38">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6542,19 +6542,19 @@
         <v>6.5</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB38">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC38">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AD38">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE38">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
         <v>2</v>
@@ -6573,37 +6573,37 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6643,13 +6643,13 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -6662,56 +6662,56 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O39">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="P39">
+        <v>4.2</v>
+      </c>
+      <c r="Q39">
+        <v>2.92</v>
+      </c>
+      <c r="R39">
+        <v>1.82</v>
+      </c>
+      <c r="S39">
+        <v>1.65</v>
+      </c>
+      <c r="T39">
+        <v>2.07</v>
+      </c>
+      <c r="U39">
         <v>3.8</v>
       </c>
-      <c r="Q39">
-        <v>3.05</v>
-      </c>
-      <c r="R39">
-        <v>1.81</v>
-      </c>
-      <c r="S39">
-        <v>1.6</v>
-      </c>
-      <c r="T39">
-        <v>2.25</v>
-      </c>
-      <c r="U39">
-        <v>4.33</v>
-      </c>
       <c r="V39">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W39">
         <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y39">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z39">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AA39">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AB39">
         <v>1.36</v>
       </c>
       <c r="AC39">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="AD39">
         <v>1.08</v>
@@ -6720,53 +6720,53 @@
         <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AG39">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
+          <t>["45+2"]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ39">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AK39">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL39">
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,130 +6806,130 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
         <v>1.19</v>
       </c>
       <c r="O40">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="P40">
-        <v>9.25</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R40">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="S40">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="U40">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="V40">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W40">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA40">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AB40">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AC40">
         <v>1.88</v>
       </c>
       <c r="AD40">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE40">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AF40">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG40">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
+          <t>["18", "68", "85"]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK40">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,130 +6969,130 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P41">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q41">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R41">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U41">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="V41">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AC41">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AD41">
         <v>1.66</v>
       </c>
       <c r="AE41">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AF41">
         <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "72"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88", "88"]</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7132,130 +7132,130 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="O42">
+        <v>3.25</v>
+      </c>
+      <c r="P42">
+        <v>2.4</v>
+      </c>
+      <c r="Q42">
         <v>3.3</v>
       </c>
-      <c r="P42">
-        <v>2.38</v>
-      </c>
-      <c r="Q42">
-        <v>3.48</v>
-      </c>
       <c r="R42">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T42">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
         <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z42">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AA42">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB42">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC42">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AD42">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE42">
         <v>1.07</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG42">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,16 +7295,16 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -7314,29 +7314,29 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
         <v>2.4</v>
       </c>
       <c r="O43">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="R43">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="S43">
         <v>1.42</v>
       </c>
       <c r="T43">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U43">
         <v>2.99</v>
@@ -7351,74 +7351,74 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB43">
         <v>1.65</v>
       </c>
       <c r="AC43">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
         <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AJ43">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AK43">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,100 +7458,100 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="O44">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P44">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="Q44">
         <v>1.91</v>
       </c>
       <c r="R44">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="S44">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T44">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="U44">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="V44">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="W44">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z44">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA44">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AB44">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="AC44">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AD44">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AE44">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF44">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AG44">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK44">
         <v>2.36</v>
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,130 +7621,130 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P45">
-        <v>4.59</v>
+        <v>4</v>
       </c>
       <c r="Q45">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="R45">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="S45">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T45">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U45">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="V45">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="AA45">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB45">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AC45">
         <v>1.89</v>
       </c>
       <c r="AD45">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AE45">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "46"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1"]</t>
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,130 +7784,130 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q46">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="U46">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="V46">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>5.28</v>
+        <v>4.54</v>
       </c>
       <c r="AA46">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB46">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AC46">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="AD46">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
+        <v>1.19</v>
+      </c>
+      <c r="AF46">
+        <v>1.53</v>
+      </c>
+      <c r="AG46">
+        <v>2.32</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>["54", "58"]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>["5", "11"]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.25</v>
       </c>
-      <c r="AF46">
-        <v>1.44</v>
-      </c>
-      <c r="AG46">
-        <v>2.56</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
+      <c r="AK46">
         <v>1.22</v>
       </c>
-      <c r="AK46">
-        <v>1.24</v>
-      </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -7959,33 +7959,33 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P47">
         <v>6</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R47">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="S47">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T47">
         <v>2.44</v>
@@ -8015,7 +8015,7 @@
         <v>1.61</v>
       </c>
       <c r="AC47">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AD47">
         <v>1.18</v>
@@ -8024,53 +8024,53 @@
         <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AG47">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
+          <t>["61", "85"]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8436,78 +8436,78 @@
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O50">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P50">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="R50">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="S50">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T50">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U50">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V50">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W50">
         <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y50">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z50">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AA50">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AB50">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC50">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AD50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE50">
         <v>1.01</v>
@@ -8520,46 +8520,46 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "76"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "90+5"]</t>
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL50">
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -8774,60 +8774,60 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
         <v>1.91</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
         <v>3.93</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R52">
         <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
         <v>3</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V52">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="AA52">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB52">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
         <v>3.14</v>
@@ -8842,50 +8842,50 @@
         <v>1.76</v>
       </c>
       <c r="AG52">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
+          <t>["90+6"]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL52">
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,25 +9079,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -9107,65 +9107,65 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P54">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Q54">
-        <v>4.84</v>
+        <v>3.6</v>
       </c>
       <c r="R54">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T54">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U54">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X54">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z54">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="AA54">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AB54">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AC54">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE54">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF54">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG54">
         <v>1.85</v>
@@ -9177,41 +9177,41 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G55">
@@ -9270,68 +9270,68 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="O55">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P55">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q55">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="R55">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T55">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U55">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V55">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z55">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA55">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB55">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC55">
         <v>3.9</v>
       </c>
       <c r="AD55">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE55">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG55">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,37 +9344,37 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AK55">
+        <v>1.29</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>1</v>
+      </c>
+      <c r="AN55">
+        <v>6</v>
+      </c>
+      <c r="AO55">
+        <v>8</v>
+      </c>
+      <c r="AP55">
+        <v>23</v>
+      </c>
+      <c r="AQ55">
         <v>1.33</v>
       </c>
-      <c r="AL55">
-        <v>0</v>
-      </c>
-      <c r="AM55">
-        <v>-1</v>
-      </c>
-      <c r="AN55">
-        <v>-1</v>
-      </c>
-      <c r="AO55">
-        <v>-1</v>
-      </c>
-      <c r="AP55">
-        <v>-1</v>
-      </c>
-      <c r="AQ55">
-        <v>0</v>
-      </c>
       <c r="AR55">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9405,19 +9405,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -9426,118 +9426,118 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="O56">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="P56">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="Q56">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S56">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T56">
         <v>2.29</v>
       </c>
       <c r="U56">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="V56">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z56">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AA56">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB56">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC56">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AD56">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
         <v>1.95</v>
       </c>
       <c r="AG56">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ56">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL56">
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -9568,16 +9568,16 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -9589,118 +9589,118 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N57">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="P57">
-        <v>3.01</v>
+        <v>3.34</v>
       </c>
       <c r="Q57">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R57">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S57">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T57">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U57">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V57">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W57">
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y57">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z57">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="AA57">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="AB57">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC57">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD57">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG57">
         <v>1.73</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
+          <t>["90+8"]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK57">
+        <v>1.62</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>2</v>
+      </c>
+      <c r="AN57">
+        <v>7</v>
+      </c>
+      <c r="AO57">
+        <v>13</v>
+      </c>
+      <c r="AP57">
+        <v>12</v>
+      </c>
+      <c r="AQ57">
+        <v>1.36</v>
+      </c>
+      <c r="AR57">
         <v>1.58</v>
       </c>
-      <c r="AL57">
-        <v>0</v>
-      </c>
-      <c r="AM57">
-        <v>-1</v>
-      </c>
-      <c r="AN57">
-        <v>-1</v>
-      </c>
-      <c r="AO57">
-        <v>-1</v>
-      </c>
-      <c r="AP57">
-        <v>-1</v>
-      </c>
-      <c r="AQ57">
-        <v>0</v>
-      </c>
-      <c r="AR57">
-        <v>0</v>
-      </c>
       <c r="AS57">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
@@ -9716,40 +9716,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58">
         <v>0</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -9759,115 +9759,115 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q58">
-        <v>4.03</v>
+        <v>2.55</v>
       </c>
       <c r="R58">
+        <v>2.69</v>
+      </c>
+      <c r="S58">
+        <v>1.14</v>
+      </c>
+      <c r="T58">
+        <v>4.7</v>
+      </c>
+      <c r="U58">
+        <v>1.79</v>
+      </c>
+      <c r="V58">
+        <v>1.94</v>
+      </c>
+      <c r="W58">
+        <v>1.26</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.03</v>
+      </c>
+      <c r="Z58">
+        <v>9</v>
+      </c>
+      <c r="AA58">
+        <v>1.2</v>
+      </c>
+      <c r="AB58">
+        <v>4</v>
+      </c>
+      <c r="AC58">
+        <v>1.65</v>
+      </c>
+      <c r="AD58">
+        <v>2.17</v>
+      </c>
+      <c r="AE58">
+        <v>1.55</v>
+      </c>
+      <c r="AF58">
+        <v>1.22</v>
+      </c>
+      <c r="AG58">
+        <v>3.5</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>["29", "40"]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.17</v>
+      </c>
+      <c r="AK58">
+        <v>1.55</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>5</v>
+      </c>
+      <c r="AN58">
+        <v>8</v>
+      </c>
+      <c r="AO58">
+        <v>15</v>
+      </c>
+      <c r="AP58">
+        <v>20</v>
+      </c>
+      <c r="AQ58">
         <v>1.95</v>
       </c>
-      <c r="S58">
-        <v>1.48</v>
-      </c>
-      <c r="T58">
-        <v>2.47</v>
-      </c>
-      <c r="U58">
-        <v>3.4</v>
-      </c>
-      <c r="V58">
-        <v>1.29</v>
-      </c>
-      <c r="W58">
-        <v>1.03</v>
-      </c>
-      <c r="X58">
-        <v>1.05</v>
-      </c>
-      <c r="Y58">
-        <v>1.4</v>
-      </c>
-      <c r="Z58">
-        <v>2.75</v>
-      </c>
-      <c r="AA58">
-        <v>2.3</v>
-      </c>
-      <c r="AB58">
-        <v>1.58</v>
-      </c>
-      <c r="AC58">
-        <v>4.4</v>
-      </c>
-      <c r="AD58">
-        <v>1.17</v>
-      </c>
-      <c r="AE58">
-        <v>1.02</v>
-      </c>
-      <c r="AF58">
-        <v>1.93</v>
-      </c>
-      <c r="AG58">
-        <v>1.77</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.33</v>
-      </c>
-      <c r="AK58">
-        <v>1.29</v>
-      </c>
-      <c r="AL58">
-        <v>0</v>
-      </c>
-      <c r="AM58">
-        <v>-1</v>
-      </c>
-      <c r="AN58">
-        <v>-1</v>
-      </c>
-      <c r="AO58">
-        <v>-1</v>
-      </c>
-      <c r="AP58">
-        <v>-1</v>
-      </c>
-      <c r="AQ58">
-        <v>0</v>
-      </c>
       <c r="AR58">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-31 16:00:00</t>
+          <t>2026-08-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9884,91 +9884,91 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="O59">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="P59">
-        <v>2.9</v>
+        <v>17</v>
       </c>
       <c r="Q59">
-        <v>2.4</v>
+        <v>1.38</v>
       </c>
       <c r="R59">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="S59">
         <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="U59">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V59">
         <v>1.95</v>
       </c>
       <c r="W59">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z59">
         <v>7.8</v>
       </c>
       <c r="AA59">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB59">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="AC59">
         <v>1.71</v>
@@ -9977,56 +9977,56 @@
         <v>2.15</v>
       </c>
       <c r="AE59">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF59">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG59">
-        <v>3.56</v>
+        <v>1.65</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "51"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ59">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AK59">
-        <v>1.77</v>
+        <v>5.75</v>
       </c>
       <c r="AL59">
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10057,16 +10057,16 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -10078,118 +10078,118 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
+        <v>1.8</v>
+      </c>
+      <c r="O60">
+        <v>3.45</v>
+      </c>
+      <c r="P60">
+        <v>4.85</v>
+      </c>
+      <c r="Q60">
+        <v>2.45</v>
+      </c>
+      <c r="R60">
+        <v>2.04</v>
+      </c>
+      <c r="S60">
+        <v>1.38</v>
+      </c>
+      <c r="T60">
+        <v>2.7</v>
+      </c>
+      <c r="U60">
+        <v>2.88</v>
+      </c>
+      <c r="V60">
+        <v>1.41</v>
+      </c>
+      <c r="W60">
+        <v>1.02</v>
+      </c>
+      <c r="X60">
+        <v>1.03</v>
+      </c>
+      <c r="Y60">
+        <v>1.3</v>
+      </c>
+      <c r="Z60">
+        <v>3.05</v>
+      </c>
+      <c r="AA60">
+        <v>2.08</v>
+      </c>
+      <c r="AB60">
+        <v>1.76</v>
+      </c>
+      <c r="AC60">
+        <v>3.8</v>
+      </c>
+      <c r="AD60">
+        <v>1.24</v>
+      </c>
+      <c r="AE60">
+        <v>1.09</v>
+      </c>
+      <c r="AF60">
+        <v>2</v>
+      </c>
+      <c r="AG60">
+        <v>1.73</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>["79"]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.22</v>
+      </c>
+      <c r="AK60">
+        <v>1.9</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>4</v>
+      </c>
+      <c r="AN60">
+        <v>2</v>
+      </c>
+      <c r="AO60">
+        <v>9</v>
+      </c>
+      <c r="AP60">
+        <v>8</v>
+      </c>
+      <c r="AQ60">
         <v>1.15</v>
       </c>
-      <c r="O60">
-        <v>7.5</v>
-      </c>
-      <c r="P60">
-        <v>19</v>
-      </c>
-      <c r="Q60">
-        <v>1.49</v>
-      </c>
-      <c r="R60">
-        <v>3.4</v>
-      </c>
-      <c r="S60">
-        <v>1.18</v>
-      </c>
-      <c r="T60">
-        <v>4.5</v>
-      </c>
-      <c r="U60">
-        <v>2.02</v>
-      </c>
-      <c r="V60">
-        <v>1.79</v>
-      </c>
-      <c r="W60">
-        <v>1.19</v>
-      </c>
-      <c r="X60">
-        <v>1.01</v>
-      </c>
-      <c r="Y60">
-        <v>1.07</v>
-      </c>
-      <c r="Z60">
-        <v>7</v>
-      </c>
-      <c r="AA60">
-        <v>1.32</v>
-      </c>
-      <c r="AB60">
-        <v>2.94</v>
-      </c>
-      <c r="AC60">
-        <v>1.94</v>
-      </c>
-      <c r="AD60">
-        <v>1.94</v>
-      </c>
-      <c r="AE60">
-        <v>1.31</v>
-      </c>
-      <c r="AF60">
-        <v>1.93</v>
-      </c>
-      <c r="AG60">
-        <v>1.8</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.08</v>
-      </c>
-      <c r="AK60">
-        <v>5.6</v>
-      </c>
-      <c r="AL60">
-        <v>0</v>
-      </c>
-      <c r="AM60">
-        <v>-1</v>
-      </c>
-      <c r="AN60">
-        <v>-1</v>
-      </c>
-      <c r="AO60">
-        <v>-1</v>
-      </c>
-      <c r="AP60">
-        <v>-1</v>
-      </c>
-      <c r="AQ60">
-        <v>0</v>
-      </c>
       <c r="AR60">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.75</v>
+        <v>4.22</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P61">
-        <v>4.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q61">
-        <v>2.29</v>
+        <v>4.45</v>
       </c>
       <c r="R61">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="S61">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="U61">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="V61">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>3.73</v>
+        <v>4.1</v>
       </c>
       <c r="AA61">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC61">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD61">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
         <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AG61">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK61">
-        <v>2.09</v>
+        <v>1.23</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-31 16:15:00</t>
+          <t>2026-08-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,139 +10383,139 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
-        <v>4.22</v>
+        <v>1.12</v>
       </c>
       <c r="O62">
-        <v>3.88</v>
+        <v>11</v>
       </c>
       <c r="P62">
-        <v>1.79</v>
+        <v>17</v>
       </c>
       <c r="Q62">
-        <v>4.45</v>
+        <v>1.38</v>
       </c>
       <c r="R62">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T62">
-        <v>3.22</v>
+        <v>4.95</v>
       </c>
       <c r="U62">
-        <v>2.72</v>
+        <v>1.62</v>
       </c>
       <c r="V62">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="W62">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z62">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC62">
-        <v>2.83</v>
+        <v>1.52</v>
       </c>
       <c r="AD62">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.74</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG62">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "21", "51", "71", "90"]</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "59"]</t>
         </is>
       </c>
       <c r="AJ62">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AK62">
-        <v>1.23</v>
+        <v>8</v>
       </c>
       <c r="AL62">
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN62">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO62">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP62">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ62">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AR62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS62">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT62">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G63">
@@ -10574,68 +10574,68 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N63">
+        <v>4.3</v>
+      </c>
+      <c r="O63">
+        <v>3.6</v>
+      </c>
+      <c r="P63">
+        <v>1.63</v>
+      </c>
+      <c r="Q63">
+        <v>5.25</v>
+      </c>
+      <c r="R63">
+        <v>2.25</v>
+      </c>
+      <c r="S63">
+        <v>1.37</v>
+      </c>
+      <c r="T63">
+        <v>2.73</v>
+      </c>
+      <c r="U63">
+        <v>2.84</v>
+      </c>
+      <c r="V63">
+        <v>1.42</v>
+      </c>
+      <c r="W63">
+        <v>1.05</v>
+      </c>
+      <c r="X63">
+        <v>1.04</v>
+      </c>
+      <c r="Y63">
+        <v>1.25</v>
+      </c>
+      <c r="Z63">
+        <v>3.5</v>
+      </c>
+      <c r="AA63">
+        <v>1.85</v>
+      </c>
+      <c r="AB63">
+        <v>1.96</v>
+      </c>
+      <c r="AC63">
+        <v>2.83</v>
+      </c>
+      <c r="AD63">
+        <v>1.33</v>
+      </c>
+      <c r="AE63">
         <v>1.08</v>
       </c>
-      <c r="O63">
-        <v>10</v>
-      </c>
-      <c r="P63">
-        <v>19</v>
-      </c>
-      <c r="Q63">
-        <v>1.46</v>
-      </c>
-      <c r="R63">
-        <v>3.44</v>
-      </c>
-      <c r="S63">
-        <v>1.16</v>
-      </c>
-      <c r="T63">
-        <v>4.9</v>
-      </c>
-      <c r="U63">
-        <v>1.79</v>
-      </c>
-      <c r="V63">
-        <v>1.88</v>
-      </c>
-      <c r="W63">
-        <v>1.26</v>
-      </c>
-      <c r="X63">
-        <v>1.01</v>
-      </c>
-      <c r="Y63">
-        <v>1.07</v>
-      </c>
-      <c r="Z63">
-        <v>8</v>
-      </c>
-      <c r="AA63">
-        <v>1.28</v>
-      </c>
-      <c r="AB63">
-        <v>3.75</v>
-      </c>
-      <c r="AC63">
-        <v>1.78</v>
-      </c>
-      <c r="AD63">
-        <v>2.2</v>
-      </c>
-      <c r="AE63">
-        <v>1.47</v>
-      </c>
       <c r="AF63">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,37 +10648,37 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK63">
-        <v>5.6</v>
+        <v>1.12</v>
       </c>
       <c r="AL63">
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN63">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO63">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP63">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -11073,58 +11073,58 @@
         <v>3.35</v>
       </c>
       <c r="P66">
-        <v>4.2</v>
+        <v>4.97</v>
       </c>
       <c r="Q66">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R66">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S66">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T66">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U66">
         <v>3</v>
       </c>
       <c r="V66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z66">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AA66">
         <v>2.25</v>
       </c>
       <c r="AB66">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC66">
-        <v>3.82</v>
+        <v>4.17</v>
       </c>
       <c r="AD66">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE66">
         <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AG66">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="P70">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q70">
         <v>0</v>
